--- a/売上管理マクロ/2025年営業実績（FS業務)だみー.xlsx
+++ b/売上管理マクロ/2025年営業実績（FS業務)だみー.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB53771E-A534-45A8-94AA-93376F5635C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006AC59B-E446-4B53-9CC5-F8DC4C1CDC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="777" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="777" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ" sheetId="39" r:id="rId1"/>
@@ -5874,6 +5874,24 @@
     <xf numFmtId="176" fontId="16" fillId="5" borderId="225" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5883,6 +5901,60 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="188" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="187" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="187" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="187" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5901,46 +5973,25 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5949,106 +6000,10 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="187" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="188" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="229" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="38" fontId="22" fillId="16" borderId="135" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6136,67 +6091,112 @@
     <xf numFmtId="0" fontId="21" fillId="16" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="188" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="187" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="187" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="187" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="184" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="186" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="187" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="188" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="230" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="229" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6784,58 +6784,58 @@
         <v>88</v>
       </c>
       <c r="C1" s="133"/>
-      <c r="D1" s="604" t="s">
+      <c r="D1" s="589" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="608"/>
-      <c r="F1" s="606" t="s">
+      <c r="E1" s="593"/>
+      <c r="F1" s="591" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="607"/>
-      <c r="H1" s="606" t="s">
+      <c r="G1" s="592"/>
+      <c r="H1" s="591" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="607"/>
-      <c r="J1" s="608" t="s">
+      <c r="I1" s="592"/>
+      <c r="J1" s="593" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="607"/>
-      <c r="L1" s="606" t="s">
+      <c r="K1" s="592"/>
+      <c r="L1" s="591" t="s">
         <v>58</v>
       </c>
-      <c r="M1" s="607"/>
-      <c r="N1" s="606" t="s">
+      <c r="M1" s="592"/>
+      <c r="N1" s="591" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="607"/>
-      <c r="P1" s="606" t="s">
+      <c r="O1" s="592"/>
+      <c r="P1" s="591" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="607"/>
-      <c r="R1" s="606" t="s">
+      <c r="Q1" s="592"/>
+      <c r="R1" s="591" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="607"/>
-      <c r="T1" s="606" t="s">
+      <c r="S1" s="592"/>
+      <c r="T1" s="591" t="s">
         <v>62</v>
       </c>
-      <c r="U1" s="607"/>
-      <c r="V1" s="606" t="s">
+      <c r="U1" s="592"/>
+      <c r="V1" s="591" t="s">
         <v>63</v>
       </c>
-      <c r="W1" s="607"/>
-      <c r="X1" s="606" t="s">
+      <c r="W1" s="592"/>
+      <c r="X1" s="591" t="s">
         <v>64</v>
       </c>
-      <c r="Y1" s="607"/>
-      <c r="Z1" s="608" t="s">
+      <c r="Y1" s="592"/>
+      <c r="Z1" s="593" t="s">
         <v>65</v>
       </c>
-      <c r="AA1" s="609"/>
-      <c r="AB1" s="604" t="s">
+      <c r="AA1" s="594"/>
+      <c r="AB1" s="589" t="s">
         <v>75</v>
       </c>
-      <c r="AC1" s="605"/>
+      <c r="AC1" s="590"/>
     </row>
     <row r="2" spans="1:29" ht="21.75" customHeight="1">
       <c r="B2" s="135" t="s">
@@ -8817,268 +8817,268 @@
     </row>
     <row r="34" spans="2:29" ht="14.5" thickBot="1">
       <c r="C34" s="124"/>
-      <c r="D34" s="593" t="s">
+      <c r="D34" s="578" t="s">
         <v>79</v>
       </c>
-      <c r="E34" s="594"/>
-      <c r="F34" s="593" t="s">
+      <c r="E34" s="579"/>
+      <c r="F34" s="578" t="s">
         <v>55</v>
       </c>
-      <c r="G34" s="594"/>
-      <c r="H34" s="593" t="s">
+      <c r="G34" s="579"/>
+      <c r="H34" s="578" t="s">
         <v>56</v>
       </c>
-      <c r="I34" s="594"/>
-      <c r="J34" s="593" t="s">
+      <c r="I34" s="579"/>
+      <c r="J34" s="578" t="s">
         <v>57</v>
       </c>
-      <c r="K34" s="594"/>
-      <c r="L34" s="593" t="s">
+      <c r="K34" s="579"/>
+      <c r="L34" s="578" t="s">
         <v>58</v>
       </c>
-      <c r="M34" s="594"/>
-      <c r="N34" s="593" t="s">
+      <c r="M34" s="579"/>
+      <c r="N34" s="578" t="s">
         <v>59</v>
       </c>
-      <c r="O34" s="594"/>
-      <c r="P34" s="593" t="s">
+      <c r="O34" s="579"/>
+      <c r="P34" s="578" t="s">
         <v>60</v>
       </c>
-      <c r="Q34" s="594"/>
-      <c r="R34" s="593" t="s">
+      <c r="Q34" s="579"/>
+      <c r="R34" s="578" t="s">
         <v>61</v>
       </c>
-      <c r="S34" s="594"/>
-      <c r="T34" s="593" t="s">
+      <c r="S34" s="579"/>
+      <c r="T34" s="578" t="s">
         <v>62</v>
       </c>
-      <c r="U34" s="594"/>
-      <c r="V34" s="593" t="s">
+      <c r="U34" s="579"/>
+      <c r="V34" s="578" t="s">
         <v>63</v>
       </c>
-      <c r="W34" s="594"/>
-      <c r="X34" s="593" t="s">
+      <c r="W34" s="579"/>
+      <c r="X34" s="578" t="s">
         <v>64</v>
       </c>
-      <c r="Y34" s="594"/>
-      <c r="Z34" s="593" t="s">
+      <c r="Y34" s="579"/>
+      <c r="Z34" s="578" t="s">
         <v>65</v>
       </c>
-      <c r="AA34" s="595"/>
-      <c r="AB34" s="596" t="s">
+      <c r="AA34" s="580"/>
+      <c r="AB34" s="581" t="s">
         <v>80</v>
       </c>
-      <c r="AC34" s="597"/>
+      <c r="AC34" s="582"/>
     </row>
     <row r="35" spans="2:29" ht="14">
       <c r="C35" s="125" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="598">
+      <c r="D35" s="583">
         <f>E8+E20+E27</f>
         <v>24872000</v>
       </c>
-      <c r="E35" s="599"/>
-      <c r="F35" s="598">
+      <c r="E35" s="584"/>
+      <c r="F35" s="583">
         <f>G8+G20+G27</f>
         <v>25208500</v>
       </c>
-      <c r="G35" s="599"/>
-      <c r="H35" s="598">
+      <c r="G35" s="584"/>
+      <c r="H35" s="583">
         <f>I8+I20+I27</f>
         <v>23849000</v>
       </c>
-      <c r="I35" s="599"/>
-      <c r="J35" s="598">
+      <c r="I35" s="584"/>
+      <c r="J35" s="583">
         <f t="shared" ref="J35" si="29">K8+K20+K27</f>
         <v>24079955</v>
       </c>
-      <c r="K35" s="599"/>
-      <c r="L35" s="598">
+      <c r="K35" s="584"/>
+      <c r="L35" s="583">
         <f t="shared" ref="L35" si="30">M8+M20+M27</f>
         <v>22063525</v>
       </c>
-      <c r="M35" s="599"/>
-      <c r="N35" s="598">
+      <c r="M35" s="584"/>
+      <c r="N35" s="583">
         <f>O8+O20+O27</f>
         <v>22324945</v>
       </c>
-      <c r="O35" s="599"/>
-      <c r="P35" s="598">
+      <c r="O35" s="584"/>
+      <c r="P35" s="583">
         <f t="shared" ref="P35" si="31">Q8+Q20+Q27</f>
         <v>21906435</v>
       </c>
-      <c r="Q35" s="599"/>
-      <c r="R35" s="598">
+      <c r="Q35" s="584"/>
+      <c r="R35" s="583">
         <f t="shared" ref="R35" si="32">S8+S20+S27</f>
         <v>21510630</v>
       </c>
-      <c r="S35" s="599"/>
-      <c r="T35" s="598">
+      <c r="S35" s="584"/>
+      <c r="T35" s="583">
         <f t="shared" ref="T35" si="33">U8+U20+U27</f>
         <v>22846290</v>
       </c>
-      <c r="U35" s="599"/>
-      <c r="V35" s="598">
+      <c r="U35" s="584"/>
+      <c r="V35" s="583">
         <f t="shared" ref="V35" si="34">W8+W20+W27</f>
         <v>20680425</v>
       </c>
-      <c r="W35" s="599"/>
-      <c r="X35" s="598">
+      <c r="W35" s="584"/>
+      <c r="X35" s="583">
         <f t="shared" ref="X35" si="35">Y8+Y20+Y27</f>
         <v>20245900</v>
       </c>
-      <c r="Y35" s="599"/>
-      <c r="Z35" s="602">
+      <c r="Y35" s="584"/>
+      <c r="Z35" s="587">
         <f t="shared" ref="Z35" si="36">AA8+AA20+AA27</f>
         <v>23251080</v>
       </c>
-      <c r="AA35" s="603"/>
-      <c r="AB35" s="600">
+      <c r="AA35" s="588"/>
+      <c r="AB35" s="585">
         <f>SUM(D35:Z35)</f>
         <v>272838685</v>
       </c>
-      <c r="AC35" s="601"/>
+      <c r="AC35" s="586"/>
     </row>
     <row r="36" spans="2:29" ht="14">
       <c r="C36" s="126" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="581">
+      <c r="D36" s="566">
         <f>E14+E23+E30</f>
         <v>16138382</v>
       </c>
-      <c r="E36" s="582"/>
-      <c r="F36" s="581">
+      <c r="E36" s="567"/>
+      <c r="F36" s="566">
         <f>G14+G23+G30</f>
         <v>15506005</v>
       </c>
-      <c r="G36" s="582"/>
-      <c r="H36" s="581">
+      <c r="G36" s="567"/>
+      <c r="H36" s="566">
         <f>I14+I23+I30</f>
         <v>15517156</v>
       </c>
-      <c r="I36" s="582"/>
-      <c r="J36" s="581">
+      <c r="I36" s="567"/>
+      <c r="J36" s="566">
         <f t="shared" ref="J36" si="37">K14+K23+K30</f>
         <v>15608812</v>
       </c>
-      <c r="K36" s="582"/>
-      <c r="L36" s="581">
+      <c r="K36" s="567"/>
+      <c r="L36" s="566">
         <f t="shared" ref="L36" si="38">M14+M23+M30</f>
         <v>15473091</v>
       </c>
-      <c r="M36" s="582"/>
-      <c r="N36" s="581">
+      <c r="M36" s="567"/>
+      <c r="N36" s="566">
         <f t="shared" ref="N36" si="39">O14+O23+O30</f>
         <v>15611342</v>
       </c>
-      <c r="O36" s="582"/>
-      <c r="P36" s="581">
+      <c r="O36" s="567"/>
+      <c r="P36" s="566">
         <f t="shared" ref="P36" si="40">Q14+Q23+Q30</f>
         <v>14715435.968020039</v>
       </c>
-      <c r="Q36" s="582"/>
-      <c r="R36" s="581">
+      <c r="Q36" s="567"/>
+      <c r="R36" s="566">
         <f t="shared" ref="R36" si="41">S14+S23+S30</f>
         <v>14561770</v>
       </c>
-      <c r="S36" s="582"/>
-      <c r="T36" s="581">
+      <c r="S36" s="567"/>
+      <c r="T36" s="566">
         <f t="shared" ref="T36" si="42">U14+U23+U30</f>
         <v>15018225.423097797</v>
       </c>
-      <c r="U36" s="582"/>
-      <c r="V36" s="581">
+      <c r="U36" s="567"/>
+      <c r="V36" s="566">
         <f t="shared" ref="V36" si="43">W14+W23+W30</f>
         <v>14605413</v>
       </c>
-      <c r="W36" s="582"/>
-      <c r="X36" s="581">
+      <c r="W36" s="567"/>
+      <c r="X36" s="566">
         <f t="shared" ref="X36" si="44">Y14+Y23+Y30</f>
         <v>14624170</v>
       </c>
-      <c r="Y36" s="582"/>
-      <c r="Z36" s="585">
+      <c r="Y36" s="567"/>
+      <c r="Z36" s="570">
         <f t="shared" ref="Z36" si="45">AA14+AA23+AA30</f>
         <v>11887402.444444444</v>
       </c>
-      <c r="AA36" s="586"/>
-      <c r="AB36" s="583">
+      <c r="AA36" s="571"/>
+      <c r="AB36" s="568">
         <f>SUM(D36:Z36)</f>
         <v>179267204.83556229</v>
       </c>
-      <c r="AC36" s="584"/>
+      <c r="AC36" s="569"/>
     </row>
     <row r="37" spans="2:29" ht="14.5" thickBot="1">
       <c r="C37" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="D37" s="587">
+      <c r="D37" s="572">
         <f>D35-D36</f>
         <v>8733618</v>
       </c>
-      <c r="E37" s="588"/>
-      <c r="F37" s="587">
+      <c r="E37" s="573"/>
+      <c r="F37" s="572">
         <f>F35-F36</f>
         <v>9702495</v>
       </c>
-      <c r="G37" s="588"/>
-      <c r="H37" s="587">
+      <c r="G37" s="573"/>
+      <c r="H37" s="572">
         <f>H35-H36</f>
         <v>8331844</v>
       </c>
-      <c r="I37" s="588"/>
-      <c r="J37" s="587">
+      <c r="I37" s="573"/>
+      <c r="J37" s="572">
         <f>J35-J36</f>
         <v>8471143</v>
       </c>
-      <c r="K37" s="588"/>
-      <c r="L37" s="587">
+      <c r="K37" s="573"/>
+      <c r="L37" s="572">
         <f>L35-L36</f>
         <v>6590434</v>
       </c>
-      <c r="M37" s="588"/>
-      <c r="N37" s="587">
+      <c r="M37" s="573"/>
+      <c r="N37" s="572">
         <f>N35-N36</f>
         <v>6713603</v>
       </c>
-      <c r="O37" s="588"/>
-      <c r="P37" s="587">
+      <c r="O37" s="573"/>
+      <c r="P37" s="572">
         <f>P35-P36</f>
         <v>7190999.0319799613</v>
       </c>
-      <c r="Q37" s="588"/>
-      <c r="R37" s="587">
+      <c r="Q37" s="573"/>
+      <c r="R37" s="572">
         <f>R35-R36</f>
         <v>6948860</v>
       </c>
-      <c r="S37" s="588"/>
-      <c r="T37" s="587">
+      <c r="S37" s="573"/>
+      <c r="T37" s="572">
         <f>T35-T36</f>
         <v>7828064.5769022033</v>
       </c>
-      <c r="U37" s="588"/>
-      <c r="V37" s="587">
+      <c r="U37" s="573"/>
+      <c r="V37" s="572">
         <f>V35-V36</f>
         <v>6075012</v>
       </c>
-      <c r="W37" s="588"/>
-      <c r="X37" s="587">
+      <c r="W37" s="573"/>
+      <c r="X37" s="572">
         <f>X35-X36</f>
         <v>5621730</v>
       </c>
-      <c r="Y37" s="588"/>
-      <c r="Z37" s="591">
+      <c r="Y37" s="573"/>
+      <c r="Z37" s="576">
         <f>Z35-Z36</f>
         <v>11363677.555555556</v>
       </c>
-      <c r="AA37" s="592"/>
-      <c r="AB37" s="589">
+      <c r="AA37" s="577"/>
+      <c r="AB37" s="574">
         <f>SUM(D37:Z37)</f>
         <v>93571480.164437711</v>
       </c>
-      <c r="AC37" s="590"/>
+      <c r="AC37" s="575"/>
     </row>
     <row r="38" spans="2:29" ht="13.5" thickBot="1">
       <c r="Z38" s="284"/>
@@ -10162,15 +10162,15 @@
     <row r="2" spans="1:25" s="1" customFormat="1" ht="27.75" customHeight="1">
       <c r="A2" s="28"/>
       <c r="B2" s="25"/>
-      <c r="C2" s="623" t="s">
+      <c r="C2" s="556" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="624"/>
-      <c r="E2" s="624"/>
-      <c r="F2" s="624"/>
-      <c r="G2" s="624"/>
-      <c r="H2" s="624"/>
-      <c r="I2" s="625"/>
+      <c r="D2" s="557"/>
+      <c r="E2" s="557"/>
+      <c r="F2" s="557"/>
+      <c r="G2" s="557"/>
+      <c r="H2" s="557"/>
+      <c r="I2" s="558"/>
       <c r="J2" s="97" t="s">
         <v>35</v>
       </c>
@@ -10235,15 +10235,15 @@
       <c r="A3" s="29">
         <v>2018041</v>
       </c>
-      <c r="C3" s="627">
+      <c r="C3" s="560">
         <v>1</v>
       </c>
-      <c r="D3" s="628"/>
-      <c r="E3" s="628"/>
-      <c r="F3" s="628"/>
-      <c r="G3" s="628"/>
-      <c r="H3" s="628"/>
-      <c r="I3" s="626" t="s">
+      <c r="D3" s="561"/>
+      <c r="E3" s="561"/>
+      <c r="F3" s="561"/>
+      <c r="G3" s="561"/>
+      <c r="H3" s="561"/>
+      <c r="I3" s="559" t="s">
         <v>31</v>
       </c>
       <c r="J3" s="98" t="s">
@@ -10308,13 +10308,13 @@
         <v>2018041</v>
       </c>
       <c r="B4" s="27"/>
-      <c r="C4" s="627"/>
-      <c r="D4" s="628"/>
-      <c r="E4" s="628"/>
-      <c r="F4" s="628"/>
-      <c r="G4" s="628"/>
-      <c r="H4" s="628"/>
-      <c r="I4" s="626"/>
+      <c r="C4" s="560"/>
+      <c r="D4" s="561"/>
+      <c r="E4" s="561"/>
+      <c r="F4" s="561"/>
+      <c r="G4" s="561"/>
+      <c r="H4" s="561"/>
+      <c r="I4" s="559"/>
       <c r="J4" s="91" t="s">
         <v>25</v>
       </c>
@@ -10366,13 +10366,13 @@
         <v>2018041</v>
       </c>
       <c r="B5" s="27"/>
-      <c r="C5" s="627"/>
-      <c r="D5" s="628"/>
-      <c r="E5" s="628"/>
-      <c r="F5" s="628"/>
-      <c r="G5" s="628"/>
-      <c r="H5" s="628"/>
-      <c r="I5" s="626"/>
+      <c r="C5" s="560"/>
+      <c r="D5" s="561"/>
+      <c r="E5" s="561"/>
+      <c r="F5" s="561"/>
+      <c r="G5" s="561"/>
+      <c r="H5" s="561"/>
+      <c r="I5" s="559"/>
       <c r="J5" s="91" t="s">
         <v>37</v>
       </c>
@@ -10402,13 +10402,13 @@
         <v>2018041</v>
       </c>
       <c r="B6" s="27"/>
-      <c r="C6" s="627"/>
-      <c r="D6" s="628"/>
-      <c r="E6" s="628"/>
-      <c r="F6" s="628"/>
-      <c r="G6" s="628"/>
-      <c r="H6" s="628"/>
-      <c r="I6" s="626"/>
+      <c r="C6" s="560"/>
+      <c r="D6" s="561"/>
+      <c r="E6" s="561"/>
+      <c r="F6" s="561"/>
+      <c r="G6" s="561"/>
+      <c r="H6" s="561"/>
+      <c r="I6" s="559"/>
       <c r="J6" s="91" t="s">
         <v>38</v>
       </c>
@@ -10460,13 +10460,13 @@
         <v>2018041</v>
       </c>
       <c r="B7" s="27"/>
-      <c r="C7" s="627"/>
-      <c r="D7" s="628"/>
-      <c r="E7" s="628"/>
-      <c r="F7" s="628"/>
-      <c r="G7" s="628"/>
-      <c r="H7" s="628"/>
-      <c r="I7" s="626"/>
+      <c r="C7" s="560"/>
+      <c r="D7" s="561"/>
+      <c r="E7" s="561"/>
+      <c r="F7" s="561"/>
+      <c r="G7" s="561"/>
+      <c r="H7" s="561"/>
+      <c r="I7" s="559"/>
       <c r="J7" s="91" t="s">
         <v>26</v>
       </c>
@@ -10518,13 +10518,13 @@
         <v>2018041</v>
       </c>
       <c r="B8" s="27"/>
-      <c r="C8" s="627"/>
-      <c r="D8" s="628"/>
-      <c r="E8" s="628"/>
-      <c r="F8" s="628"/>
-      <c r="G8" s="628"/>
-      <c r="H8" s="628"/>
-      <c r="I8" s="626"/>
+      <c r="C8" s="560"/>
+      <c r="D8" s="561"/>
+      <c r="E8" s="561"/>
+      <c r="F8" s="561"/>
+      <c r="G8" s="561"/>
+      <c r="H8" s="561"/>
+      <c r="I8" s="559"/>
       <c r="J8" s="91" t="s">
         <v>27</v>
       </c>
@@ -10576,13 +10576,13 @@
         <v>2018041</v>
       </c>
       <c r="B9" s="27"/>
-      <c r="C9" s="627"/>
-      <c r="D9" s="628"/>
-      <c r="E9" s="628"/>
-      <c r="F9" s="628"/>
-      <c r="G9" s="628"/>
-      <c r="H9" s="628"/>
-      <c r="I9" s="626"/>
+      <c r="C9" s="560"/>
+      <c r="D9" s="561"/>
+      <c r="E9" s="561"/>
+      <c r="F9" s="561"/>
+      <c r="G9" s="561"/>
+      <c r="H9" s="561"/>
+      <c r="I9" s="559"/>
       <c r="J9" s="91" t="s">
         <v>28</v>
       </c>
@@ -10634,13 +10634,13 @@
         <v>2018041</v>
       </c>
       <c r="B10" s="27"/>
-      <c r="C10" s="627"/>
-      <c r="D10" s="628"/>
-      <c r="E10" s="628"/>
-      <c r="F10" s="628"/>
-      <c r="G10" s="628"/>
-      <c r="H10" s="628"/>
-      <c r="I10" s="626"/>
+      <c r="C10" s="560"/>
+      <c r="D10" s="561"/>
+      <c r="E10" s="561"/>
+      <c r="F10" s="561"/>
+      <c r="G10" s="561"/>
+      <c r="H10" s="561"/>
+      <c r="I10" s="559"/>
       <c r="J10" s="92" t="s">
         <v>29</v>
       </c>
@@ -10690,20 +10690,20 @@
       <c r="A11" s="29">
         <v>2022027</v>
       </c>
-      <c r="C11" s="620">
+      <c r="C11" s="544">
         <f>C3+1</f>
         <v>2</v>
       </c>
-      <c r="D11" s="621"/>
-      <c r="E11" s="621" t="s">
+      <c r="D11" s="545"/>
+      <c r="E11" s="545" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="621"/>
-      <c r="G11" s="621"/>
-      <c r="H11" s="621" t="s">
+      <c r="F11" s="545"/>
+      <c r="G11" s="545"/>
+      <c r="H11" s="545" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="619" t="s">
+      <c r="I11" s="543" t="s">
         <v>31</v>
       </c>
       <c r="J11" s="98" t="s">
@@ -10768,13 +10768,13 @@
         <v>2022027</v>
       </c>
       <c r="B12" s="27"/>
-      <c r="C12" s="620"/>
-      <c r="D12" s="621"/>
-      <c r="E12" s="621"/>
-      <c r="F12" s="621"/>
-      <c r="G12" s="621"/>
-      <c r="H12" s="621"/>
-      <c r="I12" s="619"/>
+      <c r="C12" s="544"/>
+      <c r="D12" s="545"/>
+      <c r="E12" s="545"/>
+      <c r="F12" s="545"/>
+      <c r="G12" s="545"/>
+      <c r="H12" s="545"/>
+      <c r="I12" s="543"/>
       <c r="J12" s="91" t="s">
         <v>25</v>
       </c>
@@ -10820,13 +10820,13 @@
         <v>2022027</v>
       </c>
       <c r="B13" s="27"/>
-      <c r="C13" s="620"/>
-      <c r="D13" s="621"/>
-      <c r="E13" s="621"/>
-      <c r="F13" s="621"/>
-      <c r="G13" s="621"/>
-      <c r="H13" s="621"/>
-      <c r="I13" s="619"/>
+      <c r="C13" s="544"/>
+      <c r="D13" s="545"/>
+      <c r="E13" s="545"/>
+      <c r="F13" s="545"/>
+      <c r="G13" s="545"/>
+      <c r="H13" s="545"/>
+      <c r="I13" s="543"/>
       <c r="J13" s="91" t="s">
         <v>37</v>
       </c>
@@ -10872,13 +10872,13 @@
         <v>2022027</v>
       </c>
       <c r="B14" s="27"/>
-      <c r="C14" s="620"/>
-      <c r="D14" s="621"/>
-      <c r="E14" s="621"/>
-      <c r="F14" s="621"/>
-      <c r="G14" s="621"/>
-      <c r="H14" s="621"/>
-      <c r="I14" s="619"/>
+      <c r="C14" s="544"/>
+      <c r="D14" s="545"/>
+      <c r="E14" s="545"/>
+      <c r="F14" s="545"/>
+      <c r="G14" s="545"/>
+      <c r="H14" s="545"/>
+      <c r="I14" s="543"/>
       <c r="J14" s="91" t="s">
         <v>38</v>
       </c>
@@ -10924,13 +10924,13 @@
         <v>2022027</v>
       </c>
       <c r="B15" s="27"/>
-      <c r="C15" s="620"/>
-      <c r="D15" s="621"/>
-      <c r="E15" s="621"/>
-      <c r="F15" s="621"/>
-      <c r="G15" s="621"/>
-      <c r="H15" s="621"/>
-      <c r="I15" s="619"/>
+      <c r="C15" s="544"/>
+      <c r="D15" s="545"/>
+      <c r="E15" s="545"/>
+      <c r="F15" s="545"/>
+      <c r="G15" s="545"/>
+      <c r="H15" s="545"/>
+      <c r="I15" s="543"/>
       <c r="J15" s="91" t="s">
         <v>26</v>
       </c>
@@ -10976,13 +10976,13 @@
         <v>2022027</v>
       </c>
       <c r="B16" s="27"/>
-      <c r="C16" s="620"/>
-      <c r="D16" s="621"/>
-      <c r="E16" s="621"/>
-      <c r="F16" s="621"/>
-      <c r="G16" s="621"/>
-      <c r="H16" s="621"/>
-      <c r="I16" s="619"/>
+      <c r="C16" s="544"/>
+      <c r="D16" s="545"/>
+      <c r="E16" s="545"/>
+      <c r="F16" s="545"/>
+      <c r="G16" s="545"/>
+      <c r="H16" s="545"/>
+      <c r="I16" s="543"/>
       <c r="J16" s="91" t="s">
         <v>27</v>
       </c>
@@ -11028,13 +11028,13 @@
         <v>2022027</v>
       </c>
       <c r="B17" s="27"/>
-      <c r="C17" s="620"/>
-      <c r="D17" s="621"/>
-      <c r="E17" s="621"/>
-      <c r="F17" s="621"/>
-      <c r="G17" s="621"/>
-      <c r="H17" s="621"/>
-      <c r="I17" s="619"/>
+      <c r="C17" s="544"/>
+      <c r="D17" s="545"/>
+      <c r="E17" s="545"/>
+      <c r="F17" s="545"/>
+      <c r="G17" s="545"/>
+      <c r="H17" s="545"/>
+      <c r="I17" s="543"/>
       <c r="J17" s="91" t="s">
         <v>28</v>
       </c>
@@ -11080,13 +11080,13 @@
         <v>2022027</v>
       </c>
       <c r="B18" s="27"/>
-      <c r="C18" s="620"/>
-      <c r="D18" s="621"/>
-      <c r="E18" s="621"/>
-      <c r="F18" s="621"/>
-      <c r="G18" s="621"/>
-      <c r="H18" s="621"/>
-      <c r="I18" s="619"/>
+      <c r="C18" s="544"/>
+      <c r="D18" s="545"/>
+      <c r="E18" s="545"/>
+      <c r="F18" s="545"/>
+      <c r="G18" s="545"/>
+      <c r="H18" s="545"/>
+      <c r="I18" s="543"/>
       <c r="J18" s="92" t="s">
         <v>29</v>
       </c>
@@ -11131,16 +11131,16 @@
         <v>2018037</v>
       </c>
       <c r="B19" s="17"/>
-      <c r="C19" s="540">
+      <c r="C19" s="546">
         <f>C11+1</f>
         <v>3</v>
       </c>
-      <c r="D19" s="525"/>
-      <c r="E19" s="525"/>
-      <c r="F19" s="525"/>
-      <c r="G19" s="525"/>
-      <c r="H19" s="525"/>
-      <c r="I19" s="528" t="s">
+      <c r="D19" s="549"/>
+      <c r="E19" s="549"/>
+      <c r="F19" s="549"/>
+      <c r="G19" s="549"/>
+      <c r="H19" s="549"/>
+      <c r="I19" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J19" s="175" t="s">
@@ -11205,13 +11205,13 @@
         <v>2018037</v>
       </c>
       <c r="B20" s="24"/>
-      <c r="C20" s="541"/>
-      <c r="D20" s="526"/>
-      <c r="E20" s="526"/>
-      <c r="F20" s="526"/>
-      <c r="G20" s="526"/>
-      <c r="H20" s="526"/>
-      <c r="I20" s="529"/>
+      <c r="C20" s="547"/>
+      <c r="D20" s="550"/>
+      <c r="E20" s="550"/>
+      <c r="F20" s="550"/>
+      <c r="G20" s="550"/>
+      <c r="H20" s="550"/>
+      <c r="I20" s="553"/>
       <c r="J20" s="176" t="s">
         <v>25</v>
       </c>
@@ -11259,17 +11259,17 @@
     </row>
     <row r="21" spans="1:24">
       <c r="A21" s="14">
-        <f t="shared" ref="A21:B26" si="8">A20</f>
+        <f t="shared" ref="A21:A26" si="8">A20</f>
         <v>2018037</v>
       </c>
       <c r="B21" s="24"/>
-      <c r="C21" s="541"/>
-      <c r="D21" s="526"/>
-      <c r="E21" s="526"/>
-      <c r="F21" s="526"/>
-      <c r="G21" s="526"/>
-      <c r="H21" s="526"/>
-      <c r="I21" s="529"/>
+      <c r="C21" s="547"/>
+      <c r="D21" s="550"/>
+      <c r="E21" s="550"/>
+      <c r="F21" s="550"/>
+      <c r="G21" s="550"/>
+      <c r="H21" s="550"/>
+      <c r="I21" s="553"/>
       <c r="J21" s="176" t="s">
         <v>37</v>
       </c>
@@ -11299,13 +11299,13 @@
         <v>2018037</v>
       </c>
       <c r="B22" s="24"/>
-      <c r="C22" s="541"/>
-      <c r="D22" s="526"/>
-      <c r="E22" s="526"/>
-      <c r="F22" s="526"/>
-      <c r="G22" s="526"/>
-      <c r="H22" s="526"/>
-      <c r="I22" s="529"/>
+      <c r="C22" s="547"/>
+      <c r="D22" s="550"/>
+      <c r="E22" s="550"/>
+      <c r="F22" s="550"/>
+      <c r="G22" s="550"/>
+      <c r="H22" s="550"/>
+      <c r="I22" s="553"/>
       <c r="J22" s="176" t="s">
         <v>38</v>
       </c>
@@ -11357,13 +11357,13 @@
         <v>2018037</v>
       </c>
       <c r="B23" s="24"/>
-      <c r="C23" s="541"/>
-      <c r="D23" s="526"/>
-      <c r="E23" s="526"/>
-      <c r="F23" s="526"/>
-      <c r="G23" s="526"/>
-      <c r="H23" s="526"/>
-      <c r="I23" s="529"/>
+      <c r="C23" s="547"/>
+      <c r="D23" s="550"/>
+      <c r="E23" s="550"/>
+      <c r="F23" s="550"/>
+      <c r="G23" s="550"/>
+      <c r="H23" s="550"/>
+      <c r="I23" s="553"/>
       <c r="J23" s="176" t="s">
         <v>26</v>
       </c>
@@ -11415,13 +11415,13 @@
         <v>2018037</v>
       </c>
       <c r="B24" s="24"/>
-      <c r="C24" s="541"/>
-      <c r="D24" s="526"/>
-      <c r="E24" s="526"/>
-      <c r="F24" s="526"/>
-      <c r="G24" s="526"/>
-      <c r="H24" s="526"/>
-      <c r="I24" s="529"/>
+      <c r="C24" s="547"/>
+      <c r="D24" s="550"/>
+      <c r="E24" s="550"/>
+      <c r="F24" s="550"/>
+      <c r="G24" s="550"/>
+      <c r="H24" s="550"/>
+      <c r="I24" s="553"/>
       <c r="J24" s="176" t="s">
         <v>27</v>
       </c>
@@ -11473,13 +11473,13 @@
         <v>2018037</v>
       </c>
       <c r="B25" s="24"/>
-      <c r="C25" s="541"/>
-      <c r="D25" s="526"/>
-      <c r="E25" s="526"/>
-      <c r="F25" s="526"/>
-      <c r="G25" s="526"/>
-      <c r="H25" s="526"/>
-      <c r="I25" s="529"/>
+      <c r="C25" s="547"/>
+      <c r="D25" s="550"/>
+      <c r="E25" s="550"/>
+      <c r="F25" s="550"/>
+      <c r="G25" s="550"/>
+      <c r="H25" s="550"/>
+      <c r="I25" s="553"/>
       <c r="J25" s="176" t="s">
         <v>28</v>
       </c>
@@ -11531,13 +11531,13 @@
         <v>2018037</v>
       </c>
       <c r="B26" s="24"/>
-      <c r="C26" s="542"/>
-      <c r="D26" s="527"/>
-      <c r="E26" s="527"/>
-      <c r="F26" s="527"/>
-      <c r="G26" s="527"/>
-      <c r="H26" s="527"/>
-      <c r="I26" s="530"/>
+      <c r="C26" s="548"/>
+      <c r="D26" s="551"/>
+      <c r="E26" s="551"/>
+      <c r="F26" s="551"/>
+      <c r="G26" s="551"/>
+      <c r="H26" s="551"/>
+      <c r="I26" s="554"/>
       <c r="J26" s="177" t="s">
         <v>29</v>
       </c>
@@ -11588,18 +11588,18 @@
         <v>2020024</v>
       </c>
       <c r="B27" s="17"/>
-      <c r="C27" s="522">
+      <c r="C27" s="528">
         <f t="shared" ref="C27" si="9">C19+1</f>
         <v>4</v>
       </c>
-      <c r="D27" s="531"/>
-      <c r="E27" s="531" t="s">
+      <c r="D27" s="522"/>
+      <c r="E27" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="610"/>
-      <c r="G27" s="531"/>
-      <c r="H27" s="531"/>
-      <c r="I27" s="534" t="s">
+      <c r="F27" s="531"/>
+      <c r="G27" s="522"/>
+      <c r="H27" s="522"/>
+      <c r="I27" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J27" s="175" t="s">
@@ -11664,13 +11664,13 @@
         <v>2020024</v>
       </c>
       <c r="B28" s="24"/>
-      <c r="C28" s="523"/>
-      <c r="D28" s="532"/>
-      <c r="E28" s="532"/>
-      <c r="F28" s="611"/>
-      <c r="G28" s="613"/>
-      <c r="H28" s="532"/>
-      <c r="I28" s="535"/>
+      <c r="C28" s="529"/>
+      <c r="D28" s="523"/>
+      <c r="E28" s="523"/>
+      <c r="F28" s="532"/>
+      <c r="G28" s="534"/>
+      <c r="H28" s="523"/>
+      <c r="I28" s="526"/>
       <c r="J28" s="176" t="s">
         <v>25</v>
       </c>
@@ -11700,17 +11700,17 @@
     </row>
     <row r="29" spans="1:24">
       <c r="A29" s="14">
-        <f t="shared" ref="A29:B29" si="12">A28</f>
+        <f t="shared" ref="A29" si="12">A28</f>
         <v>2020024</v>
       </c>
       <c r="B29" s="24"/>
-      <c r="C29" s="523"/>
-      <c r="D29" s="532"/>
-      <c r="E29" s="532"/>
-      <c r="F29" s="611"/>
-      <c r="G29" s="613"/>
-      <c r="H29" s="532"/>
-      <c r="I29" s="535"/>
+      <c r="C29" s="529"/>
+      <c r="D29" s="523"/>
+      <c r="E29" s="523"/>
+      <c r="F29" s="532"/>
+      <c r="G29" s="534"/>
+      <c r="H29" s="523"/>
+      <c r="I29" s="526"/>
       <c r="J29" s="176" t="s">
         <v>37</v>
       </c>
@@ -11734,17 +11734,17 @@
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="14">
-        <f t="shared" ref="A30:B30" si="13">A29</f>
+        <f t="shared" ref="A30" si="13">A29</f>
         <v>2020024</v>
       </c>
       <c r="B30" s="24"/>
-      <c r="C30" s="523"/>
-      <c r="D30" s="532"/>
-      <c r="E30" s="532"/>
-      <c r="F30" s="611"/>
-      <c r="G30" s="613"/>
-      <c r="H30" s="532"/>
-      <c r="I30" s="535"/>
+      <c r="C30" s="529"/>
+      <c r="D30" s="523"/>
+      <c r="E30" s="523"/>
+      <c r="F30" s="532"/>
+      <c r="G30" s="534"/>
+      <c r="H30" s="523"/>
+      <c r="I30" s="526"/>
       <c r="J30" s="176" t="s">
         <v>38</v>
       </c>
@@ -11774,17 +11774,17 @@
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="14">
-        <f t="shared" ref="A31:B31" si="14">A30</f>
+        <f t="shared" ref="A31" si="14">A30</f>
         <v>2020024</v>
       </c>
       <c r="B31" s="24"/>
-      <c r="C31" s="523"/>
-      <c r="D31" s="532"/>
-      <c r="E31" s="532"/>
-      <c r="F31" s="611"/>
-      <c r="G31" s="613"/>
-      <c r="H31" s="532"/>
-      <c r="I31" s="535"/>
+      <c r="C31" s="529"/>
+      <c r="D31" s="523"/>
+      <c r="E31" s="523"/>
+      <c r="F31" s="532"/>
+      <c r="G31" s="534"/>
+      <c r="H31" s="523"/>
+      <c r="I31" s="526"/>
       <c r="J31" s="176" t="s">
         <v>26</v>
       </c>
@@ -11814,17 +11814,17 @@
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="14">
-        <f t="shared" ref="A32:B32" si="15">A31</f>
+        <f t="shared" ref="A32" si="15">A31</f>
         <v>2020024</v>
       </c>
       <c r="B32" s="24"/>
-      <c r="C32" s="523"/>
-      <c r="D32" s="532"/>
-      <c r="E32" s="532"/>
-      <c r="F32" s="611"/>
-      <c r="G32" s="613"/>
-      <c r="H32" s="532"/>
-      <c r="I32" s="535"/>
+      <c r="C32" s="529"/>
+      <c r="D32" s="523"/>
+      <c r="E32" s="523"/>
+      <c r="F32" s="532"/>
+      <c r="G32" s="534"/>
+      <c r="H32" s="523"/>
+      <c r="I32" s="526"/>
       <c r="J32" s="176" t="s">
         <v>27</v>
       </c>
@@ -11854,17 +11854,17 @@
     </row>
     <row r="33" spans="1:24">
       <c r="A33" s="14">
-        <f t="shared" ref="A33:B33" si="16">A32</f>
+        <f t="shared" ref="A33" si="16">A32</f>
         <v>2020024</v>
       </c>
       <c r="B33" s="24"/>
-      <c r="C33" s="523"/>
-      <c r="D33" s="532"/>
-      <c r="E33" s="532"/>
-      <c r="F33" s="611"/>
-      <c r="G33" s="613"/>
-      <c r="H33" s="532"/>
-      <c r="I33" s="535"/>
+      <c r="C33" s="529"/>
+      <c r="D33" s="523"/>
+      <c r="E33" s="523"/>
+      <c r="F33" s="532"/>
+      <c r="G33" s="534"/>
+      <c r="H33" s="523"/>
+      <c r="I33" s="526"/>
       <c r="J33" s="176" t="s">
         <v>28</v>
       </c>
@@ -11894,17 +11894,17 @@
     </row>
     <row r="34" spans="1:24">
       <c r="A34" s="14">
-        <f t="shared" ref="A34:B34" si="17">A33</f>
+        <f t="shared" ref="A34" si="17">A33</f>
         <v>2020024</v>
       </c>
       <c r="B34" s="24"/>
-      <c r="C34" s="524"/>
-      <c r="D34" s="545"/>
-      <c r="E34" s="545"/>
-      <c r="F34" s="629"/>
-      <c r="G34" s="630"/>
-      <c r="H34" s="545"/>
-      <c r="I34" s="546"/>
+      <c r="C34" s="530"/>
+      <c r="D34" s="562"/>
+      <c r="E34" s="562"/>
+      <c r="F34" s="564"/>
+      <c r="G34" s="565"/>
+      <c r="H34" s="562"/>
+      <c r="I34" s="563"/>
       <c r="J34" s="180" t="s">
         <v>29</v>
       </c>
@@ -11935,18 +11935,18 @@
     <row r="35" spans="1:24">
       <c r="A35" s="13"/>
       <c r="B35" s="17"/>
-      <c r="C35" s="522">
+      <c r="C35" s="528">
         <f t="shared" ref="C35" si="18">C27+1</f>
         <v>5</v>
       </c>
-      <c r="D35" s="531"/>
-      <c r="E35" s="531" t="s">
+      <c r="D35" s="522"/>
+      <c r="E35" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="610"/>
-      <c r="G35" s="531"/>
-      <c r="H35" s="531"/>
-      <c r="I35" s="534" t="s">
+      <c r="F35" s="531"/>
+      <c r="G35" s="522"/>
+      <c r="H35" s="522"/>
+      <c r="I35" s="525" t="s">
         <v>103</v>
       </c>
       <c r="J35" s="175" t="s">
@@ -12011,13 +12011,13 @@
         <v>0</v>
       </c>
       <c r="B36" s="24"/>
-      <c r="C36" s="523"/>
-      <c r="D36" s="532"/>
-      <c r="E36" s="532"/>
-      <c r="F36" s="611"/>
-      <c r="G36" s="613"/>
-      <c r="H36" s="532"/>
-      <c r="I36" s="535"/>
+      <c r="C36" s="529"/>
+      <c r="D36" s="523"/>
+      <c r="E36" s="523"/>
+      <c r="F36" s="532"/>
+      <c r="G36" s="534"/>
+      <c r="H36" s="523"/>
+      <c r="I36" s="526"/>
       <c r="J36" s="176" t="s">
         <v>104</v>
       </c>
@@ -12047,17 +12047,17 @@
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="14">
-        <f t="shared" ref="A37:B37" si="21">A36</f>
+        <f t="shared" ref="A37" si="21">A36</f>
         <v>0</v>
       </c>
       <c r="B37" s="24"/>
-      <c r="C37" s="523"/>
-      <c r="D37" s="532"/>
-      <c r="E37" s="532"/>
-      <c r="F37" s="611"/>
-      <c r="G37" s="613"/>
-      <c r="H37" s="532"/>
-      <c r="I37" s="535"/>
+      <c r="C37" s="529"/>
+      <c r="D37" s="523"/>
+      <c r="E37" s="523"/>
+      <c r="F37" s="532"/>
+      <c r="G37" s="534"/>
+      <c r="H37" s="523"/>
+      <c r="I37" s="526"/>
       <c r="J37" s="176"/>
       <c r="K37" s="223"/>
       <c r="L37" s="223"/>
@@ -12079,17 +12079,17 @@
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="14">
-        <f t="shared" ref="A38:B38" si="22">A37</f>
+        <f t="shared" ref="A38" si="22">A37</f>
         <v>0</v>
       </c>
       <c r="B38" s="24"/>
-      <c r="C38" s="523"/>
-      <c r="D38" s="532"/>
-      <c r="E38" s="532"/>
-      <c r="F38" s="611"/>
-      <c r="G38" s="613"/>
-      <c r="H38" s="532"/>
-      <c r="I38" s="535"/>
+      <c r="C38" s="529"/>
+      <c r="D38" s="523"/>
+      <c r="E38" s="523"/>
+      <c r="F38" s="532"/>
+      <c r="G38" s="534"/>
+      <c r="H38" s="523"/>
+      <c r="I38" s="526"/>
       <c r="J38" s="176"/>
       <c r="K38" s="223"/>
       <c r="L38" s="223"/>
@@ -12111,17 +12111,17 @@
     </row>
     <row r="39" spans="1:24">
       <c r="A39" s="14">
-        <f t="shared" ref="A39:B39" si="23">A38</f>
+        <f t="shared" ref="A39" si="23">A38</f>
         <v>0</v>
       </c>
       <c r="B39" s="24"/>
-      <c r="C39" s="523"/>
-      <c r="D39" s="532"/>
-      <c r="E39" s="532"/>
-      <c r="F39" s="611"/>
-      <c r="G39" s="613"/>
-      <c r="H39" s="532"/>
-      <c r="I39" s="535"/>
+      <c r="C39" s="529"/>
+      <c r="D39" s="523"/>
+      <c r="E39" s="523"/>
+      <c r="F39" s="532"/>
+      <c r="G39" s="534"/>
+      <c r="H39" s="523"/>
+      <c r="I39" s="526"/>
       <c r="J39" s="176"/>
       <c r="K39" s="224"/>
       <c r="L39" s="224"/>
@@ -12143,17 +12143,17 @@
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="14">
-        <f t="shared" ref="A40:B40" si="24">A39</f>
+        <f t="shared" ref="A40" si="24">A39</f>
         <v>0</v>
       </c>
       <c r="B40" s="24"/>
-      <c r="C40" s="523"/>
-      <c r="D40" s="532"/>
-      <c r="E40" s="532"/>
-      <c r="F40" s="611"/>
-      <c r="G40" s="613"/>
-      <c r="H40" s="532"/>
-      <c r="I40" s="535"/>
+      <c r="C40" s="529"/>
+      <c r="D40" s="523"/>
+      <c r="E40" s="523"/>
+      <c r="F40" s="532"/>
+      <c r="G40" s="534"/>
+      <c r="H40" s="523"/>
+      <c r="I40" s="526"/>
       <c r="J40" s="176"/>
       <c r="K40" s="224"/>
       <c r="L40" s="224"/>
@@ -12175,17 +12175,17 @@
     </row>
     <row r="41" spans="1:24">
       <c r="A41" s="14">
-        <f t="shared" ref="A41:B41" si="25">A40</f>
+        <f t="shared" ref="A41" si="25">A40</f>
         <v>0</v>
       </c>
       <c r="B41" s="24"/>
-      <c r="C41" s="523"/>
-      <c r="D41" s="532"/>
-      <c r="E41" s="532"/>
-      <c r="F41" s="611"/>
-      <c r="G41" s="613"/>
-      <c r="H41" s="532"/>
-      <c r="I41" s="535"/>
+      <c r="C41" s="529"/>
+      <c r="D41" s="523"/>
+      <c r="E41" s="523"/>
+      <c r="F41" s="532"/>
+      <c r="G41" s="534"/>
+      <c r="H41" s="523"/>
+      <c r="I41" s="526"/>
       <c r="J41" s="176"/>
       <c r="K41" s="224"/>
       <c r="L41" s="224"/>
@@ -12207,17 +12207,17 @@
     </row>
     <row r="42" spans="1:24">
       <c r="A42" s="14">
-        <f t="shared" ref="A42:B42" si="26">A41</f>
+        <f t="shared" ref="A42" si="26">A41</f>
         <v>0</v>
       </c>
       <c r="B42" s="24"/>
-      <c r="C42" s="524"/>
-      <c r="D42" s="533"/>
-      <c r="E42" s="533"/>
-      <c r="F42" s="612"/>
-      <c r="G42" s="614"/>
-      <c r="H42" s="533"/>
-      <c r="I42" s="536"/>
+      <c r="C42" s="530"/>
+      <c r="D42" s="524"/>
+      <c r="E42" s="524"/>
+      <c r="F42" s="533"/>
+      <c r="G42" s="535"/>
+      <c r="H42" s="524"/>
+      <c r="I42" s="527"/>
       <c r="J42" s="182"/>
       <c r="K42" s="452"/>
       <c r="L42" s="452"/>
@@ -12240,16 +12240,16 @@
     <row r="43" spans="1:24">
       <c r="A43" s="13"/>
       <c r="B43" s="17"/>
-      <c r="C43" s="540">
+      <c r="C43" s="546">
         <f t="shared" ref="C43" si="27">C35+1</f>
         <v>6</v>
       </c>
-      <c r="D43" s="531"/>
-      <c r="E43" s="531"/>
-      <c r="F43" s="610"/>
-      <c r="G43" s="531"/>
-      <c r="H43" s="531"/>
-      <c r="I43" s="534" t="s">
+      <c r="D43" s="522"/>
+      <c r="E43" s="522"/>
+      <c r="F43" s="531"/>
+      <c r="G43" s="522"/>
+      <c r="H43" s="522"/>
+      <c r="I43" s="525" t="s">
         <v>103</v>
       </c>
       <c r="J43" s="187" t="s">
@@ -12314,13 +12314,13 @@
         <v>0</v>
       </c>
       <c r="B44" s="24"/>
-      <c r="C44" s="541"/>
-      <c r="D44" s="532"/>
-      <c r="E44" s="532"/>
-      <c r="F44" s="611"/>
-      <c r="G44" s="613"/>
-      <c r="H44" s="532"/>
-      <c r="I44" s="535"/>
+      <c r="C44" s="547"/>
+      <c r="D44" s="523"/>
+      <c r="E44" s="523"/>
+      <c r="F44" s="532"/>
+      <c r="G44" s="534"/>
+      <c r="H44" s="523"/>
+      <c r="I44" s="526"/>
       <c r="J44" s="453" t="s">
         <v>104</v>
       </c>
@@ -12354,17 +12354,17 @@
     </row>
     <row r="45" spans="1:24">
       <c r="A45" s="14">
-        <f t="shared" ref="A45:B50" si="30">A44</f>
+        <f t="shared" ref="A45:A50" si="30">A44</f>
         <v>0</v>
       </c>
       <c r="B45" s="24"/>
-      <c r="C45" s="541"/>
-      <c r="D45" s="532"/>
-      <c r="E45" s="532"/>
-      <c r="F45" s="611"/>
-      <c r="G45" s="613"/>
-      <c r="H45" s="532"/>
-      <c r="I45" s="535"/>
+      <c r="C45" s="547"/>
+      <c r="D45" s="523"/>
+      <c r="E45" s="523"/>
+      <c r="F45" s="532"/>
+      <c r="G45" s="534"/>
+      <c r="H45" s="523"/>
+      <c r="I45" s="526"/>
       <c r="J45" s="453"/>
       <c r="K45" s="223"/>
       <c r="L45" s="223"/>
@@ -12392,13 +12392,13 @@
         <v>0</v>
       </c>
       <c r="B46" s="24"/>
-      <c r="C46" s="541"/>
-      <c r="D46" s="532"/>
-      <c r="E46" s="532"/>
-      <c r="F46" s="611"/>
-      <c r="G46" s="613"/>
-      <c r="H46" s="532"/>
-      <c r="I46" s="535"/>
+      <c r="C46" s="547"/>
+      <c r="D46" s="523"/>
+      <c r="E46" s="523"/>
+      <c r="F46" s="532"/>
+      <c r="G46" s="534"/>
+      <c r="H46" s="523"/>
+      <c r="I46" s="526"/>
       <c r="J46" s="453"/>
       <c r="K46" s="223"/>
       <c r="L46" s="223"/>
@@ -12426,13 +12426,13 @@
         <v>0</v>
       </c>
       <c r="B47" s="24"/>
-      <c r="C47" s="541"/>
-      <c r="D47" s="532"/>
-      <c r="E47" s="532"/>
-      <c r="F47" s="611"/>
-      <c r="G47" s="613"/>
-      <c r="H47" s="532"/>
-      <c r="I47" s="535"/>
+      <c r="C47" s="547"/>
+      <c r="D47" s="523"/>
+      <c r="E47" s="523"/>
+      <c r="F47" s="532"/>
+      <c r="G47" s="534"/>
+      <c r="H47" s="523"/>
+      <c r="I47" s="526"/>
       <c r="J47" s="453"/>
       <c r="K47" s="224"/>
       <c r="L47" s="224"/>
@@ -12460,13 +12460,13 @@
         <v>0</v>
       </c>
       <c r="B48" s="24"/>
-      <c r="C48" s="541"/>
-      <c r="D48" s="532"/>
-      <c r="E48" s="532"/>
-      <c r="F48" s="611"/>
-      <c r="G48" s="613"/>
-      <c r="H48" s="532"/>
-      <c r="I48" s="535"/>
+      <c r="C48" s="547"/>
+      <c r="D48" s="523"/>
+      <c r="E48" s="523"/>
+      <c r="F48" s="532"/>
+      <c r="G48" s="534"/>
+      <c r="H48" s="523"/>
+      <c r="I48" s="526"/>
       <c r="J48" s="453"/>
       <c r="K48" s="224"/>
       <c r="L48" s="224"/>
@@ -12494,13 +12494,13 @@
         <v>0</v>
       </c>
       <c r="B49" s="24"/>
-      <c r="C49" s="541"/>
-      <c r="D49" s="532"/>
-      <c r="E49" s="532"/>
-      <c r="F49" s="611"/>
-      <c r="G49" s="613"/>
-      <c r="H49" s="532"/>
-      <c r="I49" s="535"/>
+      <c r="C49" s="547"/>
+      <c r="D49" s="523"/>
+      <c r="E49" s="523"/>
+      <c r="F49" s="532"/>
+      <c r="G49" s="534"/>
+      <c r="H49" s="523"/>
+      <c r="I49" s="526"/>
       <c r="J49" s="453"/>
       <c r="K49" s="224"/>
       <c r="L49" s="224"/>
@@ -12528,13 +12528,13 @@
         <v>0</v>
       </c>
       <c r="B50" s="24"/>
-      <c r="C50" s="622"/>
-      <c r="D50" s="616"/>
-      <c r="E50" s="616"/>
-      <c r="F50" s="617"/>
-      <c r="G50" s="618"/>
-      <c r="H50" s="616"/>
-      <c r="I50" s="615"/>
+      <c r="C50" s="555"/>
+      <c r="D50" s="537"/>
+      <c r="E50" s="537"/>
+      <c r="F50" s="538"/>
+      <c r="G50" s="539"/>
+      <c r="H50" s="537"/>
+      <c r="I50" s="536"/>
       <c r="J50" s="454"/>
       <c r="K50" s="425"/>
       <c r="L50" s="425"/>
@@ -12559,13 +12559,13 @@
     <row r="51" spans="1:24" ht="32.4" customHeight="1" thickTop="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
-      <c r="C51" s="558"/>
-      <c r="D51" s="559"/>
-      <c r="E51" s="559"/>
-      <c r="F51" s="559"/>
-      <c r="G51" s="559"/>
-      <c r="H51" s="559"/>
-      <c r="I51" s="560"/>
+      <c r="C51" s="540"/>
+      <c r="D51" s="541"/>
+      <c r="E51" s="541"/>
+      <c r="F51" s="541"/>
+      <c r="G51" s="541"/>
+      <c r="H51" s="541"/>
+      <c r="I51" s="542"/>
       <c r="J51" s="96" t="str">
         <f>J2</f>
         <v>人件費合計</v>
@@ -16149,15 +16149,15 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="1" customFormat="1" ht="27.75" customHeight="1">
-      <c r="C2" s="552" t="s">
+      <c r="C2" s="605" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="553"/>
-      <c r="E2" s="553"/>
-      <c r="F2" s="553"/>
-      <c r="G2" s="553"/>
-      <c r="H2" s="553"/>
-      <c r="I2" s="554"/>
+      <c r="D2" s="606"/>
+      <c r="E2" s="606"/>
+      <c r="F2" s="606"/>
+      <c r="G2" s="606"/>
+      <c r="H2" s="606"/>
+      <c r="I2" s="607"/>
       <c r="J2" s="463" t="s">
         <v>35</v>
       </c>
@@ -16222,16 +16222,16 @@
       <c r="A3" s="13">
         <v>2018038</v>
       </c>
-      <c r="C3" s="561">
+      <c r="C3" s="611">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="D3" s="543"/>
-      <c r="E3" s="543"/>
-      <c r="F3" s="543"/>
-      <c r="G3" s="543"/>
-      <c r="H3" s="543"/>
-      <c r="I3" s="544" t="s">
+      <c r="D3" s="598"/>
+      <c r="E3" s="598"/>
+      <c r="F3" s="598"/>
+      <c r="G3" s="598"/>
+      <c r="H3" s="598"/>
+      <c r="I3" s="599" t="s">
         <v>31</v>
       </c>
       <c r="J3" s="187" t="s">
@@ -16296,13 +16296,13 @@
         <v>2018038</v>
       </c>
       <c r="B4" s="24"/>
-      <c r="C4" s="562"/>
-      <c r="D4" s="526"/>
-      <c r="E4" s="526"/>
-      <c r="F4" s="526"/>
-      <c r="G4" s="526"/>
-      <c r="H4" s="526"/>
-      <c r="I4" s="529"/>
+      <c r="C4" s="612"/>
+      <c r="D4" s="550"/>
+      <c r="E4" s="550"/>
+      <c r="F4" s="550"/>
+      <c r="G4" s="550"/>
+      <c r="H4" s="550"/>
+      <c r="I4" s="553"/>
       <c r="J4" s="176" t="s">
         <v>25</v>
       </c>
@@ -16354,13 +16354,13 @@
         <v>2018038</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="C5" s="562"/>
-      <c r="D5" s="526"/>
-      <c r="E5" s="526"/>
-      <c r="F5" s="526"/>
-      <c r="G5" s="526"/>
-      <c r="H5" s="526"/>
-      <c r="I5" s="529"/>
+      <c r="C5" s="612"/>
+      <c r="D5" s="550"/>
+      <c r="E5" s="550"/>
+      <c r="F5" s="550"/>
+      <c r="G5" s="550"/>
+      <c r="H5" s="550"/>
+      <c r="I5" s="553"/>
       <c r="J5" s="176" t="s">
         <v>37</v>
       </c>
@@ -16412,13 +16412,13 @@
         <v>2018038</v>
       </c>
       <c r="B6" s="24"/>
-      <c r="C6" s="562"/>
-      <c r="D6" s="526"/>
-      <c r="E6" s="526"/>
-      <c r="F6" s="526"/>
-      <c r="G6" s="526"/>
-      <c r="H6" s="526"/>
-      <c r="I6" s="529"/>
+      <c r="C6" s="612"/>
+      <c r="D6" s="550"/>
+      <c r="E6" s="550"/>
+      <c r="F6" s="550"/>
+      <c r="G6" s="550"/>
+      <c r="H6" s="550"/>
+      <c r="I6" s="553"/>
       <c r="J6" s="176" t="s">
         <v>38</v>
       </c>
@@ -16470,13 +16470,13 @@
         <v>2018038</v>
       </c>
       <c r="B7" s="24"/>
-      <c r="C7" s="562"/>
-      <c r="D7" s="526"/>
-      <c r="E7" s="526"/>
-      <c r="F7" s="526"/>
-      <c r="G7" s="526"/>
-      <c r="H7" s="526"/>
-      <c r="I7" s="529"/>
+      <c r="C7" s="612"/>
+      <c r="D7" s="550"/>
+      <c r="E7" s="550"/>
+      <c r="F7" s="550"/>
+      <c r="G7" s="550"/>
+      <c r="H7" s="550"/>
+      <c r="I7" s="553"/>
       <c r="J7" s="176" t="s">
         <v>26</v>
       </c>
@@ -16528,13 +16528,13 @@
         <v>2018038</v>
       </c>
       <c r="B8" s="24"/>
-      <c r="C8" s="562"/>
-      <c r="D8" s="526"/>
-      <c r="E8" s="526"/>
-      <c r="F8" s="526"/>
-      <c r="G8" s="526"/>
-      <c r="H8" s="526"/>
-      <c r="I8" s="529"/>
+      <c r="C8" s="612"/>
+      <c r="D8" s="550"/>
+      <c r="E8" s="550"/>
+      <c r="F8" s="550"/>
+      <c r="G8" s="550"/>
+      <c r="H8" s="550"/>
+      <c r="I8" s="553"/>
       <c r="J8" s="176" t="s">
         <v>27</v>
       </c>
@@ -16586,13 +16586,13 @@
         <v>2018038</v>
       </c>
       <c r="B9" s="24"/>
-      <c r="C9" s="562"/>
-      <c r="D9" s="526"/>
-      <c r="E9" s="526"/>
-      <c r="F9" s="526"/>
-      <c r="G9" s="526"/>
-      <c r="H9" s="526"/>
-      <c r="I9" s="529"/>
+      <c r="C9" s="612"/>
+      <c r="D9" s="550"/>
+      <c r="E9" s="550"/>
+      <c r="F9" s="550"/>
+      <c r="G9" s="550"/>
+      <c r="H9" s="550"/>
+      <c r="I9" s="553"/>
       <c r="J9" s="176" t="s">
         <v>28</v>
       </c>
@@ -16644,13 +16644,13 @@
         <v>2018038</v>
       </c>
       <c r="B10" s="24"/>
-      <c r="C10" s="563"/>
-      <c r="D10" s="527"/>
-      <c r="E10" s="527"/>
-      <c r="F10" s="527"/>
-      <c r="G10" s="527"/>
-      <c r="H10" s="527"/>
-      <c r="I10" s="530"/>
+      <c r="C10" s="613"/>
+      <c r="D10" s="551"/>
+      <c r="E10" s="551"/>
+      <c r="F10" s="551"/>
+      <c r="G10" s="551"/>
+      <c r="H10" s="551"/>
+      <c r="I10" s="554"/>
       <c r="J10" s="177" t="s">
         <v>29</v>
       </c>
@@ -16700,16 +16700,16 @@
       <c r="A11" s="13">
         <v>2019002</v>
       </c>
-      <c r="C11" s="564">
+      <c r="C11" s="614">
         <f>C3+1</f>
         <v>2</v>
       </c>
-      <c r="D11" s="525"/>
-      <c r="E11" s="525"/>
-      <c r="F11" s="525"/>
-      <c r="G11" s="525"/>
-      <c r="H11" s="525"/>
-      <c r="I11" s="528" t="s">
+      <c r="D11" s="549"/>
+      <c r="E11" s="549"/>
+      <c r="F11" s="549"/>
+      <c r="G11" s="549"/>
+      <c r="H11" s="549"/>
+      <c r="I11" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J11" s="175" t="s">
@@ -16774,13 +16774,13 @@
         <v>2019002</v>
       </c>
       <c r="B12" s="24"/>
-      <c r="C12" s="562"/>
-      <c r="D12" s="526"/>
-      <c r="E12" s="526"/>
-      <c r="F12" s="526"/>
-      <c r="G12" s="526"/>
-      <c r="H12" s="526"/>
-      <c r="I12" s="529"/>
+      <c r="C12" s="612"/>
+      <c r="D12" s="550"/>
+      <c r="E12" s="550"/>
+      <c r="F12" s="550"/>
+      <c r="G12" s="550"/>
+      <c r="H12" s="550"/>
+      <c r="I12" s="553"/>
       <c r="J12" s="176" t="s">
         <v>25</v>
       </c>
@@ -16832,13 +16832,13 @@
         <v>2019002</v>
       </c>
       <c r="B13" s="24"/>
-      <c r="C13" s="562"/>
-      <c r="D13" s="526"/>
-      <c r="E13" s="526"/>
-      <c r="F13" s="526"/>
-      <c r="G13" s="526"/>
-      <c r="H13" s="526"/>
-      <c r="I13" s="529"/>
+      <c r="C13" s="612"/>
+      <c r="D13" s="550"/>
+      <c r="E13" s="550"/>
+      <c r="F13" s="550"/>
+      <c r="G13" s="550"/>
+      <c r="H13" s="550"/>
+      <c r="I13" s="553"/>
       <c r="J13" s="176" t="s">
         <v>37</v>
       </c>
@@ -16890,13 +16890,13 @@
         <v>2019002</v>
       </c>
       <c r="B14" s="24"/>
-      <c r="C14" s="562"/>
-      <c r="D14" s="526"/>
-      <c r="E14" s="526"/>
-      <c r="F14" s="526"/>
-      <c r="G14" s="526"/>
-      <c r="H14" s="526"/>
-      <c r="I14" s="529"/>
+      <c r="C14" s="612"/>
+      <c r="D14" s="550"/>
+      <c r="E14" s="550"/>
+      <c r="F14" s="550"/>
+      <c r="G14" s="550"/>
+      <c r="H14" s="550"/>
+      <c r="I14" s="553"/>
       <c r="J14" s="176" t="s">
         <v>38</v>
       </c>
@@ -16948,13 +16948,13 @@
         <v>2019002</v>
       </c>
       <c r="B15" s="24"/>
-      <c r="C15" s="562"/>
-      <c r="D15" s="526"/>
-      <c r="E15" s="526"/>
-      <c r="F15" s="526"/>
-      <c r="G15" s="526"/>
-      <c r="H15" s="526"/>
-      <c r="I15" s="529"/>
+      <c r="C15" s="612"/>
+      <c r="D15" s="550"/>
+      <c r="E15" s="550"/>
+      <c r="F15" s="550"/>
+      <c r="G15" s="550"/>
+      <c r="H15" s="550"/>
+      <c r="I15" s="553"/>
       <c r="J15" s="176" t="s">
         <v>26</v>
       </c>
@@ -17006,13 +17006,13 @@
         <v>2019002</v>
       </c>
       <c r="B16" s="24"/>
-      <c r="C16" s="562"/>
-      <c r="D16" s="526"/>
-      <c r="E16" s="526"/>
-      <c r="F16" s="526"/>
-      <c r="G16" s="526"/>
-      <c r="H16" s="526"/>
-      <c r="I16" s="529"/>
+      <c r="C16" s="612"/>
+      <c r="D16" s="550"/>
+      <c r="E16" s="550"/>
+      <c r="F16" s="550"/>
+      <c r="G16" s="550"/>
+      <c r="H16" s="550"/>
+      <c r="I16" s="553"/>
       <c r="J16" s="176" t="s">
         <v>27</v>
       </c>
@@ -17064,13 +17064,13 @@
         <v>2019002</v>
       </c>
       <c r="B17" s="24"/>
-      <c r="C17" s="562"/>
-      <c r="D17" s="526"/>
-      <c r="E17" s="526"/>
-      <c r="F17" s="526"/>
-      <c r="G17" s="526"/>
-      <c r="H17" s="526"/>
-      <c r="I17" s="529"/>
+      <c r="C17" s="612"/>
+      <c r="D17" s="550"/>
+      <c r="E17" s="550"/>
+      <c r="F17" s="550"/>
+      <c r="G17" s="550"/>
+      <c r="H17" s="550"/>
+      <c r="I17" s="553"/>
       <c r="J17" s="176" t="s">
         <v>28</v>
       </c>
@@ -17122,13 +17122,13 @@
         <v>2019002</v>
       </c>
       <c r="B18" s="24"/>
-      <c r="C18" s="563"/>
-      <c r="D18" s="527"/>
-      <c r="E18" s="527"/>
-      <c r="F18" s="527"/>
-      <c r="G18" s="527"/>
-      <c r="H18" s="527"/>
-      <c r="I18" s="530"/>
+      <c r="C18" s="613"/>
+      <c r="D18" s="551"/>
+      <c r="E18" s="551"/>
+      <c r="F18" s="551"/>
+      <c r="G18" s="551"/>
+      <c r="H18" s="551"/>
+      <c r="I18" s="554"/>
       <c r="J18" s="177" t="s">
         <v>29</v>
       </c>
@@ -17178,16 +17178,16 @@
       <c r="A19" s="13">
         <v>2019024</v>
       </c>
-      <c r="C19" s="540">
+      <c r="C19" s="546">
         <f>C11+1</f>
         <v>3</v>
       </c>
-      <c r="D19" s="525"/>
-      <c r="E19" s="525"/>
-      <c r="F19" s="525"/>
-      <c r="G19" s="525"/>
-      <c r="H19" s="525"/>
-      <c r="I19" s="528" t="s">
+      <c r="D19" s="549"/>
+      <c r="E19" s="549"/>
+      <c r="F19" s="549"/>
+      <c r="G19" s="549"/>
+      <c r="H19" s="549"/>
+      <c r="I19" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J19" s="175" t="s">
@@ -17252,13 +17252,13 @@
         <v>2019024</v>
       </c>
       <c r="B20" s="24"/>
-      <c r="C20" s="541"/>
-      <c r="D20" s="526"/>
-      <c r="E20" s="526"/>
-      <c r="F20" s="526"/>
-      <c r="G20" s="526"/>
-      <c r="H20" s="526"/>
-      <c r="I20" s="529"/>
+      <c r="C20" s="547"/>
+      <c r="D20" s="550"/>
+      <c r="E20" s="550"/>
+      <c r="F20" s="550"/>
+      <c r="G20" s="550"/>
+      <c r="H20" s="550"/>
+      <c r="I20" s="553"/>
       <c r="J20" s="176" t="s">
         <v>25</v>
       </c>
@@ -17310,13 +17310,13 @@
         <v>2019024</v>
       </c>
       <c r="B21" s="24"/>
-      <c r="C21" s="541"/>
-      <c r="D21" s="526"/>
-      <c r="E21" s="526"/>
-      <c r="F21" s="526"/>
-      <c r="G21" s="526"/>
-      <c r="H21" s="526"/>
-      <c r="I21" s="529"/>
+      <c r="C21" s="547"/>
+      <c r="D21" s="550"/>
+      <c r="E21" s="550"/>
+      <c r="F21" s="550"/>
+      <c r="G21" s="550"/>
+      <c r="H21" s="550"/>
+      <c r="I21" s="553"/>
       <c r="J21" s="176" t="s">
         <v>37</v>
       </c>
@@ -17368,13 +17368,13 @@
         <v>2019024</v>
       </c>
       <c r="B22" s="24"/>
-      <c r="C22" s="541"/>
-      <c r="D22" s="526"/>
-      <c r="E22" s="526"/>
-      <c r="F22" s="526"/>
-      <c r="G22" s="526"/>
-      <c r="H22" s="526"/>
-      <c r="I22" s="529"/>
+      <c r="C22" s="547"/>
+      <c r="D22" s="550"/>
+      <c r="E22" s="550"/>
+      <c r="F22" s="550"/>
+      <c r="G22" s="550"/>
+      <c r="H22" s="550"/>
+      <c r="I22" s="553"/>
       <c r="J22" s="176" t="s">
         <v>38</v>
       </c>
@@ -17426,13 +17426,13 @@
         <v>2019024</v>
       </c>
       <c r="B23" s="24"/>
-      <c r="C23" s="541"/>
-      <c r="D23" s="526"/>
-      <c r="E23" s="526"/>
-      <c r="F23" s="526"/>
-      <c r="G23" s="526"/>
-      <c r="H23" s="526"/>
-      <c r="I23" s="529"/>
+      <c r="C23" s="547"/>
+      <c r="D23" s="550"/>
+      <c r="E23" s="550"/>
+      <c r="F23" s="550"/>
+      <c r="G23" s="550"/>
+      <c r="H23" s="550"/>
+      <c r="I23" s="553"/>
       <c r="J23" s="176" t="s">
         <v>26</v>
       </c>
@@ -17484,13 +17484,13 @@
         <v>2019024</v>
       </c>
       <c r="B24" s="24"/>
-      <c r="C24" s="541"/>
-      <c r="D24" s="526"/>
-      <c r="E24" s="526"/>
-      <c r="F24" s="526"/>
-      <c r="G24" s="526"/>
-      <c r="H24" s="526"/>
-      <c r="I24" s="529"/>
+      <c r="C24" s="547"/>
+      <c r="D24" s="550"/>
+      <c r="E24" s="550"/>
+      <c r="F24" s="550"/>
+      <c r="G24" s="550"/>
+      <c r="H24" s="550"/>
+      <c r="I24" s="553"/>
       <c r="J24" s="176" t="s">
         <v>27</v>
       </c>
@@ -17542,13 +17542,13 @@
         <v>2019024</v>
       </c>
       <c r="B25" s="24"/>
-      <c r="C25" s="541"/>
-      <c r="D25" s="526"/>
-      <c r="E25" s="526"/>
-      <c r="F25" s="526"/>
-      <c r="G25" s="526"/>
-      <c r="H25" s="526"/>
-      <c r="I25" s="529"/>
+      <c r="C25" s="547"/>
+      <c r="D25" s="550"/>
+      <c r="E25" s="550"/>
+      <c r="F25" s="550"/>
+      <c r="G25" s="550"/>
+      <c r="H25" s="550"/>
+      <c r="I25" s="553"/>
       <c r="J25" s="176" t="s">
         <v>28</v>
       </c>
@@ -17600,13 +17600,13 @@
         <v>2019024</v>
       </c>
       <c r="B26" s="24"/>
-      <c r="C26" s="541"/>
-      <c r="D26" s="547"/>
-      <c r="E26" s="547"/>
-      <c r="F26" s="547"/>
-      <c r="G26" s="547"/>
-      <c r="H26" s="547"/>
-      <c r="I26" s="548"/>
+      <c r="C26" s="547"/>
+      <c r="D26" s="600"/>
+      <c r="E26" s="600"/>
+      <c r="F26" s="600"/>
+      <c r="G26" s="600"/>
+      <c r="H26" s="600"/>
+      <c r="I26" s="601"/>
       <c r="J26" s="180" t="s">
         <v>29</v>
       </c>
@@ -17656,16 +17656,16 @@
       <c r="A27" s="13">
         <v>2018024</v>
       </c>
-      <c r="C27" s="540">
+      <c r="C27" s="546">
         <f t="shared" ref="C27" si="10">C19+1</f>
         <v>4</v>
       </c>
-      <c r="D27" s="525"/>
-      <c r="E27" s="525"/>
-      <c r="F27" s="525"/>
-      <c r="G27" s="525"/>
-      <c r="H27" s="525"/>
-      <c r="I27" s="528" t="s">
+      <c r="D27" s="549"/>
+      <c r="E27" s="549"/>
+      <c r="F27" s="549"/>
+      <c r="G27" s="549"/>
+      <c r="H27" s="549"/>
+      <c r="I27" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J27" s="175" t="s">
@@ -17730,13 +17730,13 @@
         <v>2018024</v>
       </c>
       <c r="B28" s="24"/>
-      <c r="C28" s="541"/>
-      <c r="D28" s="526"/>
-      <c r="E28" s="526"/>
-      <c r="F28" s="526"/>
-      <c r="G28" s="526"/>
-      <c r="H28" s="526"/>
-      <c r="I28" s="529"/>
+      <c r="C28" s="547"/>
+      <c r="D28" s="550"/>
+      <c r="E28" s="550"/>
+      <c r="F28" s="550"/>
+      <c r="G28" s="550"/>
+      <c r="H28" s="550"/>
+      <c r="I28" s="553"/>
       <c r="J28" s="176" t="s">
         <v>25</v>
       </c>
@@ -17788,13 +17788,13 @@
         <v>2018024</v>
       </c>
       <c r="B29" s="24"/>
-      <c r="C29" s="541"/>
-      <c r="D29" s="526"/>
-      <c r="E29" s="526"/>
-      <c r="F29" s="526"/>
-      <c r="G29" s="526"/>
-      <c r="H29" s="526"/>
-      <c r="I29" s="529"/>
+      <c r="C29" s="547"/>
+      <c r="D29" s="550"/>
+      <c r="E29" s="550"/>
+      <c r="F29" s="550"/>
+      <c r="G29" s="550"/>
+      <c r="H29" s="550"/>
+      <c r="I29" s="553"/>
       <c r="J29" s="176" t="s">
         <v>37</v>
       </c>
@@ -17846,13 +17846,13 @@
         <v>2018024</v>
       </c>
       <c r="B30" s="24"/>
-      <c r="C30" s="541"/>
-      <c r="D30" s="526"/>
-      <c r="E30" s="526"/>
-      <c r="F30" s="526"/>
-      <c r="G30" s="526"/>
-      <c r="H30" s="526"/>
-      <c r="I30" s="529"/>
+      <c r="C30" s="547"/>
+      <c r="D30" s="550"/>
+      <c r="E30" s="550"/>
+      <c r="F30" s="550"/>
+      <c r="G30" s="550"/>
+      <c r="H30" s="550"/>
+      <c r="I30" s="553"/>
       <c r="J30" s="176" t="s">
         <v>38</v>
       </c>
@@ -17904,13 +17904,13 @@
         <v>2018024</v>
       </c>
       <c r="B31" s="24"/>
-      <c r="C31" s="541"/>
-      <c r="D31" s="526"/>
-      <c r="E31" s="526"/>
-      <c r="F31" s="526"/>
-      <c r="G31" s="526"/>
-      <c r="H31" s="526"/>
-      <c r="I31" s="529"/>
+      <c r="C31" s="547"/>
+      <c r="D31" s="550"/>
+      <c r="E31" s="550"/>
+      <c r="F31" s="550"/>
+      <c r="G31" s="550"/>
+      <c r="H31" s="550"/>
+      <c r="I31" s="553"/>
       <c r="J31" s="176" t="s">
         <v>26</v>
       </c>
@@ -17962,13 +17962,13 @@
         <v>2018024</v>
       </c>
       <c r="B32" s="24"/>
-      <c r="C32" s="541"/>
-      <c r="D32" s="526"/>
-      <c r="E32" s="526"/>
-      <c r="F32" s="526"/>
-      <c r="G32" s="526"/>
-      <c r="H32" s="526"/>
-      <c r="I32" s="529"/>
+      <c r="C32" s="547"/>
+      <c r="D32" s="550"/>
+      <c r="E32" s="550"/>
+      <c r="F32" s="550"/>
+      <c r="G32" s="550"/>
+      <c r="H32" s="550"/>
+      <c r="I32" s="553"/>
       <c r="J32" s="176" t="s">
         <v>27</v>
       </c>
@@ -18020,13 +18020,13 @@
         <v>2018024</v>
       </c>
       <c r="B33" s="24"/>
-      <c r="C33" s="541"/>
-      <c r="D33" s="526"/>
-      <c r="E33" s="526"/>
-      <c r="F33" s="526"/>
-      <c r="G33" s="526"/>
-      <c r="H33" s="526"/>
-      <c r="I33" s="529"/>
+      <c r="C33" s="547"/>
+      <c r="D33" s="550"/>
+      <c r="E33" s="550"/>
+      <c r="F33" s="550"/>
+      <c r="G33" s="550"/>
+      <c r="H33" s="550"/>
+      <c r="I33" s="553"/>
       <c r="J33" s="176" t="s">
         <v>28</v>
       </c>
@@ -18078,13 +18078,13 @@
         <v>2018024</v>
       </c>
       <c r="B34" s="24"/>
-      <c r="C34" s="542"/>
-      <c r="D34" s="527"/>
-      <c r="E34" s="527"/>
-      <c r="F34" s="527"/>
-      <c r="G34" s="527"/>
-      <c r="H34" s="527"/>
-      <c r="I34" s="530"/>
+      <c r="C34" s="548"/>
+      <c r="D34" s="551"/>
+      <c r="E34" s="551"/>
+      <c r="F34" s="551"/>
+      <c r="G34" s="551"/>
+      <c r="H34" s="551"/>
+      <c r="I34" s="554"/>
       <c r="J34" s="177" t="s">
         <v>29</v>
       </c>
@@ -18134,18 +18134,18 @@
       <c r="A35" s="13">
         <v>2018032</v>
       </c>
-      <c r="C35" s="522">
+      <c r="C35" s="528">
         <f t="shared" ref="C35" si="14">C27+1</f>
         <v>5</v>
       </c>
-      <c r="D35" s="531"/>
-      <c r="E35" s="531" t="s">
+      <c r="D35" s="522"/>
+      <c r="E35" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="531"/>
-      <c r="G35" s="531"/>
-      <c r="H35" s="531"/>
-      <c r="I35" s="534" t="s">
+      <c r="F35" s="522"/>
+      <c r="G35" s="522"/>
+      <c r="H35" s="522"/>
+      <c r="I35" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J35" s="175" t="s">
@@ -18210,13 +18210,13 @@
         <v>2018032</v>
       </c>
       <c r="B36" s="24"/>
-      <c r="C36" s="523"/>
-      <c r="D36" s="532"/>
-      <c r="E36" s="532"/>
-      <c r="F36" s="532"/>
-      <c r="G36" s="532"/>
-      <c r="H36" s="532"/>
-      <c r="I36" s="535"/>
+      <c r="C36" s="529"/>
+      <c r="D36" s="523"/>
+      <c r="E36" s="523"/>
+      <c r="F36" s="523"/>
+      <c r="G36" s="523"/>
+      <c r="H36" s="523"/>
+      <c r="I36" s="526"/>
       <c r="J36" s="176" t="s">
         <v>25</v>
       </c>
@@ -18256,13 +18256,13 @@
         <v>2018032</v>
       </c>
       <c r="B37" s="24"/>
-      <c r="C37" s="523"/>
-      <c r="D37" s="532"/>
-      <c r="E37" s="532"/>
-      <c r="F37" s="532"/>
-      <c r="G37" s="532"/>
-      <c r="H37" s="532"/>
-      <c r="I37" s="535"/>
+      <c r="C37" s="529"/>
+      <c r="D37" s="523"/>
+      <c r="E37" s="523"/>
+      <c r="F37" s="523"/>
+      <c r="G37" s="523"/>
+      <c r="H37" s="523"/>
+      <c r="I37" s="526"/>
       <c r="J37" s="176" t="s">
         <v>37</v>
       </c>
@@ -18302,13 +18302,13 @@
         <v>2018032</v>
       </c>
       <c r="B38" s="24"/>
-      <c r="C38" s="523"/>
-      <c r="D38" s="532"/>
-      <c r="E38" s="532"/>
-      <c r="F38" s="532"/>
-      <c r="G38" s="532"/>
-      <c r="H38" s="532"/>
-      <c r="I38" s="535"/>
+      <c r="C38" s="529"/>
+      <c r="D38" s="523"/>
+      <c r="E38" s="523"/>
+      <c r="F38" s="523"/>
+      <c r="G38" s="523"/>
+      <c r="H38" s="523"/>
+      <c r="I38" s="526"/>
       <c r="J38" s="176" t="s">
         <v>38</v>
       </c>
@@ -18348,13 +18348,13 @@
         <v>2018032</v>
       </c>
       <c r="B39" s="24"/>
-      <c r="C39" s="523"/>
-      <c r="D39" s="532"/>
-      <c r="E39" s="532"/>
-      <c r="F39" s="532"/>
-      <c r="G39" s="532"/>
-      <c r="H39" s="532"/>
-      <c r="I39" s="535"/>
+      <c r="C39" s="529"/>
+      <c r="D39" s="523"/>
+      <c r="E39" s="523"/>
+      <c r="F39" s="523"/>
+      <c r="G39" s="523"/>
+      <c r="H39" s="523"/>
+      <c r="I39" s="526"/>
       <c r="J39" s="176" t="s">
         <v>26</v>
       </c>
@@ -18394,13 +18394,13 @@
         <v>2018032</v>
       </c>
       <c r="B40" s="24"/>
-      <c r="C40" s="523"/>
-      <c r="D40" s="532"/>
-      <c r="E40" s="532"/>
-      <c r="F40" s="532"/>
-      <c r="G40" s="532"/>
-      <c r="H40" s="532"/>
-      <c r="I40" s="535"/>
+      <c r="C40" s="529"/>
+      <c r="D40" s="523"/>
+      <c r="E40" s="523"/>
+      <c r="F40" s="523"/>
+      <c r="G40" s="523"/>
+      <c r="H40" s="523"/>
+      <c r="I40" s="526"/>
       <c r="J40" s="176" t="s">
         <v>27</v>
       </c>
@@ -18440,13 +18440,13 @@
         <v>2018032</v>
       </c>
       <c r="B41" s="24"/>
-      <c r="C41" s="523"/>
-      <c r="D41" s="532"/>
-      <c r="E41" s="532"/>
-      <c r="F41" s="532"/>
-      <c r="G41" s="532"/>
-      <c r="H41" s="532"/>
-      <c r="I41" s="535"/>
+      <c r="C41" s="529"/>
+      <c r="D41" s="523"/>
+      <c r="E41" s="523"/>
+      <c r="F41" s="523"/>
+      <c r="G41" s="523"/>
+      <c r="H41" s="523"/>
+      <c r="I41" s="526"/>
       <c r="J41" s="176" t="s">
         <v>28</v>
       </c>
@@ -18486,13 +18486,13 @@
         <v>2018032</v>
       </c>
       <c r="B42" s="24"/>
-      <c r="C42" s="524"/>
-      <c r="D42" s="533"/>
-      <c r="E42" s="533"/>
-      <c r="F42" s="533"/>
-      <c r="G42" s="533"/>
-      <c r="H42" s="533"/>
-      <c r="I42" s="536"/>
+      <c r="C42" s="530"/>
+      <c r="D42" s="524"/>
+      <c r="E42" s="524"/>
+      <c r="F42" s="524"/>
+      <c r="G42" s="524"/>
+      <c r="H42" s="524"/>
+      <c r="I42" s="527"/>
       <c r="J42" s="177" t="s">
         <v>29</v>
       </c>
@@ -18530,16 +18530,16 @@
       <c r="A43" s="13">
         <v>2018040</v>
       </c>
-      <c r="C43" s="540">
+      <c r="C43" s="546">
         <f t="shared" ref="C43" si="17">C35+1</f>
         <v>6</v>
       </c>
-      <c r="D43" s="525"/>
-      <c r="E43" s="525"/>
-      <c r="F43" s="525"/>
-      <c r="G43" s="525"/>
-      <c r="H43" s="525"/>
-      <c r="I43" s="528" t="s">
+      <c r="D43" s="549"/>
+      <c r="E43" s="549"/>
+      <c r="F43" s="549"/>
+      <c r="G43" s="549"/>
+      <c r="H43" s="549"/>
+      <c r="I43" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J43" s="175" t="s">
@@ -18604,13 +18604,13 @@
         <v>2018040</v>
       </c>
       <c r="B44" s="24"/>
-      <c r="C44" s="541"/>
-      <c r="D44" s="526"/>
-      <c r="E44" s="526"/>
-      <c r="F44" s="526"/>
-      <c r="G44" s="526"/>
-      <c r="H44" s="526"/>
-      <c r="I44" s="529"/>
+      <c r="C44" s="547"/>
+      <c r="D44" s="550"/>
+      <c r="E44" s="550"/>
+      <c r="F44" s="550"/>
+      <c r="G44" s="550"/>
+      <c r="H44" s="550"/>
+      <c r="I44" s="553"/>
       <c r="J44" s="176" t="s">
         <v>25</v>
       </c>
@@ -18662,13 +18662,13 @@
         <v>2018040</v>
       </c>
       <c r="B45" s="24"/>
-      <c r="C45" s="541"/>
-      <c r="D45" s="526"/>
-      <c r="E45" s="526"/>
-      <c r="F45" s="526"/>
-      <c r="G45" s="526"/>
-      <c r="H45" s="526"/>
-      <c r="I45" s="529"/>
+      <c r="C45" s="547"/>
+      <c r="D45" s="550"/>
+      <c r="E45" s="550"/>
+      <c r="F45" s="550"/>
+      <c r="G45" s="550"/>
+      <c r="H45" s="550"/>
+      <c r="I45" s="553"/>
       <c r="J45" s="176" t="s">
         <v>37</v>
       </c>
@@ -18720,13 +18720,13 @@
         <v>2018040</v>
       </c>
       <c r="B46" s="24"/>
-      <c r="C46" s="541"/>
-      <c r="D46" s="526"/>
-      <c r="E46" s="526"/>
-      <c r="F46" s="526"/>
-      <c r="G46" s="526"/>
-      <c r="H46" s="526"/>
-      <c r="I46" s="529"/>
+      <c r="C46" s="547"/>
+      <c r="D46" s="550"/>
+      <c r="E46" s="550"/>
+      <c r="F46" s="550"/>
+      <c r="G46" s="550"/>
+      <c r="H46" s="550"/>
+      <c r="I46" s="553"/>
       <c r="J46" s="176" t="s">
         <v>38</v>
       </c>
@@ -18778,13 +18778,13 @@
         <v>2018040</v>
       </c>
       <c r="B47" s="24"/>
-      <c r="C47" s="541"/>
-      <c r="D47" s="526"/>
-      <c r="E47" s="526"/>
-      <c r="F47" s="526"/>
-      <c r="G47" s="526"/>
-      <c r="H47" s="526"/>
-      <c r="I47" s="529"/>
+      <c r="C47" s="547"/>
+      <c r="D47" s="550"/>
+      <c r="E47" s="550"/>
+      <c r="F47" s="550"/>
+      <c r="G47" s="550"/>
+      <c r="H47" s="550"/>
+      <c r="I47" s="553"/>
       <c r="J47" s="176" t="s">
         <v>26</v>
       </c>
@@ -18836,13 +18836,13 @@
         <v>2018040</v>
       </c>
       <c r="B48" s="24"/>
-      <c r="C48" s="541"/>
-      <c r="D48" s="526"/>
-      <c r="E48" s="526"/>
-      <c r="F48" s="526"/>
-      <c r="G48" s="526"/>
-      <c r="H48" s="526"/>
-      <c r="I48" s="529"/>
+      <c r="C48" s="547"/>
+      <c r="D48" s="550"/>
+      <c r="E48" s="550"/>
+      <c r="F48" s="550"/>
+      <c r="G48" s="550"/>
+      <c r="H48" s="550"/>
+      <c r="I48" s="553"/>
       <c r="J48" s="176" t="s">
         <v>27</v>
       </c>
@@ -18894,13 +18894,13 @@
         <v>2018040</v>
       </c>
       <c r="B49" s="24"/>
-      <c r="C49" s="541"/>
-      <c r="D49" s="526"/>
-      <c r="E49" s="526"/>
-      <c r="F49" s="526"/>
-      <c r="G49" s="526"/>
-      <c r="H49" s="526"/>
-      <c r="I49" s="529"/>
+      <c r="C49" s="547"/>
+      <c r="D49" s="550"/>
+      <c r="E49" s="550"/>
+      <c r="F49" s="550"/>
+      <c r="G49" s="550"/>
+      <c r="H49" s="550"/>
+      <c r="I49" s="553"/>
       <c r="J49" s="176" t="s">
         <v>28</v>
       </c>
@@ -18952,13 +18952,13 @@
         <v>2018040</v>
       </c>
       <c r="B50" s="24"/>
-      <c r="C50" s="542"/>
-      <c r="D50" s="527"/>
-      <c r="E50" s="527"/>
-      <c r="F50" s="527"/>
-      <c r="G50" s="527"/>
-      <c r="H50" s="527"/>
-      <c r="I50" s="530"/>
+      <c r="C50" s="548"/>
+      <c r="D50" s="551"/>
+      <c r="E50" s="551"/>
+      <c r="F50" s="551"/>
+      <c r="G50" s="551"/>
+      <c r="H50" s="551"/>
+      <c r="I50" s="554"/>
       <c r="J50" s="177" t="s">
         <v>29</v>
       </c>
@@ -19008,16 +19008,16 @@
       <c r="A51" s="13">
         <v>2018047</v>
       </c>
-      <c r="C51" s="540">
+      <c r="C51" s="546">
         <f t="shared" ref="C51" si="20">C43+1</f>
         <v>7</v>
       </c>
-      <c r="D51" s="525"/>
-      <c r="E51" s="525"/>
-      <c r="F51" s="525"/>
-      <c r="G51" s="525"/>
-      <c r="H51" s="525"/>
-      <c r="I51" s="528" t="s">
+      <c r="D51" s="549"/>
+      <c r="E51" s="549"/>
+      <c r="F51" s="549"/>
+      <c r="G51" s="549"/>
+      <c r="H51" s="549"/>
+      <c r="I51" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J51" s="175" t="s">
@@ -19082,13 +19082,13 @@
         <v>2018047</v>
       </c>
       <c r="B52" s="24"/>
-      <c r="C52" s="541"/>
-      <c r="D52" s="526"/>
-      <c r="E52" s="526"/>
-      <c r="F52" s="526"/>
-      <c r="G52" s="526"/>
-      <c r="H52" s="526"/>
-      <c r="I52" s="529"/>
+      <c r="C52" s="547"/>
+      <c r="D52" s="550"/>
+      <c r="E52" s="550"/>
+      <c r="F52" s="550"/>
+      <c r="G52" s="550"/>
+      <c r="H52" s="550"/>
+      <c r="I52" s="553"/>
       <c r="J52" s="176" t="s">
         <v>25</v>
       </c>
@@ -19140,13 +19140,13 @@
         <v>2018047</v>
       </c>
       <c r="B53" s="24"/>
-      <c r="C53" s="541"/>
-      <c r="D53" s="526"/>
-      <c r="E53" s="526"/>
-      <c r="F53" s="526"/>
-      <c r="G53" s="526"/>
-      <c r="H53" s="526"/>
-      <c r="I53" s="529"/>
+      <c r="C53" s="547"/>
+      <c r="D53" s="550"/>
+      <c r="E53" s="550"/>
+      <c r="F53" s="550"/>
+      <c r="G53" s="550"/>
+      <c r="H53" s="550"/>
+      <c r="I53" s="553"/>
       <c r="J53" s="176" t="s">
         <v>37</v>
       </c>
@@ -19198,13 +19198,13 @@
         <v>2018047</v>
       </c>
       <c r="B54" s="24"/>
-      <c r="C54" s="541"/>
-      <c r="D54" s="526"/>
-      <c r="E54" s="526"/>
-      <c r="F54" s="526"/>
-      <c r="G54" s="526"/>
-      <c r="H54" s="526"/>
-      <c r="I54" s="529"/>
+      <c r="C54" s="547"/>
+      <c r="D54" s="550"/>
+      <c r="E54" s="550"/>
+      <c r="F54" s="550"/>
+      <c r="G54" s="550"/>
+      <c r="H54" s="550"/>
+      <c r="I54" s="553"/>
       <c r="J54" s="176" t="s">
         <v>38</v>
       </c>
@@ -19256,13 +19256,13 @@
         <v>2018047</v>
       </c>
       <c r="B55" s="24"/>
-      <c r="C55" s="541"/>
-      <c r="D55" s="526"/>
-      <c r="E55" s="526"/>
-      <c r="F55" s="526"/>
-      <c r="G55" s="526"/>
-      <c r="H55" s="526"/>
-      <c r="I55" s="529"/>
+      <c r="C55" s="547"/>
+      <c r="D55" s="550"/>
+      <c r="E55" s="550"/>
+      <c r="F55" s="550"/>
+      <c r="G55" s="550"/>
+      <c r="H55" s="550"/>
+      <c r="I55" s="553"/>
       <c r="J55" s="176" t="s">
         <v>26</v>
       </c>
@@ -19314,13 +19314,13 @@
         <v>2018047</v>
       </c>
       <c r="B56" s="24"/>
-      <c r="C56" s="541"/>
-      <c r="D56" s="526"/>
-      <c r="E56" s="526"/>
-      <c r="F56" s="526"/>
-      <c r="G56" s="526"/>
-      <c r="H56" s="526"/>
-      <c r="I56" s="529"/>
+      <c r="C56" s="547"/>
+      <c r="D56" s="550"/>
+      <c r="E56" s="550"/>
+      <c r="F56" s="550"/>
+      <c r="G56" s="550"/>
+      <c r="H56" s="550"/>
+      <c r="I56" s="553"/>
       <c r="J56" s="176" t="s">
         <v>27</v>
       </c>
@@ -19372,13 +19372,13 @@
         <v>2018047</v>
       </c>
       <c r="B57" s="24"/>
-      <c r="C57" s="541"/>
-      <c r="D57" s="526"/>
-      <c r="E57" s="526"/>
-      <c r="F57" s="526"/>
-      <c r="G57" s="526"/>
-      <c r="H57" s="526"/>
-      <c r="I57" s="529"/>
+      <c r="C57" s="547"/>
+      <c r="D57" s="550"/>
+      <c r="E57" s="550"/>
+      <c r="F57" s="550"/>
+      <c r="G57" s="550"/>
+      <c r="H57" s="550"/>
+      <c r="I57" s="553"/>
       <c r="J57" s="176" t="s">
         <v>28</v>
       </c>
@@ -19430,13 +19430,13 @@
         <v>2018047</v>
       </c>
       <c r="B58" s="24"/>
-      <c r="C58" s="542"/>
-      <c r="D58" s="527"/>
-      <c r="E58" s="527"/>
-      <c r="F58" s="527"/>
-      <c r="G58" s="527"/>
-      <c r="H58" s="527"/>
-      <c r="I58" s="530"/>
+      <c r="C58" s="548"/>
+      <c r="D58" s="551"/>
+      <c r="E58" s="551"/>
+      <c r="F58" s="551"/>
+      <c r="G58" s="551"/>
+      <c r="H58" s="551"/>
+      <c r="I58" s="554"/>
       <c r="J58" s="177" t="s">
         <v>29</v>
       </c>
@@ -19486,18 +19486,18 @@
       <c r="A59" s="13">
         <v>2019020</v>
       </c>
-      <c r="C59" s="522">
+      <c r="C59" s="528">
         <f t="shared" ref="C59" si="23">C51+1</f>
         <v>8</v>
       </c>
-      <c r="D59" s="531"/>
-      <c r="E59" s="531" t="s">
+      <c r="D59" s="522"/>
+      <c r="E59" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F59" s="555"/>
-      <c r="G59" s="531"/>
-      <c r="H59" s="531"/>
-      <c r="I59" s="534" t="s">
+      <c r="F59" s="608"/>
+      <c r="G59" s="522"/>
+      <c r="H59" s="522"/>
+      <c r="I59" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J59" s="175" t="s">
@@ -19562,13 +19562,13 @@
         <v>2019020</v>
       </c>
       <c r="B60" s="24"/>
-      <c r="C60" s="523"/>
-      <c r="D60" s="532"/>
-      <c r="E60" s="532"/>
-      <c r="F60" s="556"/>
-      <c r="G60" s="532"/>
-      <c r="H60" s="532"/>
-      <c r="I60" s="535"/>
+      <c r="C60" s="529"/>
+      <c r="D60" s="523"/>
+      <c r="E60" s="523"/>
+      <c r="F60" s="609"/>
+      <c r="G60" s="523"/>
+      <c r="H60" s="523"/>
+      <c r="I60" s="526"/>
       <c r="J60" s="176" t="s">
         <v>25</v>
       </c>
@@ -19614,13 +19614,13 @@
         <v>2019020</v>
       </c>
       <c r="B61" s="24"/>
-      <c r="C61" s="523"/>
-      <c r="D61" s="532"/>
-      <c r="E61" s="532"/>
-      <c r="F61" s="556"/>
-      <c r="G61" s="532"/>
-      <c r="H61" s="532"/>
-      <c r="I61" s="535"/>
+      <c r="C61" s="529"/>
+      <c r="D61" s="523"/>
+      <c r="E61" s="523"/>
+      <c r="F61" s="609"/>
+      <c r="G61" s="523"/>
+      <c r="H61" s="523"/>
+      <c r="I61" s="526"/>
       <c r="J61" s="176" t="s">
         <v>37</v>
       </c>
@@ -19666,13 +19666,13 @@
         <v>2019020</v>
       </c>
       <c r="B62" s="24"/>
-      <c r="C62" s="523"/>
-      <c r="D62" s="532"/>
-      <c r="E62" s="532"/>
-      <c r="F62" s="556"/>
-      <c r="G62" s="532"/>
-      <c r="H62" s="532"/>
-      <c r="I62" s="535"/>
+      <c r="C62" s="529"/>
+      <c r="D62" s="523"/>
+      <c r="E62" s="523"/>
+      <c r="F62" s="609"/>
+      <c r="G62" s="523"/>
+      <c r="H62" s="523"/>
+      <c r="I62" s="526"/>
       <c r="J62" s="176" t="s">
         <v>38</v>
       </c>
@@ -19718,13 +19718,13 @@
         <v>2019020</v>
       </c>
       <c r="B63" s="24"/>
-      <c r="C63" s="523"/>
-      <c r="D63" s="532"/>
-      <c r="E63" s="532"/>
-      <c r="F63" s="556"/>
-      <c r="G63" s="532"/>
-      <c r="H63" s="532"/>
-      <c r="I63" s="535"/>
+      <c r="C63" s="529"/>
+      <c r="D63" s="523"/>
+      <c r="E63" s="523"/>
+      <c r="F63" s="609"/>
+      <c r="G63" s="523"/>
+      <c r="H63" s="523"/>
+      <c r="I63" s="526"/>
       <c r="J63" s="176" t="s">
         <v>26</v>
       </c>
@@ -19770,13 +19770,13 @@
         <v>2019020</v>
       </c>
       <c r="B64" s="24"/>
-      <c r="C64" s="523"/>
-      <c r="D64" s="532"/>
-      <c r="E64" s="532"/>
-      <c r="F64" s="556"/>
-      <c r="G64" s="532"/>
-      <c r="H64" s="532"/>
-      <c r="I64" s="535"/>
+      <c r="C64" s="529"/>
+      <c r="D64" s="523"/>
+      <c r="E64" s="523"/>
+      <c r="F64" s="609"/>
+      <c r="G64" s="523"/>
+      <c r="H64" s="523"/>
+      <c r="I64" s="526"/>
       <c r="J64" s="176" t="s">
         <v>27</v>
       </c>
@@ -19822,13 +19822,13 @@
         <v>2019020</v>
       </c>
       <c r="B65" s="24"/>
-      <c r="C65" s="523"/>
-      <c r="D65" s="532"/>
-      <c r="E65" s="532"/>
-      <c r="F65" s="556"/>
-      <c r="G65" s="532"/>
-      <c r="H65" s="532"/>
-      <c r="I65" s="535"/>
+      <c r="C65" s="529"/>
+      <c r="D65" s="523"/>
+      <c r="E65" s="523"/>
+      <c r="F65" s="609"/>
+      <c r="G65" s="523"/>
+      <c r="H65" s="523"/>
+      <c r="I65" s="526"/>
       <c r="J65" s="176" t="s">
         <v>28</v>
       </c>
@@ -19874,13 +19874,13 @@
         <v>2019020</v>
       </c>
       <c r="B66" s="24"/>
-      <c r="C66" s="524"/>
-      <c r="D66" s="533"/>
-      <c r="E66" s="533"/>
-      <c r="F66" s="557"/>
-      <c r="G66" s="533"/>
-      <c r="H66" s="533"/>
-      <c r="I66" s="536"/>
+      <c r="C66" s="530"/>
+      <c r="D66" s="524"/>
+      <c r="E66" s="524"/>
+      <c r="F66" s="610"/>
+      <c r="G66" s="524"/>
+      <c r="H66" s="524"/>
+      <c r="I66" s="527"/>
       <c r="J66" s="177" t="s">
         <v>29</v>
       </c>
@@ -19924,16 +19924,16 @@
       <c r="A67" s="13">
         <v>2019027</v>
       </c>
-      <c r="C67" s="540">
+      <c r="C67" s="546">
         <f t="shared" ref="C67" si="27">C59+1</f>
         <v>9</v>
       </c>
-      <c r="D67" s="525"/>
-      <c r="E67" s="525"/>
-      <c r="F67" s="525"/>
-      <c r="G67" s="525"/>
-      <c r="H67" s="525"/>
-      <c r="I67" s="528" t="s">
+      <c r="D67" s="549"/>
+      <c r="E67" s="549"/>
+      <c r="F67" s="549"/>
+      <c r="G67" s="549"/>
+      <c r="H67" s="549"/>
+      <c r="I67" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J67" s="175" t="s">
@@ -19998,13 +19998,13 @@
         <v>2019027</v>
       </c>
       <c r="B68" s="24"/>
-      <c r="C68" s="541"/>
-      <c r="D68" s="526"/>
-      <c r="E68" s="526"/>
-      <c r="F68" s="526"/>
-      <c r="G68" s="526"/>
-      <c r="H68" s="526"/>
-      <c r="I68" s="529"/>
+      <c r="C68" s="547"/>
+      <c r="D68" s="550"/>
+      <c r="E68" s="550"/>
+      <c r="F68" s="550"/>
+      <c r="G68" s="550"/>
+      <c r="H68" s="550"/>
+      <c r="I68" s="553"/>
       <c r="J68" s="176" t="s">
         <v>25</v>
       </c>
@@ -20056,13 +20056,13 @@
         <v>2019027</v>
       </c>
       <c r="B69" s="24"/>
-      <c r="C69" s="541"/>
-      <c r="D69" s="526"/>
-      <c r="E69" s="526"/>
-      <c r="F69" s="526"/>
-      <c r="G69" s="526"/>
-      <c r="H69" s="526"/>
-      <c r="I69" s="529"/>
+      <c r="C69" s="547"/>
+      <c r="D69" s="550"/>
+      <c r="E69" s="550"/>
+      <c r="F69" s="550"/>
+      <c r="G69" s="550"/>
+      <c r="H69" s="550"/>
+      <c r="I69" s="553"/>
       <c r="J69" s="176" t="s">
         <v>37</v>
       </c>
@@ -20114,13 +20114,13 @@
         <v>2019027</v>
       </c>
       <c r="B70" s="24"/>
-      <c r="C70" s="541"/>
-      <c r="D70" s="526"/>
-      <c r="E70" s="526"/>
-      <c r="F70" s="526"/>
-      <c r="G70" s="526"/>
-      <c r="H70" s="526"/>
-      <c r="I70" s="529"/>
+      <c r="C70" s="547"/>
+      <c r="D70" s="550"/>
+      <c r="E70" s="550"/>
+      <c r="F70" s="550"/>
+      <c r="G70" s="550"/>
+      <c r="H70" s="550"/>
+      <c r="I70" s="553"/>
       <c r="J70" s="176" t="s">
         <v>38</v>
       </c>
@@ -20172,13 +20172,13 @@
         <v>2019027</v>
       </c>
       <c r="B71" s="24"/>
-      <c r="C71" s="541"/>
-      <c r="D71" s="526"/>
-      <c r="E71" s="526"/>
-      <c r="F71" s="526"/>
-      <c r="G71" s="526"/>
-      <c r="H71" s="526"/>
-      <c r="I71" s="529"/>
+      <c r="C71" s="547"/>
+      <c r="D71" s="550"/>
+      <c r="E71" s="550"/>
+      <c r="F71" s="550"/>
+      <c r="G71" s="550"/>
+      <c r="H71" s="550"/>
+      <c r="I71" s="553"/>
       <c r="J71" s="176" t="s">
         <v>26</v>
       </c>
@@ -20230,13 +20230,13 @@
         <v>2019027</v>
       </c>
       <c r="B72" s="24"/>
-      <c r="C72" s="541"/>
-      <c r="D72" s="526"/>
-      <c r="E72" s="526"/>
-      <c r="F72" s="526"/>
-      <c r="G72" s="526"/>
-      <c r="H72" s="526"/>
-      <c r="I72" s="529"/>
+      <c r="C72" s="547"/>
+      <c r="D72" s="550"/>
+      <c r="E72" s="550"/>
+      <c r="F72" s="550"/>
+      <c r="G72" s="550"/>
+      <c r="H72" s="550"/>
+      <c r="I72" s="553"/>
       <c r="J72" s="176" t="s">
         <v>27</v>
       </c>
@@ -20288,13 +20288,13 @@
         <v>2019027</v>
       </c>
       <c r="B73" s="24"/>
-      <c r="C73" s="541"/>
-      <c r="D73" s="526"/>
-      <c r="E73" s="526"/>
-      <c r="F73" s="526"/>
-      <c r="G73" s="526"/>
-      <c r="H73" s="526"/>
-      <c r="I73" s="529"/>
+      <c r="C73" s="547"/>
+      <c r="D73" s="550"/>
+      <c r="E73" s="550"/>
+      <c r="F73" s="550"/>
+      <c r="G73" s="550"/>
+      <c r="H73" s="550"/>
+      <c r="I73" s="553"/>
       <c r="J73" s="176" t="s">
         <v>28</v>
       </c>
@@ -20346,13 +20346,13 @@
         <v>2019027</v>
       </c>
       <c r="B74" s="24"/>
-      <c r="C74" s="542"/>
-      <c r="D74" s="547"/>
-      <c r="E74" s="547"/>
-      <c r="F74" s="547"/>
-      <c r="G74" s="547"/>
-      <c r="H74" s="547"/>
-      <c r="I74" s="548"/>
+      <c r="C74" s="548"/>
+      <c r="D74" s="600"/>
+      <c r="E74" s="600"/>
+      <c r="F74" s="600"/>
+      <c r="G74" s="600"/>
+      <c r="H74" s="600"/>
+      <c r="I74" s="601"/>
       <c r="J74" s="180" t="s">
         <v>29</v>
       </c>
@@ -20402,16 +20402,16 @@
       <c r="A75" s="13">
         <v>2019023</v>
       </c>
-      <c r="C75" s="540">
+      <c r="C75" s="546">
         <f t="shared" ref="C75" si="30">C67+1</f>
         <v>10</v>
       </c>
-      <c r="D75" s="525"/>
-      <c r="E75" s="525"/>
-      <c r="F75" s="525"/>
-      <c r="G75" s="525"/>
-      <c r="H75" s="525"/>
-      <c r="I75" s="528" t="s">
+      <c r="D75" s="549"/>
+      <c r="E75" s="549"/>
+      <c r="F75" s="549"/>
+      <c r="G75" s="549"/>
+      <c r="H75" s="549"/>
+      <c r="I75" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J75" s="175" t="s">
@@ -20476,13 +20476,13 @@
         <v>2019023</v>
       </c>
       <c r="B76" s="24"/>
-      <c r="C76" s="541"/>
-      <c r="D76" s="526"/>
-      <c r="E76" s="526"/>
-      <c r="F76" s="526"/>
-      <c r="G76" s="526"/>
-      <c r="H76" s="526"/>
-      <c r="I76" s="529"/>
+      <c r="C76" s="547"/>
+      <c r="D76" s="550"/>
+      <c r="E76" s="550"/>
+      <c r="F76" s="550"/>
+      <c r="G76" s="550"/>
+      <c r="H76" s="550"/>
+      <c r="I76" s="553"/>
       <c r="J76" s="176" t="s">
         <v>25</v>
       </c>
@@ -20534,13 +20534,13 @@
         <v>2019023</v>
       </c>
       <c r="B77" s="24"/>
-      <c r="C77" s="541"/>
-      <c r="D77" s="526"/>
-      <c r="E77" s="526"/>
-      <c r="F77" s="526"/>
-      <c r="G77" s="526"/>
-      <c r="H77" s="526"/>
-      <c r="I77" s="529"/>
+      <c r="C77" s="547"/>
+      <c r="D77" s="550"/>
+      <c r="E77" s="550"/>
+      <c r="F77" s="550"/>
+      <c r="G77" s="550"/>
+      <c r="H77" s="550"/>
+      <c r="I77" s="553"/>
       <c r="J77" s="176" t="s">
         <v>37</v>
       </c>
@@ -20592,13 +20592,13 @@
         <v>2019023</v>
       </c>
       <c r="B78" s="24"/>
-      <c r="C78" s="541"/>
-      <c r="D78" s="526"/>
-      <c r="E78" s="526"/>
-      <c r="F78" s="526"/>
-      <c r="G78" s="526"/>
-      <c r="H78" s="526"/>
-      <c r="I78" s="529"/>
+      <c r="C78" s="547"/>
+      <c r="D78" s="550"/>
+      <c r="E78" s="550"/>
+      <c r="F78" s="550"/>
+      <c r="G78" s="550"/>
+      <c r="H78" s="550"/>
+      <c r="I78" s="553"/>
       <c r="J78" s="176" t="s">
         <v>38</v>
       </c>
@@ -20650,13 +20650,13 @@
         <v>2019023</v>
       </c>
       <c r="B79" s="24"/>
-      <c r="C79" s="541"/>
-      <c r="D79" s="526"/>
-      <c r="E79" s="526"/>
-      <c r="F79" s="526"/>
-      <c r="G79" s="526"/>
-      <c r="H79" s="526"/>
-      <c r="I79" s="529"/>
+      <c r="C79" s="547"/>
+      <c r="D79" s="550"/>
+      <c r="E79" s="550"/>
+      <c r="F79" s="550"/>
+      <c r="G79" s="550"/>
+      <c r="H79" s="550"/>
+      <c r="I79" s="553"/>
       <c r="J79" s="176" t="s">
         <v>26</v>
       </c>
@@ -20708,13 +20708,13 @@
         <v>2019023</v>
       </c>
       <c r="B80" s="24"/>
-      <c r="C80" s="541"/>
-      <c r="D80" s="526"/>
-      <c r="E80" s="526"/>
-      <c r="F80" s="526"/>
-      <c r="G80" s="526"/>
-      <c r="H80" s="526"/>
-      <c r="I80" s="529"/>
+      <c r="C80" s="547"/>
+      <c r="D80" s="550"/>
+      <c r="E80" s="550"/>
+      <c r="F80" s="550"/>
+      <c r="G80" s="550"/>
+      <c r="H80" s="550"/>
+      <c r="I80" s="553"/>
       <c r="J80" s="176" t="s">
         <v>27</v>
       </c>
@@ -20766,13 +20766,13 @@
         <v>2019023</v>
       </c>
       <c r="B81" s="24"/>
-      <c r="C81" s="541"/>
-      <c r="D81" s="526"/>
-      <c r="E81" s="526"/>
-      <c r="F81" s="526"/>
-      <c r="G81" s="526"/>
-      <c r="H81" s="526"/>
-      <c r="I81" s="529"/>
+      <c r="C81" s="547"/>
+      <c r="D81" s="550"/>
+      <c r="E81" s="550"/>
+      <c r="F81" s="550"/>
+      <c r="G81" s="550"/>
+      <c r="H81" s="550"/>
+      <c r="I81" s="553"/>
       <c r="J81" s="176" t="s">
         <v>28</v>
       </c>
@@ -20824,13 +20824,13 @@
         <v>2019023</v>
       </c>
       <c r="B82" s="24"/>
-      <c r="C82" s="542"/>
-      <c r="D82" s="527"/>
-      <c r="E82" s="527"/>
-      <c r="F82" s="527"/>
-      <c r="G82" s="527"/>
-      <c r="H82" s="527"/>
-      <c r="I82" s="530"/>
+      <c r="C82" s="548"/>
+      <c r="D82" s="551"/>
+      <c r="E82" s="551"/>
+      <c r="F82" s="551"/>
+      <c r="G82" s="551"/>
+      <c r="H82" s="551"/>
+      <c r="I82" s="554"/>
       <c r="J82" s="180" t="s">
         <v>29</v>
       </c>
@@ -20880,16 +20880,16 @@
       <c r="A83" s="13">
         <v>2020008</v>
       </c>
-      <c r="C83" s="540">
+      <c r="C83" s="546">
         <f t="shared" ref="C83" si="33">C75+1</f>
         <v>11</v>
       </c>
-      <c r="D83" s="525"/>
-      <c r="E83" s="525"/>
-      <c r="F83" s="525"/>
-      <c r="G83" s="525"/>
-      <c r="H83" s="525"/>
-      <c r="I83" s="528" t="s">
+      <c r="D83" s="549"/>
+      <c r="E83" s="549"/>
+      <c r="F83" s="549"/>
+      <c r="G83" s="549"/>
+      <c r="H83" s="549"/>
+      <c r="I83" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J83" s="175" t="s">
@@ -20954,13 +20954,13 @@
         <v>2020008</v>
       </c>
       <c r="B84" s="24"/>
-      <c r="C84" s="541"/>
-      <c r="D84" s="526"/>
-      <c r="E84" s="526"/>
-      <c r="F84" s="526"/>
-      <c r="G84" s="526"/>
-      <c r="H84" s="526"/>
-      <c r="I84" s="529"/>
+      <c r="C84" s="547"/>
+      <c r="D84" s="550"/>
+      <c r="E84" s="550"/>
+      <c r="F84" s="550"/>
+      <c r="G84" s="550"/>
+      <c r="H84" s="550"/>
+      <c r="I84" s="553"/>
       <c r="J84" s="176" t="s">
         <v>25</v>
       </c>
@@ -21012,13 +21012,13 @@
         <v>2020008</v>
       </c>
       <c r="B85" s="24"/>
-      <c r="C85" s="541"/>
-      <c r="D85" s="526"/>
-      <c r="E85" s="526"/>
-      <c r="F85" s="526"/>
-      <c r="G85" s="526"/>
-      <c r="H85" s="526"/>
-      <c r="I85" s="529"/>
+      <c r="C85" s="547"/>
+      <c r="D85" s="550"/>
+      <c r="E85" s="550"/>
+      <c r="F85" s="550"/>
+      <c r="G85" s="550"/>
+      <c r="H85" s="550"/>
+      <c r="I85" s="553"/>
       <c r="J85" s="176" t="s">
         <v>37</v>
       </c>
@@ -21070,13 +21070,13 @@
         <v>2020008</v>
       </c>
       <c r="B86" s="24"/>
-      <c r="C86" s="541"/>
-      <c r="D86" s="526"/>
-      <c r="E86" s="526"/>
-      <c r="F86" s="526"/>
-      <c r="G86" s="526"/>
-      <c r="H86" s="526"/>
-      <c r="I86" s="529"/>
+      <c r="C86" s="547"/>
+      <c r="D86" s="550"/>
+      <c r="E86" s="550"/>
+      <c r="F86" s="550"/>
+      <c r="G86" s="550"/>
+      <c r="H86" s="550"/>
+      <c r="I86" s="553"/>
       <c r="J86" s="176" t="s">
         <v>38</v>
       </c>
@@ -21128,13 +21128,13 @@
         <v>2020008</v>
       </c>
       <c r="B87" s="24"/>
-      <c r="C87" s="541"/>
-      <c r="D87" s="526"/>
-      <c r="E87" s="526"/>
-      <c r="F87" s="526"/>
-      <c r="G87" s="526"/>
-      <c r="H87" s="526"/>
-      <c r="I87" s="529"/>
+      <c r="C87" s="547"/>
+      <c r="D87" s="550"/>
+      <c r="E87" s="550"/>
+      <c r="F87" s="550"/>
+      <c r="G87" s="550"/>
+      <c r="H87" s="550"/>
+      <c r="I87" s="553"/>
       <c r="J87" s="176" t="s">
         <v>26</v>
       </c>
@@ -21186,13 +21186,13 @@
         <v>2020008</v>
       </c>
       <c r="B88" s="24"/>
-      <c r="C88" s="541"/>
-      <c r="D88" s="526"/>
-      <c r="E88" s="526"/>
-      <c r="F88" s="526"/>
-      <c r="G88" s="526"/>
-      <c r="H88" s="526"/>
-      <c r="I88" s="529"/>
+      <c r="C88" s="547"/>
+      <c r="D88" s="550"/>
+      <c r="E88" s="550"/>
+      <c r="F88" s="550"/>
+      <c r="G88" s="550"/>
+      <c r="H88" s="550"/>
+      <c r="I88" s="553"/>
       <c r="J88" s="176" t="s">
         <v>27</v>
       </c>
@@ -21244,13 +21244,13 @@
         <v>2020008</v>
       </c>
       <c r="B89" s="24"/>
-      <c r="C89" s="541"/>
-      <c r="D89" s="526"/>
-      <c r="E89" s="526"/>
-      <c r="F89" s="526"/>
-      <c r="G89" s="526"/>
-      <c r="H89" s="526"/>
-      <c r="I89" s="529"/>
+      <c r="C89" s="547"/>
+      <c r="D89" s="550"/>
+      <c r="E89" s="550"/>
+      <c r="F89" s="550"/>
+      <c r="G89" s="550"/>
+      <c r="H89" s="550"/>
+      <c r="I89" s="553"/>
       <c r="J89" s="176" t="s">
         <v>28</v>
       </c>
@@ -21302,13 +21302,13 @@
         <v>2020008</v>
       </c>
       <c r="B90" s="24"/>
-      <c r="C90" s="542"/>
-      <c r="D90" s="547"/>
-      <c r="E90" s="547"/>
-      <c r="F90" s="547"/>
-      <c r="G90" s="547"/>
-      <c r="H90" s="547"/>
-      <c r="I90" s="548"/>
+      <c r="C90" s="548"/>
+      <c r="D90" s="600"/>
+      <c r="E90" s="600"/>
+      <c r="F90" s="600"/>
+      <c r="G90" s="600"/>
+      <c r="H90" s="600"/>
+      <c r="I90" s="601"/>
       <c r="J90" s="180" t="s">
         <v>29</v>
       </c>
@@ -21358,18 +21358,18 @@
       <c r="A91" s="13">
         <v>2020006</v>
       </c>
-      <c r="C91" s="522">
+      <c r="C91" s="528">
         <f t="shared" ref="C91" si="36">C83+1</f>
         <v>12</v>
       </c>
-      <c r="D91" s="531"/>
-      <c r="E91" s="531" t="s">
+      <c r="D91" s="522"/>
+      <c r="E91" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F91" s="531"/>
-      <c r="G91" s="531"/>
-      <c r="H91" s="531"/>
-      <c r="I91" s="534" t="s">
+      <c r="F91" s="522"/>
+      <c r="G91" s="522"/>
+      <c r="H91" s="522"/>
+      <c r="I91" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J91" s="175" t="s">
@@ -21434,13 +21434,13 @@
         <v>2020006</v>
       </c>
       <c r="B92" s="24"/>
-      <c r="C92" s="523"/>
-      <c r="D92" s="532"/>
-      <c r="E92" s="532"/>
-      <c r="F92" s="532"/>
-      <c r="G92" s="532"/>
-      <c r="H92" s="532"/>
-      <c r="I92" s="535"/>
+      <c r="C92" s="529"/>
+      <c r="D92" s="523"/>
+      <c r="E92" s="523"/>
+      <c r="F92" s="523"/>
+      <c r="G92" s="523"/>
+      <c r="H92" s="523"/>
+      <c r="I92" s="526"/>
       <c r="J92" s="176" t="s">
         <v>25</v>
       </c>
@@ -21486,13 +21486,13 @@
         <v>2020006</v>
       </c>
       <c r="B93" s="24"/>
-      <c r="C93" s="523"/>
-      <c r="D93" s="532"/>
-      <c r="E93" s="532"/>
-      <c r="F93" s="532"/>
-      <c r="G93" s="532"/>
-      <c r="H93" s="532"/>
-      <c r="I93" s="535"/>
+      <c r="C93" s="529"/>
+      <c r="D93" s="523"/>
+      <c r="E93" s="523"/>
+      <c r="F93" s="523"/>
+      <c r="G93" s="523"/>
+      <c r="H93" s="523"/>
+      <c r="I93" s="526"/>
       <c r="J93" s="176" t="s">
         <v>37</v>
       </c>
@@ -21538,13 +21538,13 @@
         <v>2020006</v>
       </c>
       <c r="B94" s="24"/>
-      <c r="C94" s="523"/>
-      <c r="D94" s="532"/>
-      <c r="E94" s="532"/>
-      <c r="F94" s="532"/>
-      <c r="G94" s="532"/>
-      <c r="H94" s="532"/>
-      <c r="I94" s="535"/>
+      <c r="C94" s="529"/>
+      <c r="D94" s="523"/>
+      <c r="E94" s="523"/>
+      <c r="F94" s="523"/>
+      <c r="G94" s="523"/>
+      <c r="H94" s="523"/>
+      <c r="I94" s="526"/>
       <c r="J94" s="176" t="s">
         <v>38</v>
       </c>
@@ -21590,13 +21590,13 @@
         <v>2020006</v>
       </c>
       <c r="B95" s="24"/>
-      <c r="C95" s="523"/>
-      <c r="D95" s="532"/>
-      <c r="E95" s="532"/>
-      <c r="F95" s="532"/>
-      <c r="G95" s="532"/>
-      <c r="H95" s="532"/>
-      <c r="I95" s="535"/>
+      <c r="C95" s="529"/>
+      <c r="D95" s="523"/>
+      <c r="E95" s="523"/>
+      <c r="F95" s="523"/>
+      <c r="G95" s="523"/>
+      <c r="H95" s="523"/>
+      <c r="I95" s="526"/>
       <c r="J95" s="176" t="s">
         <v>26</v>
       </c>
@@ -21642,13 +21642,13 @@
         <v>2020006</v>
       </c>
       <c r="B96" s="24"/>
-      <c r="C96" s="523"/>
-      <c r="D96" s="532"/>
-      <c r="E96" s="532"/>
-      <c r="F96" s="532"/>
-      <c r="G96" s="532"/>
-      <c r="H96" s="532"/>
-      <c r="I96" s="535"/>
+      <c r="C96" s="529"/>
+      <c r="D96" s="523"/>
+      <c r="E96" s="523"/>
+      <c r="F96" s="523"/>
+      <c r="G96" s="523"/>
+      <c r="H96" s="523"/>
+      <c r="I96" s="526"/>
       <c r="J96" s="176" t="s">
         <v>27</v>
       </c>
@@ -21694,13 +21694,13 @@
         <v>2020006</v>
       </c>
       <c r="B97" s="24"/>
-      <c r="C97" s="523"/>
-      <c r="D97" s="532"/>
-      <c r="E97" s="532"/>
-      <c r="F97" s="532"/>
-      <c r="G97" s="532"/>
-      <c r="H97" s="532"/>
-      <c r="I97" s="535"/>
+      <c r="C97" s="529"/>
+      <c r="D97" s="523"/>
+      <c r="E97" s="523"/>
+      <c r="F97" s="523"/>
+      <c r="G97" s="523"/>
+      <c r="H97" s="523"/>
+      <c r="I97" s="526"/>
       <c r="J97" s="176" t="s">
         <v>28</v>
       </c>
@@ -21746,13 +21746,13 @@
         <v>2020006</v>
       </c>
       <c r="B98" s="24"/>
-      <c r="C98" s="524"/>
-      <c r="D98" s="545"/>
-      <c r="E98" s="545"/>
-      <c r="F98" s="545"/>
-      <c r="G98" s="545"/>
-      <c r="H98" s="545"/>
-      <c r="I98" s="546"/>
+      <c r="C98" s="530"/>
+      <c r="D98" s="562"/>
+      <c r="E98" s="562"/>
+      <c r="F98" s="562"/>
+      <c r="G98" s="562"/>
+      <c r="H98" s="562"/>
+      <c r="I98" s="563"/>
       <c r="J98" s="180" t="s">
         <v>29</v>
       </c>
@@ -21796,16 +21796,16 @@
       <c r="A99" s="13">
         <v>2020021</v>
       </c>
-      <c r="C99" s="540">
+      <c r="C99" s="546">
         <f t="shared" ref="C99" si="40">C91+1</f>
         <v>13</v>
       </c>
-      <c r="D99" s="525"/>
-      <c r="E99" s="525"/>
-      <c r="F99" s="525"/>
-      <c r="G99" s="525"/>
-      <c r="H99" s="525"/>
-      <c r="I99" s="528" t="s">
+      <c r="D99" s="549"/>
+      <c r="E99" s="549"/>
+      <c r="F99" s="549"/>
+      <c r="G99" s="549"/>
+      <c r="H99" s="549"/>
+      <c r="I99" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J99" s="175" t="s">
@@ -21870,13 +21870,13 @@
         <v>2020021</v>
       </c>
       <c r="B100" s="24"/>
-      <c r="C100" s="541"/>
-      <c r="D100" s="526"/>
-      <c r="E100" s="526"/>
-      <c r="F100" s="526"/>
-      <c r="G100" s="526"/>
-      <c r="H100" s="526"/>
-      <c r="I100" s="529"/>
+      <c r="C100" s="547"/>
+      <c r="D100" s="550"/>
+      <c r="E100" s="550"/>
+      <c r="F100" s="550"/>
+      <c r="G100" s="550"/>
+      <c r="H100" s="550"/>
+      <c r="I100" s="553"/>
       <c r="J100" s="176" t="s">
         <v>25</v>
       </c>
@@ -21928,13 +21928,13 @@
         <v>2020021</v>
       </c>
       <c r="B101" s="24"/>
-      <c r="C101" s="541"/>
-      <c r="D101" s="526"/>
-      <c r="E101" s="526"/>
-      <c r="F101" s="526"/>
-      <c r="G101" s="526"/>
-      <c r="H101" s="526"/>
-      <c r="I101" s="529"/>
+      <c r="C101" s="547"/>
+      <c r="D101" s="550"/>
+      <c r="E101" s="550"/>
+      <c r="F101" s="550"/>
+      <c r="G101" s="550"/>
+      <c r="H101" s="550"/>
+      <c r="I101" s="553"/>
       <c r="J101" s="176" t="s">
         <v>37</v>
       </c>
@@ -21986,13 +21986,13 @@
         <v>2020021</v>
       </c>
       <c r="B102" s="24"/>
-      <c r="C102" s="541"/>
-      <c r="D102" s="526"/>
-      <c r="E102" s="526"/>
-      <c r="F102" s="526"/>
-      <c r="G102" s="526"/>
-      <c r="H102" s="526"/>
-      <c r="I102" s="529"/>
+      <c r="C102" s="547"/>
+      <c r="D102" s="550"/>
+      <c r="E102" s="550"/>
+      <c r="F102" s="550"/>
+      <c r="G102" s="550"/>
+      <c r="H102" s="550"/>
+      <c r="I102" s="553"/>
       <c r="J102" s="176" t="s">
         <v>38</v>
       </c>
@@ -22044,13 +22044,13 @@
         <v>2020021</v>
       </c>
       <c r="B103" s="24"/>
-      <c r="C103" s="541"/>
-      <c r="D103" s="526"/>
-      <c r="E103" s="526"/>
-      <c r="F103" s="526"/>
-      <c r="G103" s="526"/>
-      <c r="H103" s="526"/>
-      <c r="I103" s="529"/>
+      <c r="C103" s="547"/>
+      <c r="D103" s="550"/>
+      <c r="E103" s="550"/>
+      <c r="F103" s="550"/>
+      <c r="G103" s="550"/>
+      <c r="H103" s="550"/>
+      <c r="I103" s="553"/>
       <c r="J103" s="176" t="s">
         <v>26</v>
       </c>
@@ -22102,13 +22102,13 @@
         <v>2020021</v>
       </c>
       <c r="B104" s="24"/>
-      <c r="C104" s="541"/>
-      <c r="D104" s="526"/>
-      <c r="E104" s="526"/>
-      <c r="F104" s="526"/>
-      <c r="G104" s="526"/>
-      <c r="H104" s="526"/>
-      <c r="I104" s="529"/>
+      <c r="C104" s="547"/>
+      <c r="D104" s="550"/>
+      <c r="E104" s="550"/>
+      <c r="F104" s="550"/>
+      <c r="G104" s="550"/>
+      <c r="H104" s="550"/>
+      <c r="I104" s="553"/>
       <c r="J104" s="176" t="s">
         <v>27</v>
       </c>
@@ -22160,13 +22160,13 @@
         <v>2020021</v>
       </c>
       <c r="B105" s="24"/>
-      <c r="C105" s="541"/>
-      <c r="D105" s="526"/>
-      <c r="E105" s="526"/>
-      <c r="F105" s="526"/>
-      <c r="G105" s="526"/>
-      <c r="H105" s="526"/>
-      <c r="I105" s="529"/>
+      <c r="C105" s="547"/>
+      <c r="D105" s="550"/>
+      <c r="E105" s="550"/>
+      <c r="F105" s="550"/>
+      <c r="G105" s="550"/>
+      <c r="H105" s="550"/>
+      <c r="I105" s="553"/>
       <c r="J105" s="176" t="s">
         <v>28</v>
       </c>
@@ -22218,13 +22218,13 @@
         <v>2020021</v>
       </c>
       <c r="B106" s="24"/>
-      <c r="C106" s="542"/>
-      <c r="D106" s="547"/>
-      <c r="E106" s="547"/>
-      <c r="F106" s="547"/>
-      <c r="G106" s="547"/>
-      <c r="H106" s="547"/>
-      <c r="I106" s="548"/>
+      <c r="C106" s="548"/>
+      <c r="D106" s="600"/>
+      <c r="E106" s="600"/>
+      <c r="F106" s="600"/>
+      <c r="G106" s="600"/>
+      <c r="H106" s="600"/>
+      <c r="I106" s="601"/>
       <c r="J106" s="180" t="s">
         <v>29</v>
       </c>
@@ -22274,16 +22274,16 @@
       <c r="A107" s="13">
         <v>2020025</v>
       </c>
-      <c r="C107" s="540">
+      <c r="C107" s="546">
         <f t="shared" ref="C107" si="43">C99+1</f>
         <v>14</v>
       </c>
-      <c r="D107" s="525"/>
-      <c r="E107" s="525"/>
-      <c r="F107" s="549"/>
-      <c r="G107" s="525"/>
-      <c r="H107" s="525"/>
-      <c r="I107" s="528" t="s">
+      <c r="D107" s="549"/>
+      <c r="E107" s="549"/>
+      <c r="F107" s="602"/>
+      <c r="G107" s="549"/>
+      <c r="H107" s="549"/>
+      <c r="I107" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J107" s="175" t="s">
@@ -22348,13 +22348,13 @@
         <v>2020025</v>
       </c>
       <c r="B108" s="24"/>
-      <c r="C108" s="541"/>
-      <c r="D108" s="526"/>
-      <c r="E108" s="526"/>
-      <c r="F108" s="550"/>
-      <c r="G108" s="526"/>
-      <c r="H108" s="526"/>
-      <c r="I108" s="529"/>
+      <c r="C108" s="547"/>
+      <c r="D108" s="550"/>
+      <c r="E108" s="550"/>
+      <c r="F108" s="603"/>
+      <c r="G108" s="550"/>
+      <c r="H108" s="550"/>
+      <c r="I108" s="553"/>
       <c r="J108" s="176" t="s">
         <v>25</v>
       </c>
@@ -22406,13 +22406,13 @@
         <v>2020025</v>
       </c>
       <c r="B109" s="24"/>
-      <c r="C109" s="541"/>
-      <c r="D109" s="526"/>
-      <c r="E109" s="526"/>
-      <c r="F109" s="550"/>
-      <c r="G109" s="526"/>
-      <c r="H109" s="526"/>
-      <c r="I109" s="529"/>
+      <c r="C109" s="547"/>
+      <c r="D109" s="550"/>
+      <c r="E109" s="550"/>
+      <c r="F109" s="603"/>
+      <c r="G109" s="550"/>
+      <c r="H109" s="550"/>
+      <c r="I109" s="553"/>
       <c r="J109" s="176" t="s">
         <v>37</v>
       </c>
@@ -22464,13 +22464,13 @@
         <v>2020025</v>
       </c>
       <c r="B110" s="24"/>
-      <c r="C110" s="541"/>
-      <c r="D110" s="526"/>
-      <c r="E110" s="526"/>
-      <c r="F110" s="550"/>
-      <c r="G110" s="526"/>
-      <c r="H110" s="526"/>
-      <c r="I110" s="529"/>
+      <c r="C110" s="547"/>
+      <c r="D110" s="550"/>
+      <c r="E110" s="550"/>
+      <c r="F110" s="603"/>
+      <c r="G110" s="550"/>
+      <c r="H110" s="550"/>
+      <c r="I110" s="553"/>
       <c r="J110" s="176" t="s">
         <v>38</v>
       </c>
@@ -22522,13 +22522,13 @@
         <v>2020025</v>
       </c>
       <c r="B111" s="24"/>
-      <c r="C111" s="541"/>
-      <c r="D111" s="526"/>
-      <c r="E111" s="526"/>
-      <c r="F111" s="550"/>
-      <c r="G111" s="526"/>
-      <c r="H111" s="526"/>
-      <c r="I111" s="529"/>
+      <c r="C111" s="547"/>
+      <c r="D111" s="550"/>
+      <c r="E111" s="550"/>
+      <c r="F111" s="603"/>
+      <c r="G111" s="550"/>
+      <c r="H111" s="550"/>
+      <c r="I111" s="553"/>
       <c r="J111" s="176" t="s">
         <v>26</v>
       </c>
@@ -22580,13 +22580,13 @@
         <v>2020025</v>
       </c>
       <c r="B112" s="24"/>
-      <c r="C112" s="541"/>
-      <c r="D112" s="526"/>
-      <c r="E112" s="526"/>
-      <c r="F112" s="550"/>
-      <c r="G112" s="526"/>
-      <c r="H112" s="526"/>
-      <c r="I112" s="529"/>
+      <c r="C112" s="547"/>
+      <c r="D112" s="550"/>
+      <c r="E112" s="550"/>
+      <c r="F112" s="603"/>
+      <c r="G112" s="550"/>
+      <c r="H112" s="550"/>
+      <c r="I112" s="553"/>
       <c r="J112" s="176" t="s">
         <v>27</v>
       </c>
@@ -22638,13 +22638,13 @@
         <v>2020025</v>
       </c>
       <c r="B113" s="24"/>
-      <c r="C113" s="541"/>
-      <c r="D113" s="526"/>
-      <c r="E113" s="526"/>
-      <c r="F113" s="550"/>
-      <c r="G113" s="526"/>
-      <c r="H113" s="526"/>
-      <c r="I113" s="529"/>
+      <c r="C113" s="547"/>
+      <c r="D113" s="550"/>
+      <c r="E113" s="550"/>
+      <c r="F113" s="603"/>
+      <c r="G113" s="550"/>
+      <c r="H113" s="550"/>
+      <c r="I113" s="553"/>
       <c r="J113" s="176" t="s">
         <v>28</v>
       </c>
@@ -22696,13 +22696,13 @@
         <v>2020025</v>
       </c>
       <c r="B114" s="24"/>
-      <c r="C114" s="542"/>
-      <c r="D114" s="547"/>
-      <c r="E114" s="547"/>
-      <c r="F114" s="551"/>
-      <c r="G114" s="547"/>
-      <c r="H114" s="547"/>
-      <c r="I114" s="548"/>
+      <c r="C114" s="548"/>
+      <c r="D114" s="600"/>
+      <c r="E114" s="600"/>
+      <c r="F114" s="604"/>
+      <c r="G114" s="600"/>
+      <c r="H114" s="600"/>
+      <c r="I114" s="601"/>
       <c r="J114" s="180" t="s">
         <v>29</v>
       </c>
@@ -22752,18 +22752,18 @@
       <c r="A115" s="13">
         <v>2021022</v>
       </c>
-      <c r="C115" s="522">
+      <c r="C115" s="528">
         <f t="shared" ref="C115" si="46">C107+1</f>
         <v>15</v>
       </c>
-      <c r="D115" s="531"/>
-      <c r="E115" s="531" t="s">
+      <c r="D115" s="522"/>
+      <c r="E115" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F115" s="531"/>
-      <c r="G115" s="531"/>
-      <c r="H115" s="531"/>
-      <c r="I115" s="534" t="s">
+      <c r="F115" s="522"/>
+      <c r="G115" s="522"/>
+      <c r="H115" s="522"/>
+      <c r="I115" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J115" s="175" t="s">
@@ -22828,13 +22828,13 @@
         <v>2021022</v>
       </c>
       <c r="B116" s="24"/>
-      <c r="C116" s="523"/>
-      <c r="D116" s="532"/>
-      <c r="E116" s="532"/>
-      <c r="F116" s="532"/>
-      <c r="G116" s="532"/>
-      <c r="H116" s="532"/>
-      <c r="I116" s="535"/>
+      <c r="C116" s="529"/>
+      <c r="D116" s="523"/>
+      <c r="E116" s="523"/>
+      <c r="F116" s="523"/>
+      <c r="G116" s="523"/>
+      <c r="H116" s="523"/>
+      <c r="I116" s="526"/>
       <c r="J116" s="176" t="s">
         <v>25</v>
       </c>
@@ -22866,13 +22866,13 @@
         <v>2021022</v>
       </c>
       <c r="B117" s="24"/>
-      <c r="C117" s="523"/>
-      <c r="D117" s="532"/>
-      <c r="E117" s="532"/>
-      <c r="F117" s="532"/>
-      <c r="G117" s="532"/>
-      <c r="H117" s="532"/>
-      <c r="I117" s="535"/>
+      <c r="C117" s="529"/>
+      <c r="D117" s="523"/>
+      <c r="E117" s="523"/>
+      <c r="F117" s="523"/>
+      <c r="G117" s="523"/>
+      <c r="H117" s="523"/>
+      <c r="I117" s="526"/>
       <c r="J117" s="176" t="s">
         <v>37</v>
       </c>
@@ -22904,13 +22904,13 @@
         <v>2021022</v>
       </c>
       <c r="B118" s="24"/>
-      <c r="C118" s="523"/>
-      <c r="D118" s="532"/>
-      <c r="E118" s="532"/>
-      <c r="F118" s="532"/>
-      <c r="G118" s="532"/>
-      <c r="H118" s="532"/>
-      <c r="I118" s="535"/>
+      <c r="C118" s="529"/>
+      <c r="D118" s="523"/>
+      <c r="E118" s="523"/>
+      <c r="F118" s="523"/>
+      <c r="G118" s="523"/>
+      <c r="H118" s="523"/>
+      <c r="I118" s="526"/>
       <c r="J118" s="176" t="s">
         <v>38</v>
       </c>
@@ -22942,13 +22942,13 @@
         <v>2021022</v>
       </c>
       <c r="B119" s="24"/>
-      <c r="C119" s="523"/>
-      <c r="D119" s="532"/>
-      <c r="E119" s="532"/>
-      <c r="F119" s="532"/>
-      <c r="G119" s="532"/>
-      <c r="H119" s="532"/>
-      <c r="I119" s="535"/>
+      <c r="C119" s="529"/>
+      <c r="D119" s="523"/>
+      <c r="E119" s="523"/>
+      <c r="F119" s="523"/>
+      <c r="G119" s="523"/>
+      <c r="H119" s="523"/>
+      <c r="I119" s="526"/>
       <c r="J119" s="176" t="s">
         <v>26</v>
       </c>
@@ -22980,13 +22980,13 @@
         <v>2021022</v>
       </c>
       <c r="B120" s="24"/>
-      <c r="C120" s="523"/>
-      <c r="D120" s="532"/>
-      <c r="E120" s="532"/>
-      <c r="F120" s="532"/>
-      <c r="G120" s="532"/>
-      <c r="H120" s="532"/>
-      <c r="I120" s="535"/>
+      <c r="C120" s="529"/>
+      <c r="D120" s="523"/>
+      <c r="E120" s="523"/>
+      <c r="F120" s="523"/>
+      <c r="G120" s="523"/>
+      <c r="H120" s="523"/>
+      <c r="I120" s="526"/>
       <c r="J120" s="176" t="s">
         <v>27</v>
       </c>
@@ -23018,13 +23018,13 @@
         <v>2021022</v>
       </c>
       <c r="B121" s="24"/>
-      <c r="C121" s="523"/>
-      <c r="D121" s="532"/>
-      <c r="E121" s="532"/>
-      <c r="F121" s="532"/>
-      <c r="G121" s="532"/>
-      <c r="H121" s="532"/>
-      <c r="I121" s="535"/>
+      <c r="C121" s="529"/>
+      <c r="D121" s="523"/>
+      <c r="E121" s="523"/>
+      <c r="F121" s="523"/>
+      <c r="G121" s="523"/>
+      <c r="H121" s="523"/>
+      <c r="I121" s="526"/>
       <c r="J121" s="176" t="s">
         <v>28</v>
       </c>
@@ -23056,13 +23056,13 @@
         <v>2021022</v>
       </c>
       <c r="B122" s="24"/>
-      <c r="C122" s="524"/>
-      <c r="D122" s="545"/>
-      <c r="E122" s="545"/>
-      <c r="F122" s="545"/>
-      <c r="G122" s="545"/>
-      <c r="H122" s="545"/>
-      <c r="I122" s="546"/>
+      <c r="C122" s="530"/>
+      <c r="D122" s="562"/>
+      <c r="E122" s="562"/>
+      <c r="F122" s="562"/>
+      <c r="G122" s="562"/>
+      <c r="H122" s="562"/>
+      <c r="I122" s="563"/>
       <c r="J122" s="180" t="s">
         <v>29</v>
       </c>
@@ -23092,18 +23092,18 @@
       <c r="A123" s="13">
         <v>2022005</v>
       </c>
-      <c r="C123" s="522">
+      <c r="C123" s="528">
         <f t="shared" ref="C123" si="50">C115+1</f>
         <v>16</v>
       </c>
-      <c r="D123" s="531"/>
-      <c r="E123" s="531" t="s">
+      <c r="D123" s="522"/>
+      <c r="E123" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F123" s="531"/>
-      <c r="G123" s="531"/>
-      <c r="H123" s="531"/>
-      <c r="I123" s="534" t="s">
+      <c r="F123" s="522"/>
+      <c r="G123" s="522"/>
+      <c r="H123" s="522"/>
+      <c r="I123" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J123" s="175" t="s">
@@ -23168,13 +23168,13 @@
         <v>2022005</v>
       </c>
       <c r="B124" s="24"/>
-      <c r="C124" s="523"/>
-      <c r="D124" s="532"/>
-      <c r="E124" s="532"/>
-      <c r="F124" s="532"/>
-      <c r="G124" s="532"/>
-      <c r="H124" s="532"/>
-      <c r="I124" s="535"/>
+      <c r="C124" s="529"/>
+      <c r="D124" s="523"/>
+      <c r="E124" s="523"/>
+      <c r="F124" s="523"/>
+      <c r="G124" s="523"/>
+      <c r="H124" s="523"/>
+      <c r="I124" s="526"/>
       <c r="J124" s="176" t="s">
         <v>25</v>
       </c>
@@ -23220,13 +23220,13 @@
         <v>2022005</v>
       </c>
       <c r="B125" s="24"/>
-      <c r="C125" s="523"/>
-      <c r="D125" s="532"/>
-      <c r="E125" s="532"/>
-      <c r="F125" s="532"/>
-      <c r="G125" s="532"/>
-      <c r="H125" s="532"/>
-      <c r="I125" s="535"/>
+      <c r="C125" s="529"/>
+      <c r="D125" s="523"/>
+      <c r="E125" s="523"/>
+      <c r="F125" s="523"/>
+      <c r="G125" s="523"/>
+      <c r="H125" s="523"/>
+      <c r="I125" s="526"/>
       <c r="J125" s="176" t="s">
         <v>37</v>
       </c>
@@ -23272,13 +23272,13 @@
         <v>2022005</v>
       </c>
       <c r="B126" s="24"/>
-      <c r="C126" s="523"/>
-      <c r="D126" s="532"/>
-      <c r="E126" s="532"/>
-      <c r="F126" s="532"/>
-      <c r="G126" s="532"/>
-      <c r="H126" s="532"/>
-      <c r="I126" s="535"/>
+      <c r="C126" s="529"/>
+      <c r="D126" s="523"/>
+      <c r="E126" s="523"/>
+      <c r="F126" s="523"/>
+      <c r="G126" s="523"/>
+      <c r="H126" s="523"/>
+      <c r="I126" s="526"/>
       <c r="J126" s="176" t="s">
         <v>38</v>
       </c>
@@ -23324,13 +23324,13 @@
         <v>2022005</v>
       </c>
       <c r="B127" s="24"/>
-      <c r="C127" s="523"/>
-      <c r="D127" s="532"/>
-      <c r="E127" s="532"/>
-      <c r="F127" s="532"/>
-      <c r="G127" s="532"/>
-      <c r="H127" s="532"/>
-      <c r="I127" s="535"/>
+      <c r="C127" s="529"/>
+      <c r="D127" s="523"/>
+      <c r="E127" s="523"/>
+      <c r="F127" s="523"/>
+      <c r="G127" s="523"/>
+      <c r="H127" s="523"/>
+      <c r="I127" s="526"/>
       <c r="J127" s="176" t="s">
         <v>26</v>
       </c>
@@ -23376,13 +23376,13 @@
         <v>2022005</v>
       </c>
       <c r="B128" s="24"/>
-      <c r="C128" s="523"/>
-      <c r="D128" s="532"/>
-      <c r="E128" s="532"/>
-      <c r="F128" s="532"/>
-      <c r="G128" s="532"/>
-      <c r="H128" s="532"/>
-      <c r="I128" s="535"/>
+      <c r="C128" s="529"/>
+      <c r="D128" s="523"/>
+      <c r="E128" s="523"/>
+      <c r="F128" s="523"/>
+      <c r="G128" s="523"/>
+      <c r="H128" s="523"/>
+      <c r="I128" s="526"/>
       <c r="J128" s="176" t="s">
         <v>27</v>
       </c>
@@ -23428,13 +23428,13 @@
         <v>2022005</v>
       </c>
       <c r="B129" s="24"/>
-      <c r="C129" s="523"/>
-      <c r="D129" s="532"/>
-      <c r="E129" s="532"/>
-      <c r="F129" s="532"/>
-      <c r="G129" s="532"/>
-      <c r="H129" s="532"/>
-      <c r="I129" s="535"/>
+      <c r="C129" s="529"/>
+      <c r="D129" s="523"/>
+      <c r="E129" s="523"/>
+      <c r="F129" s="523"/>
+      <c r="G129" s="523"/>
+      <c r="H129" s="523"/>
+      <c r="I129" s="526"/>
       <c r="J129" s="176" t="s">
         <v>28</v>
       </c>
@@ -23480,13 +23480,13 @@
         <v>2022005</v>
       </c>
       <c r="B130" s="24"/>
-      <c r="C130" s="524"/>
-      <c r="D130" s="545"/>
-      <c r="E130" s="545"/>
-      <c r="F130" s="545"/>
-      <c r="G130" s="545"/>
-      <c r="H130" s="545"/>
-      <c r="I130" s="546"/>
+      <c r="C130" s="530"/>
+      <c r="D130" s="562"/>
+      <c r="E130" s="562"/>
+      <c r="F130" s="562"/>
+      <c r="G130" s="562"/>
+      <c r="H130" s="562"/>
+      <c r="I130" s="563"/>
       <c r="J130" s="180" t="s">
         <v>29</v>
       </c>
@@ -23530,16 +23530,16 @@
       <c r="A131" s="13">
         <v>2022010</v>
       </c>
-      <c r="C131" s="540">
+      <c r="C131" s="546">
         <f t="shared" ref="C131" si="54">C123+1</f>
         <v>17</v>
       </c>
-      <c r="D131" s="525"/>
-      <c r="E131" s="525"/>
-      <c r="F131" s="525"/>
-      <c r="G131" s="525"/>
-      <c r="H131" s="525"/>
-      <c r="I131" s="528" t="s">
+      <c r="D131" s="549"/>
+      <c r="E131" s="549"/>
+      <c r="F131" s="549"/>
+      <c r="G131" s="549"/>
+      <c r="H131" s="549"/>
+      <c r="I131" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J131" s="175" t="s">
@@ -23604,13 +23604,13 @@
         <v>2022010</v>
       </c>
       <c r="B132" s="24"/>
-      <c r="C132" s="541"/>
-      <c r="D132" s="526"/>
-      <c r="E132" s="526"/>
-      <c r="F132" s="526"/>
-      <c r="G132" s="526"/>
-      <c r="H132" s="526"/>
-      <c r="I132" s="529"/>
+      <c r="C132" s="547"/>
+      <c r="D132" s="550"/>
+      <c r="E132" s="550"/>
+      <c r="F132" s="550"/>
+      <c r="G132" s="550"/>
+      <c r="H132" s="550"/>
+      <c r="I132" s="553"/>
       <c r="J132" s="176" t="s">
         <v>25</v>
       </c>
@@ -23662,13 +23662,13 @@
         <v>2022010</v>
       </c>
       <c r="B133" s="24"/>
-      <c r="C133" s="541"/>
-      <c r="D133" s="526"/>
-      <c r="E133" s="526"/>
-      <c r="F133" s="526"/>
-      <c r="G133" s="526"/>
-      <c r="H133" s="526"/>
-      <c r="I133" s="529"/>
+      <c r="C133" s="547"/>
+      <c r="D133" s="550"/>
+      <c r="E133" s="550"/>
+      <c r="F133" s="550"/>
+      <c r="G133" s="550"/>
+      <c r="H133" s="550"/>
+      <c r="I133" s="553"/>
       <c r="J133" s="176" t="s">
         <v>37</v>
       </c>
@@ -23720,13 +23720,13 @@
         <v>2022010</v>
       </c>
       <c r="B134" s="24"/>
-      <c r="C134" s="541"/>
-      <c r="D134" s="526"/>
-      <c r="E134" s="526"/>
-      <c r="F134" s="526"/>
-      <c r="G134" s="526"/>
-      <c r="H134" s="526"/>
-      <c r="I134" s="529"/>
+      <c r="C134" s="547"/>
+      <c r="D134" s="550"/>
+      <c r="E134" s="550"/>
+      <c r="F134" s="550"/>
+      <c r="G134" s="550"/>
+      <c r="H134" s="550"/>
+      <c r="I134" s="553"/>
       <c r="J134" s="176" t="s">
         <v>38</v>
       </c>
@@ -23778,13 +23778,13 @@
         <v>2022010</v>
       </c>
       <c r="B135" s="24"/>
-      <c r="C135" s="541"/>
-      <c r="D135" s="526"/>
-      <c r="E135" s="526"/>
-      <c r="F135" s="526"/>
-      <c r="G135" s="526"/>
-      <c r="H135" s="526"/>
-      <c r="I135" s="529"/>
+      <c r="C135" s="547"/>
+      <c r="D135" s="550"/>
+      <c r="E135" s="550"/>
+      <c r="F135" s="550"/>
+      <c r="G135" s="550"/>
+      <c r="H135" s="550"/>
+      <c r="I135" s="553"/>
       <c r="J135" s="176" t="s">
         <v>26</v>
       </c>
@@ -23836,13 +23836,13 @@
         <v>2022010</v>
       </c>
       <c r="B136" s="24"/>
-      <c r="C136" s="541"/>
-      <c r="D136" s="526"/>
-      <c r="E136" s="526"/>
-      <c r="F136" s="526"/>
-      <c r="G136" s="526"/>
-      <c r="H136" s="526"/>
-      <c r="I136" s="529"/>
+      <c r="C136" s="547"/>
+      <c r="D136" s="550"/>
+      <c r="E136" s="550"/>
+      <c r="F136" s="550"/>
+      <c r="G136" s="550"/>
+      <c r="H136" s="550"/>
+      <c r="I136" s="553"/>
       <c r="J136" s="176" t="s">
         <v>27</v>
       </c>
@@ -23894,13 +23894,13 @@
         <v>2022010</v>
       </c>
       <c r="B137" s="24"/>
-      <c r="C137" s="541"/>
-      <c r="D137" s="526"/>
-      <c r="E137" s="526"/>
-      <c r="F137" s="526"/>
-      <c r="G137" s="526"/>
-      <c r="H137" s="526"/>
-      <c r="I137" s="529"/>
+      <c r="C137" s="547"/>
+      <c r="D137" s="550"/>
+      <c r="E137" s="550"/>
+      <c r="F137" s="550"/>
+      <c r="G137" s="550"/>
+      <c r="H137" s="550"/>
+      <c r="I137" s="553"/>
       <c r="J137" s="176" t="s">
         <v>28</v>
       </c>
@@ -23952,13 +23952,13 @@
         <v>2022010</v>
       </c>
       <c r="B138" s="24"/>
-      <c r="C138" s="542"/>
-      <c r="D138" s="547"/>
-      <c r="E138" s="547"/>
-      <c r="F138" s="547"/>
-      <c r="G138" s="547"/>
-      <c r="H138" s="547"/>
-      <c r="I138" s="548"/>
+      <c r="C138" s="548"/>
+      <c r="D138" s="600"/>
+      <c r="E138" s="600"/>
+      <c r="F138" s="600"/>
+      <c r="G138" s="600"/>
+      <c r="H138" s="600"/>
+      <c r="I138" s="601"/>
       <c r="J138" s="180" t="s">
         <v>29</v>
       </c>
@@ -24008,16 +24008,16 @@
       <c r="A139" s="13">
         <v>2022020</v>
       </c>
-      <c r="C139" s="540">
+      <c r="C139" s="546">
         <f t="shared" ref="C139" si="58">C131+1</f>
         <v>18</v>
       </c>
-      <c r="D139" s="525"/>
-      <c r="E139" s="525"/>
-      <c r="F139" s="525"/>
-      <c r="G139" s="525"/>
-      <c r="H139" s="525"/>
-      <c r="I139" s="528" t="s">
+      <c r="D139" s="549"/>
+      <c r="E139" s="549"/>
+      <c r="F139" s="549"/>
+      <c r="G139" s="549"/>
+      <c r="H139" s="549"/>
+      <c r="I139" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J139" s="175" t="s">
@@ -24082,13 +24082,13 @@
         <v>2022020</v>
       </c>
       <c r="B140" s="24"/>
-      <c r="C140" s="541"/>
-      <c r="D140" s="526"/>
-      <c r="E140" s="526"/>
-      <c r="F140" s="526"/>
-      <c r="G140" s="526"/>
-      <c r="H140" s="526"/>
-      <c r="I140" s="529"/>
+      <c r="C140" s="547"/>
+      <c r="D140" s="550"/>
+      <c r="E140" s="550"/>
+      <c r="F140" s="550"/>
+      <c r="G140" s="550"/>
+      <c r="H140" s="550"/>
+      <c r="I140" s="553"/>
       <c r="J140" s="176" t="s">
         <v>25</v>
       </c>
@@ -24140,13 +24140,13 @@
         <v>2022020</v>
       </c>
       <c r="B141" s="24"/>
-      <c r="C141" s="541"/>
-      <c r="D141" s="526"/>
-      <c r="E141" s="526"/>
-      <c r="F141" s="526"/>
-      <c r="G141" s="526"/>
-      <c r="H141" s="526"/>
-      <c r="I141" s="529"/>
+      <c r="C141" s="547"/>
+      <c r="D141" s="550"/>
+      <c r="E141" s="550"/>
+      <c r="F141" s="550"/>
+      <c r="G141" s="550"/>
+      <c r="H141" s="550"/>
+      <c r="I141" s="553"/>
       <c r="J141" s="176" t="s">
         <v>37</v>
       </c>
@@ -24198,13 +24198,13 @@
         <v>2022020</v>
       </c>
       <c r="B142" s="24"/>
-      <c r="C142" s="541"/>
-      <c r="D142" s="526"/>
-      <c r="E142" s="526"/>
-      <c r="F142" s="526"/>
-      <c r="G142" s="526"/>
-      <c r="H142" s="526"/>
-      <c r="I142" s="529"/>
+      <c r="C142" s="547"/>
+      <c r="D142" s="550"/>
+      <c r="E142" s="550"/>
+      <c r="F142" s="550"/>
+      <c r="G142" s="550"/>
+      <c r="H142" s="550"/>
+      <c r="I142" s="553"/>
       <c r="J142" s="176" t="s">
         <v>38</v>
       </c>
@@ -24256,13 +24256,13 @@
         <v>2022020</v>
       </c>
       <c r="B143" s="24"/>
-      <c r="C143" s="541"/>
-      <c r="D143" s="526"/>
-      <c r="E143" s="526"/>
-      <c r="F143" s="526"/>
-      <c r="G143" s="526"/>
-      <c r="H143" s="526"/>
-      <c r="I143" s="529"/>
+      <c r="C143" s="547"/>
+      <c r="D143" s="550"/>
+      <c r="E143" s="550"/>
+      <c r="F143" s="550"/>
+      <c r="G143" s="550"/>
+      <c r="H143" s="550"/>
+      <c r="I143" s="553"/>
       <c r="J143" s="176" t="s">
         <v>26</v>
       </c>
@@ -24314,13 +24314,13 @@
         <v>2022020</v>
       </c>
       <c r="B144" s="24"/>
-      <c r="C144" s="541"/>
-      <c r="D144" s="526"/>
-      <c r="E144" s="526"/>
-      <c r="F144" s="526"/>
-      <c r="G144" s="526"/>
-      <c r="H144" s="526"/>
-      <c r="I144" s="529"/>
+      <c r="C144" s="547"/>
+      <c r="D144" s="550"/>
+      <c r="E144" s="550"/>
+      <c r="F144" s="550"/>
+      <c r="G144" s="550"/>
+      <c r="H144" s="550"/>
+      <c r="I144" s="553"/>
       <c r="J144" s="176" t="s">
         <v>27</v>
       </c>
@@ -24372,13 +24372,13 @@
         <v>2022020</v>
       </c>
       <c r="B145" s="24"/>
-      <c r="C145" s="541"/>
-      <c r="D145" s="526"/>
-      <c r="E145" s="526"/>
-      <c r="F145" s="526"/>
-      <c r="G145" s="526"/>
-      <c r="H145" s="526"/>
-      <c r="I145" s="529"/>
+      <c r="C145" s="547"/>
+      <c r="D145" s="550"/>
+      <c r="E145" s="550"/>
+      <c r="F145" s="550"/>
+      <c r="G145" s="550"/>
+      <c r="H145" s="550"/>
+      <c r="I145" s="553"/>
       <c r="J145" s="176" t="s">
         <v>28</v>
       </c>
@@ -24430,13 +24430,13 @@
         <v>2022020</v>
       </c>
       <c r="B146" s="24"/>
-      <c r="C146" s="542"/>
-      <c r="D146" s="547"/>
-      <c r="E146" s="547"/>
-      <c r="F146" s="547"/>
-      <c r="G146" s="547"/>
-      <c r="H146" s="547"/>
-      <c r="I146" s="548"/>
+      <c r="C146" s="548"/>
+      <c r="D146" s="600"/>
+      <c r="E146" s="600"/>
+      <c r="F146" s="600"/>
+      <c r="G146" s="600"/>
+      <c r="H146" s="600"/>
+      <c r="I146" s="601"/>
       <c r="J146" s="180" t="s">
         <v>29</v>
       </c>
@@ -24486,16 +24486,16 @@
       <c r="A147" s="13">
         <v>2022021</v>
       </c>
-      <c r="C147" s="540">
+      <c r="C147" s="546">
         <f t="shared" ref="C147" si="62">C139+1</f>
         <v>19</v>
       </c>
-      <c r="D147" s="525"/>
-      <c r="E147" s="525"/>
-      <c r="F147" s="537"/>
-      <c r="G147" s="525"/>
-      <c r="H147" s="525"/>
-      <c r="I147" s="528" t="s">
+      <c r="D147" s="549"/>
+      <c r="E147" s="549"/>
+      <c r="F147" s="595"/>
+      <c r="G147" s="549"/>
+      <c r="H147" s="549"/>
+      <c r="I147" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J147" s="175" t="s">
@@ -24560,13 +24560,13 @@
         <v>2022021</v>
       </c>
       <c r="B148" s="24"/>
-      <c r="C148" s="541"/>
-      <c r="D148" s="526"/>
-      <c r="E148" s="526"/>
-      <c r="F148" s="538"/>
-      <c r="G148" s="526"/>
-      <c r="H148" s="526"/>
-      <c r="I148" s="529"/>
+      <c r="C148" s="547"/>
+      <c r="D148" s="550"/>
+      <c r="E148" s="550"/>
+      <c r="F148" s="596"/>
+      <c r="G148" s="550"/>
+      <c r="H148" s="550"/>
+      <c r="I148" s="553"/>
       <c r="J148" s="176" t="s">
         <v>25</v>
       </c>
@@ -24618,13 +24618,13 @@
         <v>2022021</v>
       </c>
       <c r="B149" s="24"/>
-      <c r="C149" s="541"/>
-      <c r="D149" s="526"/>
-      <c r="E149" s="526"/>
-      <c r="F149" s="538"/>
-      <c r="G149" s="526"/>
-      <c r="H149" s="526"/>
-      <c r="I149" s="529"/>
+      <c r="C149" s="547"/>
+      <c r="D149" s="550"/>
+      <c r="E149" s="550"/>
+      <c r="F149" s="596"/>
+      <c r="G149" s="550"/>
+      <c r="H149" s="550"/>
+      <c r="I149" s="553"/>
       <c r="J149" s="176" t="s">
         <v>37</v>
       </c>
@@ -24676,13 +24676,13 @@
         <v>2022021</v>
       </c>
       <c r="B150" s="24"/>
-      <c r="C150" s="541"/>
-      <c r="D150" s="526"/>
-      <c r="E150" s="526"/>
-      <c r="F150" s="538"/>
-      <c r="G150" s="526"/>
-      <c r="H150" s="526"/>
-      <c r="I150" s="529"/>
+      <c r="C150" s="547"/>
+      <c r="D150" s="550"/>
+      <c r="E150" s="550"/>
+      <c r="F150" s="596"/>
+      <c r="G150" s="550"/>
+      <c r="H150" s="550"/>
+      <c r="I150" s="553"/>
       <c r="J150" s="176" t="s">
         <v>38</v>
       </c>
@@ -24734,13 +24734,13 @@
         <v>2022021</v>
       </c>
       <c r="B151" s="24"/>
-      <c r="C151" s="541"/>
-      <c r="D151" s="526"/>
-      <c r="E151" s="526"/>
-      <c r="F151" s="538"/>
-      <c r="G151" s="526"/>
-      <c r="H151" s="526"/>
-      <c r="I151" s="529"/>
+      <c r="C151" s="547"/>
+      <c r="D151" s="550"/>
+      <c r="E151" s="550"/>
+      <c r="F151" s="596"/>
+      <c r="G151" s="550"/>
+      <c r="H151" s="550"/>
+      <c r="I151" s="553"/>
       <c r="J151" s="176" t="s">
         <v>26</v>
       </c>
@@ -24792,13 +24792,13 @@
         <v>2022021</v>
       </c>
       <c r="B152" s="24"/>
-      <c r="C152" s="541"/>
-      <c r="D152" s="526"/>
-      <c r="E152" s="526"/>
-      <c r="F152" s="538"/>
-      <c r="G152" s="526"/>
-      <c r="H152" s="526"/>
-      <c r="I152" s="529"/>
+      <c r="C152" s="547"/>
+      <c r="D152" s="550"/>
+      <c r="E152" s="550"/>
+      <c r="F152" s="596"/>
+      <c r="G152" s="550"/>
+      <c r="H152" s="550"/>
+      <c r="I152" s="553"/>
       <c r="J152" s="176" t="s">
         <v>27</v>
       </c>
@@ -24850,13 +24850,13 @@
         <v>2022021</v>
       </c>
       <c r="B153" s="24"/>
-      <c r="C153" s="541"/>
-      <c r="D153" s="526"/>
-      <c r="E153" s="526"/>
-      <c r="F153" s="538"/>
-      <c r="G153" s="526"/>
-      <c r="H153" s="526"/>
-      <c r="I153" s="529"/>
+      <c r="C153" s="547"/>
+      <c r="D153" s="550"/>
+      <c r="E153" s="550"/>
+      <c r="F153" s="596"/>
+      <c r="G153" s="550"/>
+      <c r="H153" s="550"/>
+      <c r="I153" s="553"/>
       <c r="J153" s="176" t="s">
         <v>28</v>
       </c>
@@ -24908,13 +24908,13 @@
         <v>2022021</v>
       </c>
       <c r="B154" s="24"/>
-      <c r="C154" s="542"/>
-      <c r="D154" s="527"/>
-      <c r="E154" s="527"/>
-      <c r="F154" s="539"/>
-      <c r="G154" s="527"/>
-      <c r="H154" s="527"/>
-      <c r="I154" s="530"/>
+      <c r="C154" s="548"/>
+      <c r="D154" s="551"/>
+      <c r="E154" s="551"/>
+      <c r="F154" s="597"/>
+      <c r="G154" s="551"/>
+      <c r="H154" s="551"/>
+      <c r="I154" s="554"/>
       <c r="J154" s="177" t="s">
         <v>29</v>
       </c>
@@ -24964,16 +24964,16 @@
       <c r="A155" s="13">
         <v>2022034</v>
       </c>
-      <c r="C155" s="540">
+      <c r="C155" s="546">
         <f t="shared" ref="C155" si="66">C147+1</f>
         <v>20</v>
       </c>
-      <c r="D155" s="543"/>
-      <c r="E155" s="543"/>
-      <c r="F155" s="543"/>
-      <c r="G155" s="543"/>
-      <c r="H155" s="543"/>
-      <c r="I155" s="544" t="s">
+      <c r="D155" s="598"/>
+      <c r="E155" s="598"/>
+      <c r="F155" s="598"/>
+      <c r="G155" s="598"/>
+      <c r="H155" s="598"/>
+      <c r="I155" s="599" t="s">
         <v>31</v>
       </c>
       <c r="J155" s="187" t="s">
@@ -25038,13 +25038,13 @@
         <v>2022034</v>
       </c>
       <c r="B156" s="24"/>
-      <c r="C156" s="541"/>
-      <c r="D156" s="526"/>
-      <c r="E156" s="526"/>
-      <c r="F156" s="526"/>
-      <c r="G156" s="526"/>
-      <c r="H156" s="526"/>
-      <c r="I156" s="529"/>
+      <c r="C156" s="547"/>
+      <c r="D156" s="550"/>
+      <c r="E156" s="550"/>
+      <c r="F156" s="550"/>
+      <c r="G156" s="550"/>
+      <c r="H156" s="550"/>
+      <c r="I156" s="553"/>
       <c r="J156" s="176" t="s">
         <v>25</v>
       </c>
@@ -25092,17 +25092,17 @@
     </row>
     <row r="157" spans="1:24">
       <c r="A157" s="14">
-        <f t="shared" ref="A157:B162" si="69">A156</f>
+        <f t="shared" ref="A157:A162" si="69">A156</f>
         <v>2022034</v>
       </c>
       <c r="B157" s="24"/>
-      <c r="C157" s="541"/>
-      <c r="D157" s="526"/>
-      <c r="E157" s="526"/>
-      <c r="F157" s="526"/>
-      <c r="G157" s="526"/>
-      <c r="H157" s="526"/>
-      <c r="I157" s="529"/>
+      <c r="C157" s="547"/>
+      <c r="D157" s="550"/>
+      <c r="E157" s="550"/>
+      <c r="F157" s="550"/>
+      <c r="G157" s="550"/>
+      <c r="H157" s="550"/>
+      <c r="I157" s="553"/>
       <c r="J157" s="176" t="s">
         <v>37</v>
       </c>
@@ -25154,13 +25154,13 @@
         <v>2022034</v>
       </c>
       <c r="B158" s="24"/>
-      <c r="C158" s="541"/>
-      <c r="D158" s="526"/>
-      <c r="E158" s="526"/>
-      <c r="F158" s="526"/>
-      <c r="G158" s="526"/>
-      <c r="H158" s="526"/>
-      <c r="I158" s="529"/>
+      <c r="C158" s="547"/>
+      <c r="D158" s="550"/>
+      <c r="E158" s="550"/>
+      <c r="F158" s="550"/>
+      <c r="G158" s="550"/>
+      <c r="H158" s="550"/>
+      <c r="I158" s="553"/>
       <c r="J158" s="176" t="s">
         <v>38</v>
       </c>
@@ -25212,13 +25212,13 @@
         <v>2022034</v>
       </c>
       <c r="B159" s="24"/>
-      <c r="C159" s="541"/>
-      <c r="D159" s="526"/>
-      <c r="E159" s="526"/>
-      <c r="F159" s="526"/>
-      <c r="G159" s="526"/>
-      <c r="H159" s="526"/>
-      <c r="I159" s="529"/>
+      <c r="C159" s="547"/>
+      <c r="D159" s="550"/>
+      <c r="E159" s="550"/>
+      <c r="F159" s="550"/>
+      <c r="G159" s="550"/>
+      <c r="H159" s="550"/>
+      <c r="I159" s="553"/>
       <c r="J159" s="176" t="s">
         <v>26</v>
       </c>
@@ -25270,13 +25270,13 @@
         <v>2022034</v>
       </c>
       <c r="B160" s="24"/>
-      <c r="C160" s="541"/>
-      <c r="D160" s="526"/>
-      <c r="E160" s="526"/>
-      <c r="F160" s="526"/>
-      <c r="G160" s="526"/>
-      <c r="H160" s="526"/>
-      <c r="I160" s="529"/>
+      <c r="C160" s="547"/>
+      <c r="D160" s="550"/>
+      <c r="E160" s="550"/>
+      <c r="F160" s="550"/>
+      <c r="G160" s="550"/>
+      <c r="H160" s="550"/>
+      <c r="I160" s="553"/>
       <c r="J160" s="176" t="s">
         <v>27</v>
       </c>
@@ -25328,13 +25328,13 @@
         <v>2022034</v>
       </c>
       <c r="B161" s="24"/>
-      <c r="C161" s="541"/>
-      <c r="D161" s="526"/>
-      <c r="E161" s="526"/>
-      <c r="F161" s="526"/>
-      <c r="G161" s="526"/>
-      <c r="H161" s="526"/>
-      <c r="I161" s="529"/>
+      <c r="C161" s="547"/>
+      <c r="D161" s="550"/>
+      <c r="E161" s="550"/>
+      <c r="F161" s="550"/>
+      <c r="G161" s="550"/>
+      <c r="H161" s="550"/>
+      <c r="I161" s="553"/>
       <c r="J161" s="176" t="s">
         <v>28</v>
       </c>
@@ -25386,13 +25386,13 @@
         <v>2022034</v>
       </c>
       <c r="B162" s="24"/>
-      <c r="C162" s="542"/>
-      <c r="D162" s="527"/>
-      <c r="E162" s="527"/>
-      <c r="F162" s="527"/>
-      <c r="G162" s="527"/>
-      <c r="H162" s="527"/>
-      <c r="I162" s="530"/>
+      <c r="C162" s="548"/>
+      <c r="D162" s="551"/>
+      <c r="E162" s="551"/>
+      <c r="F162" s="551"/>
+      <c r="G162" s="551"/>
+      <c r="H162" s="551"/>
+      <c r="I162" s="554"/>
       <c r="J162" s="177" t="s">
         <v>29</v>
       </c>
@@ -25443,16 +25443,16 @@
         <v>2020004</v>
       </c>
       <c r="B163" s="26"/>
-      <c r="C163" s="540">
+      <c r="C163" s="546">
         <f t="shared" ref="C163" si="70">C155+1</f>
         <v>21</v>
       </c>
-      <c r="D163" s="543"/>
-      <c r="E163" s="543"/>
-      <c r="F163" s="525"/>
-      <c r="G163" s="543"/>
-      <c r="H163" s="543"/>
-      <c r="I163" s="544" t="s">
+      <c r="D163" s="598"/>
+      <c r="E163" s="598"/>
+      <c r="F163" s="549"/>
+      <c r="G163" s="598"/>
+      <c r="H163" s="598"/>
+      <c r="I163" s="599" t="s">
         <v>31</v>
       </c>
       <c r="J163" s="187" t="s">
@@ -25513,17 +25513,17 @@
     </row>
     <row r="164" spans="1:24">
       <c r="A164" s="14">
-        <f t="shared" ref="A164:B170" si="72">A163</f>
+        <f t="shared" ref="A164:A170" si="72">A163</f>
         <v>2020004</v>
       </c>
       <c r="B164" s="24"/>
-      <c r="C164" s="541"/>
-      <c r="D164" s="526"/>
-      <c r="E164" s="526"/>
-      <c r="F164" s="526"/>
-      <c r="G164" s="526"/>
-      <c r="H164" s="526"/>
-      <c r="I164" s="529"/>
+      <c r="C164" s="547"/>
+      <c r="D164" s="550"/>
+      <c r="E164" s="550"/>
+      <c r="F164" s="550"/>
+      <c r="G164" s="550"/>
+      <c r="H164" s="550"/>
+      <c r="I164" s="553"/>
       <c r="J164" s="176" t="s">
         <v>25</v>
       </c>
@@ -25575,13 +25575,13 @@
         <v>2020004</v>
       </c>
       <c r="B165" s="24"/>
-      <c r="C165" s="541"/>
-      <c r="D165" s="526"/>
-      <c r="E165" s="526"/>
-      <c r="F165" s="526"/>
-      <c r="G165" s="526"/>
-      <c r="H165" s="526"/>
-      <c r="I165" s="529"/>
+      <c r="C165" s="547"/>
+      <c r="D165" s="550"/>
+      <c r="E165" s="550"/>
+      <c r="F165" s="550"/>
+      <c r="G165" s="550"/>
+      <c r="H165" s="550"/>
+      <c r="I165" s="553"/>
       <c r="J165" s="176" t="s">
         <v>37</v>
       </c>
@@ -25611,13 +25611,13 @@
         <v>2020004</v>
       </c>
       <c r="B166" s="24"/>
-      <c r="C166" s="541"/>
-      <c r="D166" s="526"/>
-      <c r="E166" s="526"/>
-      <c r="F166" s="526"/>
-      <c r="G166" s="526"/>
-      <c r="H166" s="526"/>
-      <c r="I166" s="529"/>
+      <c r="C166" s="547"/>
+      <c r="D166" s="550"/>
+      <c r="E166" s="550"/>
+      <c r="F166" s="550"/>
+      <c r="G166" s="550"/>
+      <c r="H166" s="550"/>
+      <c r="I166" s="553"/>
       <c r="J166" s="176" t="s">
         <v>38</v>
       </c>
@@ -25669,13 +25669,13 @@
         <v>2020004</v>
       </c>
       <c r="B167" s="24"/>
-      <c r="C167" s="541"/>
-      <c r="D167" s="526"/>
-      <c r="E167" s="526"/>
-      <c r="F167" s="526"/>
-      <c r="G167" s="526"/>
-      <c r="H167" s="526"/>
-      <c r="I167" s="529"/>
+      <c r="C167" s="547"/>
+      <c r="D167" s="550"/>
+      <c r="E167" s="550"/>
+      <c r="F167" s="550"/>
+      <c r="G167" s="550"/>
+      <c r="H167" s="550"/>
+      <c r="I167" s="553"/>
       <c r="J167" s="176" t="s">
         <v>26</v>
       </c>
@@ -25727,13 +25727,13 @@
         <v>2020004</v>
       </c>
       <c r="B168" s="24"/>
-      <c r="C168" s="541"/>
-      <c r="D168" s="526"/>
-      <c r="E168" s="526"/>
-      <c r="F168" s="526"/>
-      <c r="G168" s="526"/>
-      <c r="H168" s="526"/>
-      <c r="I168" s="529"/>
+      <c r="C168" s="547"/>
+      <c r="D168" s="550"/>
+      <c r="E168" s="550"/>
+      <c r="F168" s="550"/>
+      <c r="G168" s="550"/>
+      <c r="H168" s="550"/>
+      <c r="I168" s="553"/>
       <c r="J168" s="176" t="s">
         <v>27</v>
       </c>
@@ -25785,13 +25785,13 @@
         <v>2020004</v>
       </c>
       <c r="B169" s="24"/>
-      <c r="C169" s="541"/>
-      <c r="D169" s="526"/>
-      <c r="E169" s="526"/>
-      <c r="F169" s="526"/>
-      <c r="G169" s="526"/>
-      <c r="H169" s="526"/>
-      <c r="I169" s="529"/>
+      <c r="C169" s="547"/>
+      <c r="D169" s="550"/>
+      <c r="E169" s="550"/>
+      <c r="F169" s="550"/>
+      <c r="G169" s="550"/>
+      <c r="H169" s="550"/>
+      <c r="I169" s="553"/>
       <c r="J169" s="176" t="s">
         <v>28</v>
       </c>
@@ -25843,13 +25843,13 @@
         <v>2020004</v>
       </c>
       <c r="B170" s="24"/>
-      <c r="C170" s="542"/>
-      <c r="D170" s="527"/>
-      <c r="E170" s="527"/>
-      <c r="F170" s="527"/>
-      <c r="G170" s="527"/>
-      <c r="H170" s="527"/>
-      <c r="I170" s="530"/>
+      <c r="C170" s="548"/>
+      <c r="D170" s="551"/>
+      <c r="E170" s="551"/>
+      <c r="F170" s="551"/>
+      <c r="G170" s="551"/>
+      <c r="H170" s="551"/>
+      <c r="I170" s="554"/>
       <c r="J170" s="177" t="s">
         <v>29</v>
       </c>
@@ -25900,16 +25900,16 @@
         <v>2018017</v>
       </c>
       <c r="B171" s="26"/>
-      <c r="C171" s="540">
+      <c r="C171" s="546">
         <f t="shared" ref="C171" si="74">C163+1</f>
         <v>22</v>
       </c>
-      <c r="D171" s="525"/>
-      <c r="E171" s="525"/>
-      <c r="F171" s="565"/>
-      <c r="G171" s="543"/>
-      <c r="H171" s="543"/>
-      <c r="I171" s="528" t="s">
+      <c r="D171" s="549"/>
+      <c r="E171" s="549"/>
+      <c r="F171" s="615"/>
+      <c r="G171" s="598"/>
+      <c r="H171" s="598"/>
+      <c r="I171" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J171" s="186" t="s">
@@ -25970,17 +25970,17 @@
     </row>
     <row r="172" spans="1:24">
       <c r="A172" s="30">
-        <f t="shared" ref="A172:B178" si="77">A171</f>
+        <f t="shared" ref="A172:A178" si="77">A171</f>
         <v>2018017</v>
       </c>
       <c r="B172" s="27"/>
-      <c r="C172" s="541"/>
-      <c r="D172" s="526"/>
-      <c r="E172" s="526"/>
-      <c r="F172" s="566"/>
-      <c r="G172" s="526"/>
-      <c r="H172" s="526"/>
-      <c r="I172" s="529"/>
+      <c r="C172" s="547"/>
+      <c r="D172" s="550"/>
+      <c r="E172" s="550"/>
+      <c r="F172" s="616"/>
+      <c r="G172" s="550"/>
+      <c r="H172" s="550"/>
+      <c r="I172" s="553"/>
       <c r="J172" s="181" t="s">
         <v>25</v>
       </c>
@@ -26032,13 +26032,13 @@
         <v>2018017</v>
       </c>
       <c r="B173" s="27"/>
-      <c r="C173" s="541"/>
-      <c r="D173" s="526"/>
-      <c r="E173" s="526"/>
-      <c r="F173" s="566"/>
-      <c r="G173" s="526"/>
-      <c r="H173" s="526"/>
-      <c r="I173" s="529"/>
+      <c r="C173" s="547"/>
+      <c r="D173" s="550"/>
+      <c r="E173" s="550"/>
+      <c r="F173" s="616"/>
+      <c r="G173" s="550"/>
+      <c r="H173" s="550"/>
+      <c r="I173" s="553"/>
       <c r="J173" s="181" t="s">
         <v>37</v>
       </c>
@@ -26090,13 +26090,13 @@
         <v>2018017</v>
       </c>
       <c r="B174" s="27"/>
-      <c r="C174" s="541"/>
-      <c r="D174" s="526"/>
-      <c r="E174" s="526"/>
-      <c r="F174" s="566"/>
-      <c r="G174" s="526"/>
-      <c r="H174" s="526"/>
-      <c r="I174" s="529"/>
+      <c r="C174" s="547"/>
+      <c r="D174" s="550"/>
+      <c r="E174" s="550"/>
+      <c r="F174" s="616"/>
+      <c r="G174" s="550"/>
+      <c r="H174" s="550"/>
+      <c r="I174" s="553"/>
       <c r="J174" s="181" t="s">
         <v>38</v>
       </c>
@@ -26148,13 +26148,13 @@
         <v>2018017</v>
       </c>
       <c r="B175" s="27"/>
-      <c r="C175" s="541"/>
-      <c r="D175" s="526"/>
-      <c r="E175" s="526"/>
-      <c r="F175" s="566"/>
-      <c r="G175" s="526"/>
-      <c r="H175" s="526"/>
-      <c r="I175" s="529"/>
+      <c r="C175" s="547"/>
+      <c r="D175" s="550"/>
+      <c r="E175" s="550"/>
+      <c r="F175" s="616"/>
+      <c r="G175" s="550"/>
+      <c r="H175" s="550"/>
+      <c r="I175" s="553"/>
       <c r="J175" s="181" t="s">
         <v>26</v>
       </c>
@@ -26206,13 +26206,13 @@
         <v>2018017</v>
       </c>
       <c r="B176" s="27"/>
-      <c r="C176" s="541"/>
-      <c r="D176" s="526"/>
-      <c r="E176" s="526"/>
-      <c r="F176" s="566"/>
-      <c r="G176" s="526"/>
-      <c r="H176" s="526"/>
-      <c r="I176" s="529"/>
+      <c r="C176" s="547"/>
+      <c r="D176" s="550"/>
+      <c r="E176" s="550"/>
+      <c r="F176" s="616"/>
+      <c r="G176" s="550"/>
+      <c r="H176" s="550"/>
+      <c r="I176" s="553"/>
       <c r="J176" s="181" t="s">
         <v>27</v>
       </c>
@@ -26264,13 +26264,13 @@
         <v>2018017</v>
       </c>
       <c r="B177" s="27"/>
-      <c r="C177" s="541"/>
-      <c r="D177" s="526"/>
-      <c r="E177" s="526"/>
-      <c r="F177" s="566"/>
-      <c r="G177" s="526"/>
-      <c r="H177" s="526"/>
-      <c r="I177" s="529"/>
+      <c r="C177" s="547"/>
+      <c r="D177" s="550"/>
+      <c r="E177" s="550"/>
+      <c r="F177" s="616"/>
+      <c r="G177" s="550"/>
+      <c r="H177" s="550"/>
+      <c r="I177" s="553"/>
       <c r="J177" s="181" t="s">
         <v>28</v>
       </c>
@@ -26322,13 +26322,13 @@
         <v>2018017</v>
       </c>
       <c r="B178" s="27"/>
-      <c r="C178" s="542"/>
-      <c r="D178" s="527"/>
-      <c r="E178" s="527"/>
-      <c r="F178" s="567"/>
-      <c r="G178" s="527"/>
-      <c r="H178" s="527"/>
-      <c r="I178" s="530"/>
+      <c r="C178" s="548"/>
+      <c r="D178" s="551"/>
+      <c r="E178" s="551"/>
+      <c r="F178" s="617"/>
+      <c r="G178" s="551"/>
+      <c r="H178" s="551"/>
+      <c r="I178" s="554"/>
       <c r="J178" s="182" t="s">
         <v>29</v>
       </c>
@@ -26379,16 +26379,16 @@
         <v>2019034</v>
       </c>
       <c r="B179" s="26"/>
-      <c r="C179" s="540">
+      <c r="C179" s="546">
         <f t="shared" ref="C179" si="78">C171+1</f>
         <v>23</v>
       </c>
-      <c r="D179" s="525"/>
-      <c r="E179" s="525"/>
-      <c r="F179" s="565"/>
-      <c r="G179" s="543"/>
-      <c r="H179" s="543"/>
-      <c r="I179" s="544" t="s">
+      <c r="D179" s="549"/>
+      <c r="E179" s="549"/>
+      <c r="F179" s="615"/>
+      <c r="G179" s="598"/>
+      <c r="H179" s="598"/>
+      <c r="I179" s="599" t="s">
         <v>31</v>
       </c>
       <c r="J179" s="186" t="s">
@@ -26449,17 +26449,17 @@
     </row>
     <row r="180" spans="1:24">
       <c r="A180" s="30">
-        <f t="shared" ref="A180:B186" si="81">A179</f>
+        <f t="shared" ref="A180:A186" si="81">A179</f>
         <v>2019034</v>
       </c>
       <c r="B180" s="27"/>
-      <c r="C180" s="541"/>
-      <c r="D180" s="526"/>
-      <c r="E180" s="526"/>
-      <c r="F180" s="566"/>
-      <c r="G180" s="526"/>
-      <c r="H180" s="526"/>
-      <c r="I180" s="529"/>
+      <c r="C180" s="547"/>
+      <c r="D180" s="550"/>
+      <c r="E180" s="550"/>
+      <c r="F180" s="616"/>
+      <c r="G180" s="550"/>
+      <c r="H180" s="550"/>
+      <c r="I180" s="553"/>
       <c r="J180" s="181" t="s">
         <v>25</v>
       </c>
@@ -26511,13 +26511,13 @@
         <v>2019034</v>
       </c>
       <c r="B181" s="27"/>
-      <c r="C181" s="541"/>
-      <c r="D181" s="526"/>
-      <c r="E181" s="526"/>
-      <c r="F181" s="566"/>
-      <c r="G181" s="526"/>
-      <c r="H181" s="526"/>
-      <c r="I181" s="529"/>
+      <c r="C181" s="547"/>
+      <c r="D181" s="550"/>
+      <c r="E181" s="550"/>
+      <c r="F181" s="616"/>
+      <c r="G181" s="550"/>
+      <c r="H181" s="550"/>
+      <c r="I181" s="553"/>
       <c r="J181" s="181" t="s">
         <v>37</v>
       </c>
@@ -26569,13 +26569,13 @@
         <v>2019034</v>
       </c>
       <c r="B182" s="27"/>
-      <c r="C182" s="541"/>
-      <c r="D182" s="526"/>
-      <c r="E182" s="526"/>
-      <c r="F182" s="566"/>
-      <c r="G182" s="526"/>
-      <c r="H182" s="526"/>
-      <c r="I182" s="529"/>
+      <c r="C182" s="547"/>
+      <c r="D182" s="550"/>
+      <c r="E182" s="550"/>
+      <c r="F182" s="616"/>
+      <c r="G182" s="550"/>
+      <c r="H182" s="550"/>
+      <c r="I182" s="553"/>
       <c r="J182" s="181" t="s">
         <v>38</v>
       </c>
@@ -26627,13 +26627,13 @@
         <v>2019034</v>
       </c>
       <c r="B183" s="27"/>
-      <c r="C183" s="541"/>
-      <c r="D183" s="526"/>
-      <c r="E183" s="526"/>
-      <c r="F183" s="566"/>
-      <c r="G183" s="526"/>
-      <c r="H183" s="526"/>
-      <c r="I183" s="529"/>
+      <c r="C183" s="547"/>
+      <c r="D183" s="550"/>
+      <c r="E183" s="550"/>
+      <c r="F183" s="616"/>
+      <c r="G183" s="550"/>
+      <c r="H183" s="550"/>
+      <c r="I183" s="553"/>
       <c r="J183" s="181" t="s">
         <v>26</v>
       </c>
@@ -26685,13 +26685,13 @@
         <v>2019034</v>
       </c>
       <c r="B184" s="27"/>
-      <c r="C184" s="541"/>
-      <c r="D184" s="526"/>
-      <c r="E184" s="526"/>
-      <c r="F184" s="566"/>
-      <c r="G184" s="526"/>
-      <c r="H184" s="526"/>
-      <c r="I184" s="529"/>
+      <c r="C184" s="547"/>
+      <c r="D184" s="550"/>
+      <c r="E184" s="550"/>
+      <c r="F184" s="616"/>
+      <c r="G184" s="550"/>
+      <c r="H184" s="550"/>
+      <c r="I184" s="553"/>
       <c r="J184" s="181" t="s">
         <v>27</v>
       </c>
@@ -26743,13 +26743,13 @@
         <v>2019034</v>
       </c>
       <c r="B185" s="27"/>
-      <c r="C185" s="541"/>
-      <c r="D185" s="526"/>
-      <c r="E185" s="526"/>
-      <c r="F185" s="566"/>
-      <c r="G185" s="526"/>
-      <c r="H185" s="526"/>
-      <c r="I185" s="529"/>
+      <c r="C185" s="547"/>
+      <c r="D185" s="550"/>
+      <c r="E185" s="550"/>
+      <c r="F185" s="616"/>
+      <c r="G185" s="550"/>
+      <c r="H185" s="550"/>
+      <c r="I185" s="553"/>
       <c r="J185" s="181" t="s">
         <v>28</v>
       </c>
@@ -26801,13 +26801,13 @@
         <v>2019034</v>
       </c>
       <c r="B186" s="27"/>
-      <c r="C186" s="542"/>
-      <c r="D186" s="527"/>
-      <c r="E186" s="527"/>
-      <c r="F186" s="567"/>
-      <c r="G186" s="527"/>
-      <c r="H186" s="527"/>
-      <c r="I186" s="530"/>
+      <c r="C186" s="548"/>
+      <c r="D186" s="551"/>
+      <c r="E186" s="551"/>
+      <c r="F186" s="617"/>
+      <c r="G186" s="551"/>
+      <c r="H186" s="551"/>
+      <c r="I186" s="554"/>
       <c r="J186" s="182" t="s">
         <v>29</v>
       </c>
@@ -26858,16 +26858,16 @@
         <v>2021008</v>
       </c>
       <c r="B187" s="26"/>
-      <c r="C187" s="540">
+      <c r="C187" s="546">
         <f t="shared" ref="C187" si="82">C179+1</f>
         <v>24</v>
       </c>
-      <c r="D187" s="525"/>
-      <c r="E187" s="525"/>
-      <c r="F187" s="571"/>
-      <c r="G187" s="525"/>
-      <c r="H187" s="525"/>
-      <c r="I187" s="528" t="s">
+      <c r="D187" s="549"/>
+      <c r="E187" s="549"/>
+      <c r="F187" s="621"/>
+      <c r="G187" s="549"/>
+      <c r="H187" s="549"/>
+      <c r="I187" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J187" s="186" t="s">
@@ -26928,17 +26928,17 @@
     </row>
     <row r="188" spans="1:24">
       <c r="A188" s="30">
-        <f t="shared" ref="A188:B194" si="85">A187</f>
+        <f t="shared" ref="A188:A194" si="85">A187</f>
         <v>2021008</v>
       </c>
       <c r="B188" s="27"/>
-      <c r="C188" s="541"/>
-      <c r="D188" s="526"/>
-      <c r="E188" s="526"/>
-      <c r="F188" s="566"/>
-      <c r="G188" s="526"/>
-      <c r="H188" s="526"/>
-      <c r="I188" s="529"/>
+      <c r="C188" s="547"/>
+      <c r="D188" s="550"/>
+      <c r="E188" s="550"/>
+      <c r="F188" s="616"/>
+      <c r="G188" s="550"/>
+      <c r="H188" s="550"/>
+      <c r="I188" s="553"/>
       <c r="J188" s="181" t="s">
         <v>25</v>
       </c>
@@ -26992,13 +26992,13 @@
         <v>2021008</v>
       </c>
       <c r="B189" s="27"/>
-      <c r="C189" s="541"/>
-      <c r="D189" s="526"/>
-      <c r="E189" s="526"/>
-      <c r="F189" s="566"/>
-      <c r="G189" s="526"/>
-      <c r="H189" s="526"/>
-      <c r="I189" s="529"/>
+      <c r="C189" s="547"/>
+      <c r="D189" s="550"/>
+      <c r="E189" s="550"/>
+      <c r="F189" s="616"/>
+      <c r="G189" s="550"/>
+      <c r="H189" s="550"/>
+      <c r="I189" s="553"/>
       <c r="J189" s="181" t="s">
         <v>37</v>
       </c>
@@ -27050,13 +27050,13 @@
         <v>2021008</v>
       </c>
       <c r="B190" s="27"/>
-      <c r="C190" s="541"/>
-      <c r="D190" s="526"/>
-      <c r="E190" s="526"/>
-      <c r="F190" s="566"/>
-      <c r="G190" s="526"/>
-      <c r="H190" s="526"/>
-      <c r="I190" s="529"/>
+      <c r="C190" s="547"/>
+      <c r="D190" s="550"/>
+      <c r="E190" s="550"/>
+      <c r="F190" s="616"/>
+      <c r="G190" s="550"/>
+      <c r="H190" s="550"/>
+      <c r="I190" s="553"/>
       <c r="J190" s="181" t="s">
         <v>38</v>
       </c>
@@ -27109,13 +27109,13 @@
         <v>2021008</v>
       </c>
       <c r="B191" s="27"/>
-      <c r="C191" s="541"/>
-      <c r="D191" s="526"/>
-      <c r="E191" s="526"/>
-      <c r="F191" s="566"/>
-      <c r="G191" s="526"/>
-      <c r="H191" s="526"/>
-      <c r="I191" s="529"/>
+      <c r="C191" s="547"/>
+      <c r="D191" s="550"/>
+      <c r="E191" s="550"/>
+      <c r="F191" s="616"/>
+      <c r="G191" s="550"/>
+      <c r="H191" s="550"/>
+      <c r="I191" s="553"/>
       <c r="J191" s="181" t="s">
         <v>26</v>
       </c>
@@ -27169,13 +27169,13 @@
         <v>2021008</v>
       </c>
       <c r="B192" s="27"/>
-      <c r="C192" s="541"/>
-      <c r="D192" s="526"/>
-      <c r="E192" s="526"/>
-      <c r="F192" s="566"/>
-      <c r="G192" s="526"/>
-      <c r="H192" s="526"/>
-      <c r="I192" s="529"/>
+      <c r="C192" s="547"/>
+      <c r="D192" s="550"/>
+      <c r="E192" s="550"/>
+      <c r="F192" s="616"/>
+      <c r="G192" s="550"/>
+      <c r="H192" s="550"/>
+      <c r="I192" s="553"/>
       <c r="J192" s="181" t="s">
         <v>27</v>
       </c>
@@ -27229,13 +27229,13 @@
         <v>2021008</v>
       </c>
       <c r="B193" s="27"/>
-      <c r="C193" s="541"/>
-      <c r="D193" s="526"/>
-      <c r="E193" s="526"/>
-      <c r="F193" s="566"/>
-      <c r="G193" s="526"/>
-      <c r="H193" s="526"/>
-      <c r="I193" s="529"/>
+      <c r="C193" s="547"/>
+      <c r="D193" s="550"/>
+      <c r="E193" s="550"/>
+      <c r="F193" s="616"/>
+      <c r="G193" s="550"/>
+      <c r="H193" s="550"/>
+      <c r="I193" s="553"/>
       <c r="J193" s="181" t="s">
         <v>28</v>
       </c>
@@ -27289,13 +27289,13 @@
         <v>2021008</v>
       </c>
       <c r="B194" s="27"/>
-      <c r="C194" s="542"/>
-      <c r="D194" s="527"/>
-      <c r="E194" s="527"/>
-      <c r="F194" s="567"/>
-      <c r="G194" s="527"/>
-      <c r="H194" s="527"/>
-      <c r="I194" s="530"/>
+      <c r="C194" s="548"/>
+      <c r="D194" s="551"/>
+      <c r="E194" s="551"/>
+      <c r="F194" s="617"/>
+      <c r="G194" s="551"/>
+      <c r="H194" s="551"/>
+      <c r="I194" s="554"/>
       <c r="J194" s="182" t="s">
         <v>29</v>
       </c>
@@ -27347,16 +27347,16 @@
       <c r="A195" s="13">
         <v>2018026</v>
       </c>
-      <c r="C195" s="540">
+      <c r="C195" s="546">
         <f t="shared" ref="C195" si="86">C187+1</f>
         <v>25</v>
       </c>
-      <c r="D195" s="525"/>
-      <c r="E195" s="525"/>
-      <c r="F195" s="568"/>
-      <c r="G195" s="525"/>
-      <c r="H195" s="525"/>
-      <c r="I195" s="528" t="s">
+      <c r="D195" s="549"/>
+      <c r="E195" s="549"/>
+      <c r="F195" s="618"/>
+      <c r="G195" s="549"/>
+      <c r="H195" s="549"/>
+      <c r="I195" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J195" s="186" t="s">
@@ -27421,13 +27421,13 @@
         <v>2018026</v>
       </c>
       <c r="B196" s="27"/>
-      <c r="C196" s="541"/>
-      <c r="D196" s="526"/>
-      <c r="E196" s="526"/>
-      <c r="F196" s="569"/>
-      <c r="G196" s="526"/>
-      <c r="H196" s="526"/>
-      <c r="I196" s="529"/>
+      <c r="C196" s="547"/>
+      <c r="D196" s="550"/>
+      <c r="E196" s="550"/>
+      <c r="F196" s="619"/>
+      <c r="G196" s="550"/>
+      <c r="H196" s="550"/>
+      <c r="I196" s="553"/>
       <c r="J196" s="181" t="s">
         <v>25</v>
       </c>
@@ -27479,13 +27479,13 @@
         <v>2018026</v>
       </c>
       <c r="B197" s="27"/>
-      <c r="C197" s="541"/>
-      <c r="D197" s="526"/>
-      <c r="E197" s="526"/>
-      <c r="F197" s="569"/>
-      <c r="G197" s="526"/>
-      <c r="H197" s="526"/>
-      <c r="I197" s="529"/>
+      <c r="C197" s="547"/>
+      <c r="D197" s="550"/>
+      <c r="E197" s="550"/>
+      <c r="F197" s="619"/>
+      <c r="G197" s="550"/>
+      <c r="H197" s="550"/>
+      <c r="I197" s="553"/>
       <c r="J197" s="181" t="s">
         <v>37</v>
       </c>
@@ -27533,17 +27533,17 @@
     </row>
     <row r="198" spans="1:24">
       <c r="A198" s="30">
-        <f t="shared" ref="A196:B202" si="91">A197</f>
+        <f t="shared" ref="A198:A202" si="91">A197</f>
         <v>2018026</v>
       </c>
       <c r="B198" s="27"/>
-      <c r="C198" s="541"/>
-      <c r="D198" s="526"/>
-      <c r="E198" s="526"/>
-      <c r="F198" s="569"/>
-      <c r="G198" s="526"/>
-      <c r="H198" s="526"/>
-      <c r="I198" s="529"/>
+      <c r="C198" s="547"/>
+      <c r="D198" s="550"/>
+      <c r="E198" s="550"/>
+      <c r="F198" s="619"/>
+      <c r="G198" s="550"/>
+      <c r="H198" s="550"/>
+      <c r="I198" s="553"/>
       <c r="J198" s="181" t="s">
         <v>38</v>
       </c>
@@ -27595,13 +27595,13 @@
         <v>2018026</v>
       </c>
       <c r="B199" s="27"/>
-      <c r="C199" s="541"/>
-      <c r="D199" s="526"/>
-      <c r="E199" s="526"/>
-      <c r="F199" s="569"/>
-      <c r="G199" s="526"/>
-      <c r="H199" s="526"/>
-      <c r="I199" s="529"/>
+      <c r="C199" s="547"/>
+      <c r="D199" s="550"/>
+      <c r="E199" s="550"/>
+      <c r="F199" s="619"/>
+      <c r="G199" s="550"/>
+      <c r="H199" s="550"/>
+      <c r="I199" s="553"/>
       <c r="J199" s="181" t="s">
         <v>26</v>
       </c>
@@ -27653,13 +27653,13 @@
         <v>2018026</v>
       </c>
       <c r="B200" s="27"/>
-      <c r="C200" s="541"/>
-      <c r="D200" s="526"/>
-      <c r="E200" s="526"/>
-      <c r="F200" s="569"/>
-      <c r="G200" s="526"/>
-      <c r="H200" s="526"/>
-      <c r="I200" s="529"/>
+      <c r="C200" s="547"/>
+      <c r="D200" s="550"/>
+      <c r="E200" s="550"/>
+      <c r="F200" s="619"/>
+      <c r="G200" s="550"/>
+      <c r="H200" s="550"/>
+      <c r="I200" s="553"/>
       <c r="J200" s="181" t="s">
         <v>27</v>
       </c>
@@ -27711,13 +27711,13 @@
         <v>2018026</v>
       </c>
       <c r="B201" s="27"/>
-      <c r="C201" s="541"/>
-      <c r="D201" s="526"/>
-      <c r="E201" s="526"/>
-      <c r="F201" s="569"/>
-      <c r="G201" s="526"/>
-      <c r="H201" s="526"/>
-      <c r="I201" s="529"/>
+      <c r="C201" s="547"/>
+      <c r="D201" s="550"/>
+      <c r="E201" s="550"/>
+      <c r="F201" s="619"/>
+      <c r="G201" s="550"/>
+      <c r="H201" s="550"/>
+      <c r="I201" s="553"/>
       <c r="J201" s="181" t="s">
         <v>28</v>
       </c>
@@ -27769,13 +27769,13 @@
         <v>2018026</v>
       </c>
       <c r="B202" s="27"/>
-      <c r="C202" s="542"/>
-      <c r="D202" s="527"/>
-      <c r="E202" s="527"/>
-      <c r="F202" s="570"/>
-      <c r="G202" s="527"/>
-      <c r="H202" s="527"/>
-      <c r="I202" s="530"/>
+      <c r="C202" s="548"/>
+      <c r="D202" s="551"/>
+      <c r="E202" s="551"/>
+      <c r="F202" s="620"/>
+      <c r="G202" s="551"/>
+      <c r="H202" s="551"/>
+      <c r="I202" s="554"/>
       <c r="J202" s="182" t="s">
         <v>29</v>
       </c>
@@ -27826,18 +27826,18 @@
         <v>2021011</v>
       </c>
       <c r="B203" s="2"/>
-      <c r="C203" s="522">
+      <c r="C203" s="528">
         <f t="shared" ref="C203" si="92">C195+1</f>
         <v>26</v>
       </c>
-      <c r="D203" s="531"/>
-      <c r="E203" s="531" t="s">
+      <c r="D203" s="522"/>
+      <c r="E203" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F203" s="531"/>
-      <c r="G203" s="531"/>
-      <c r="H203" s="531"/>
-      <c r="I203" s="534" t="s">
+      <c r="F203" s="522"/>
+      <c r="G203" s="522"/>
+      <c r="H203" s="522"/>
+      <c r="I203" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J203" s="186" t="s">
@@ -27898,17 +27898,17 @@
     </row>
     <row r="204" spans="1:24">
       <c r="A204" s="30">
-        <f t="shared" ref="A204:B210" si="95">A203</f>
+        <f t="shared" ref="A204:A210" si="95">A203</f>
         <v>2021011</v>
       </c>
       <c r="B204" s="27"/>
-      <c r="C204" s="523"/>
-      <c r="D204" s="532"/>
-      <c r="E204" s="532"/>
-      <c r="F204" s="532"/>
-      <c r="G204" s="532"/>
-      <c r="H204" s="532"/>
-      <c r="I204" s="535"/>
+      <c r="C204" s="529"/>
+      <c r="D204" s="523"/>
+      <c r="E204" s="523"/>
+      <c r="F204" s="523"/>
+      <c r="G204" s="523"/>
+      <c r="H204" s="523"/>
+      <c r="I204" s="526"/>
       <c r="J204" s="181" t="s">
         <v>25</v>
       </c>
@@ -27942,13 +27942,13 @@
         <v>2021011</v>
       </c>
       <c r="B205" s="27"/>
-      <c r="C205" s="523"/>
-      <c r="D205" s="532"/>
-      <c r="E205" s="532"/>
-      <c r="F205" s="532"/>
-      <c r="G205" s="532"/>
-      <c r="H205" s="532"/>
-      <c r="I205" s="535"/>
+      <c r="C205" s="529"/>
+      <c r="D205" s="523"/>
+      <c r="E205" s="523"/>
+      <c r="F205" s="523"/>
+      <c r="G205" s="523"/>
+      <c r="H205" s="523"/>
+      <c r="I205" s="526"/>
       <c r="J205" s="181" t="s">
         <v>37</v>
       </c>
@@ -27976,13 +27976,13 @@
         <v>2021011</v>
       </c>
       <c r="B206" s="27"/>
-      <c r="C206" s="523"/>
-      <c r="D206" s="532"/>
-      <c r="E206" s="532"/>
-      <c r="F206" s="532"/>
-      <c r="G206" s="532"/>
-      <c r="H206" s="532"/>
-      <c r="I206" s="535"/>
+      <c r="C206" s="529"/>
+      <c r="D206" s="523"/>
+      <c r="E206" s="523"/>
+      <c r="F206" s="523"/>
+      <c r="G206" s="523"/>
+      <c r="H206" s="523"/>
+      <c r="I206" s="526"/>
       <c r="J206" s="181" t="s">
         <v>38</v>
       </c>
@@ -28016,13 +28016,13 @@
         <v>2021011</v>
       </c>
       <c r="B207" s="27"/>
-      <c r="C207" s="523"/>
-      <c r="D207" s="532"/>
-      <c r="E207" s="532"/>
-      <c r="F207" s="532"/>
-      <c r="G207" s="532"/>
-      <c r="H207" s="532"/>
-      <c r="I207" s="535"/>
+      <c r="C207" s="529"/>
+      <c r="D207" s="523"/>
+      <c r="E207" s="523"/>
+      <c r="F207" s="523"/>
+      <c r="G207" s="523"/>
+      <c r="H207" s="523"/>
+      <c r="I207" s="526"/>
       <c r="J207" s="181" t="s">
         <v>26</v>
       </c>
@@ -28056,13 +28056,13 @@
         <v>2021011</v>
       </c>
       <c r="B208" s="27"/>
-      <c r="C208" s="523"/>
-      <c r="D208" s="532"/>
-      <c r="E208" s="532"/>
-      <c r="F208" s="532"/>
-      <c r="G208" s="532"/>
-      <c r="H208" s="532"/>
-      <c r="I208" s="535"/>
+      <c r="C208" s="529"/>
+      <c r="D208" s="523"/>
+      <c r="E208" s="523"/>
+      <c r="F208" s="523"/>
+      <c r="G208" s="523"/>
+      <c r="H208" s="523"/>
+      <c r="I208" s="526"/>
       <c r="J208" s="181" t="s">
         <v>27</v>
       </c>
@@ -28096,13 +28096,13 @@
         <v>2021011</v>
       </c>
       <c r="B209" s="27"/>
-      <c r="C209" s="523"/>
-      <c r="D209" s="532"/>
-      <c r="E209" s="532"/>
-      <c r="F209" s="532"/>
-      <c r="G209" s="532"/>
-      <c r="H209" s="532"/>
-      <c r="I209" s="535"/>
+      <c r="C209" s="529"/>
+      <c r="D209" s="523"/>
+      <c r="E209" s="523"/>
+      <c r="F209" s="523"/>
+      <c r="G209" s="523"/>
+      <c r="H209" s="523"/>
+      <c r="I209" s="526"/>
       <c r="J209" s="181" t="s">
         <v>28</v>
       </c>
@@ -28136,13 +28136,13 @@
         <v>2021011</v>
       </c>
       <c r="B210" s="27"/>
-      <c r="C210" s="524"/>
-      <c r="D210" s="533"/>
-      <c r="E210" s="533"/>
-      <c r="F210" s="533"/>
-      <c r="G210" s="533"/>
-      <c r="H210" s="533"/>
-      <c r="I210" s="536"/>
+      <c r="C210" s="530"/>
+      <c r="D210" s="524"/>
+      <c r="E210" s="524"/>
+      <c r="F210" s="524"/>
+      <c r="G210" s="524"/>
+      <c r="H210" s="524"/>
+      <c r="I210" s="527"/>
       <c r="J210" s="182" t="s">
         <v>29</v>
       </c>
@@ -28175,16 +28175,16 @@
         <v>2023032</v>
       </c>
       <c r="B211" s="2"/>
-      <c r="C211" s="522">
+      <c r="C211" s="528">
         <f t="shared" ref="C211:C243" si="96">C203+1</f>
         <v>27</v>
       </c>
-      <c r="D211" s="525"/>
-      <c r="E211" s="525"/>
-      <c r="F211" s="525"/>
-      <c r="G211" s="525"/>
-      <c r="H211" s="525"/>
-      <c r="I211" s="528" t="s">
+      <c r="D211" s="549"/>
+      <c r="E211" s="549"/>
+      <c r="F211" s="549"/>
+      <c r="G211" s="549"/>
+      <c r="H211" s="549"/>
+      <c r="I211" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J211" s="186" t="s">
@@ -28245,17 +28245,17 @@
     </row>
     <row r="212" spans="1:24">
       <c r="A212" s="30">
-        <f t="shared" ref="A212:B212" si="99">A211</f>
+        <f t="shared" ref="A212" si="99">A211</f>
         <v>2023032</v>
       </c>
       <c r="B212" s="27"/>
-      <c r="C212" s="523"/>
-      <c r="D212" s="526"/>
-      <c r="E212" s="526"/>
-      <c r="F212" s="526"/>
-      <c r="G212" s="526"/>
-      <c r="H212" s="526"/>
-      <c r="I212" s="529"/>
+      <c r="C212" s="529"/>
+      <c r="D212" s="550"/>
+      <c r="E212" s="550"/>
+      <c r="F212" s="550"/>
+      <c r="G212" s="550"/>
+      <c r="H212" s="550"/>
+      <c r="I212" s="553"/>
       <c r="J212" s="181" t="s">
         <v>25</v>
       </c>
@@ -28303,17 +28303,17 @@
     </row>
     <row r="213" spans="1:24">
       <c r="A213" s="30">
-        <f t="shared" ref="A213:B213" si="100">A212</f>
+        <f t="shared" ref="A213" si="100">A212</f>
         <v>2023032</v>
       </c>
       <c r="B213" s="27"/>
-      <c r="C213" s="523"/>
-      <c r="D213" s="526"/>
-      <c r="E213" s="526"/>
-      <c r="F213" s="526"/>
-      <c r="G213" s="526"/>
-      <c r="H213" s="526"/>
-      <c r="I213" s="529"/>
+      <c r="C213" s="529"/>
+      <c r="D213" s="550"/>
+      <c r="E213" s="550"/>
+      <c r="F213" s="550"/>
+      <c r="G213" s="550"/>
+      <c r="H213" s="550"/>
+      <c r="I213" s="553"/>
       <c r="J213" s="181" t="s">
         <v>37</v>
       </c>
@@ -28361,17 +28361,17 @@
     </row>
     <row r="214" spans="1:24">
       <c r="A214" s="30">
-        <f t="shared" ref="A214:B214" si="101">A213</f>
+        <f t="shared" ref="A214" si="101">A213</f>
         <v>2023032</v>
       </c>
       <c r="B214" s="27"/>
-      <c r="C214" s="523"/>
-      <c r="D214" s="526"/>
-      <c r="E214" s="526"/>
-      <c r="F214" s="526"/>
-      <c r="G214" s="526"/>
-      <c r="H214" s="526"/>
-      <c r="I214" s="529"/>
+      <c r="C214" s="529"/>
+      <c r="D214" s="550"/>
+      <c r="E214" s="550"/>
+      <c r="F214" s="550"/>
+      <c r="G214" s="550"/>
+      <c r="H214" s="550"/>
+      <c r="I214" s="553"/>
       <c r="J214" s="181" t="s">
         <v>38</v>
       </c>
@@ -28419,17 +28419,17 @@
     </row>
     <row r="215" spans="1:24">
       <c r="A215" s="30">
-        <f t="shared" ref="A215:B215" si="102">A214</f>
+        <f t="shared" ref="A215" si="102">A214</f>
         <v>2023032</v>
       </c>
       <c r="B215" s="27"/>
-      <c r="C215" s="523"/>
-      <c r="D215" s="526"/>
-      <c r="E215" s="526"/>
-      <c r="F215" s="526"/>
-      <c r="G215" s="526"/>
-      <c r="H215" s="526"/>
-      <c r="I215" s="529"/>
+      <c r="C215" s="529"/>
+      <c r="D215" s="550"/>
+      <c r="E215" s="550"/>
+      <c r="F215" s="550"/>
+      <c r="G215" s="550"/>
+      <c r="H215" s="550"/>
+      <c r="I215" s="553"/>
       <c r="J215" s="181" t="s">
         <v>26</v>
       </c>
@@ -28477,17 +28477,17 @@
     </row>
     <row r="216" spans="1:24">
       <c r="A216" s="30">
-        <f t="shared" ref="A216:B216" si="103">A215</f>
+        <f t="shared" ref="A216" si="103">A215</f>
         <v>2023032</v>
       </c>
       <c r="B216" s="27"/>
-      <c r="C216" s="523"/>
-      <c r="D216" s="526"/>
-      <c r="E216" s="526"/>
-      <c r="F216" s="526"/>
-      <c r="G216" s="526"/>
-      <c r="H216" s="526"/>
-      <c r="I216" s="529"/>
+      <c r="C216" s="529"/>
+      <c r="D216" s="550"/>
+      <c r="E216" s="550"/>
+      <c r="F216" s="550"/>
+      <c r="G216" s="550"/>
+      <c r="H216" s="550"/>
+      <c r="I216" s="553"/>
       <c r="J216" s="181" t="s">
         <v>27</v>
       </c>
@@ -28535,17 +28535,17 @@
     </row>
     <row r="217" spans="1:24">
       <c r="A217" s="30">
-        <f t="shared" ref="A217:B217" si="104">A216</f>
+        <f t="shared" ref="A217" si="104">A216</f>
         <v>2023032</v>
       </c>
       <c r="B217" s="27"/>
-      <c r="C217" s="523"/>
-      <c r="D217" s="526"/>
-      <c r="E217" s="526"/>
-      <c r="F217" s="526"/>
-      <c r="G217" s="526"/>
-      <c r="H217" s="526"/>
-      <c r="I217" s="529"/>
+      <c r="C217" s="529"/>
+      <c r="D217" s="550"/>
+      <c r="E217" s="550"/>
+      <c r="F217" s="550"/>
+      <c r="G217" s="550"/>
+      <c r="H217" s="550"/>
+      <c r="I217" s="553"/>
       <c r="J217" s="181" t="s">
         <v>28</v>
       </c>
@@ -28593,17 +28593,17 @@
     </row>
     <row r="218" spans="1:24">
       <c r="A218" s="30">
-        <f t="shared" ref="A218:B218" si="105">A217</f>
+        <f t="shared" ref="A218" si="105">A217</f>
         <v>2023032</v>
       </c>
       <c r="B218" s="27"/>
-      <c r="C218" s="524"/>
-      <c r="D218" s="527"/>
-      <c r="E218" s="527"/>
-      <c r="F218" s="527"/>
-      <c r="G218" s="527"/>
-      <c r="H218" s="527"/>
-      <c r="I218" s="530"/>
+      <c r="C218" s="530"/>
+      <c r="D218" s="551"/>
+      <c r="E218" s="551"/>
+      <c r="F218" s="551"/>
+      <c r="G218" s="551"/>
+      <c r="H218" s="551"/>
+      <c r="I218" s="554"/>
       <c r="J218" s="182" t="s">
         <v>29</v>
       </c>
@@ -28654,18 +28654,18 @@
         <v>2024020</v>
       </c>
       <c r="B219" s="2"/>
-      <c r="C219" s="522">
+      <c r="C219" s="528">
         <f t="shared" si="96"/>
         <v>28</v>
       </c>
-      <c r="D219" s="531"/>
-      <c r="E219" s="531" t="s">
+      <c r="D219" s="522"/>
+      <c r="E219" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F219" s="531"/>
-      <c r="G219" s="531"/>
-      <c r="H219" s="531"/>
-      <c r="I219" s="534" t="s">
+      <c r="F219" s="522"/>
+      <c r="G219" s="522"/>
+      <c r="H219" s="522"/>
+      <c r="I219" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J219" s="186" t="s">
@@ -28726,17 +28726,17 @@
     </row>
     <row r="220" spans="1:24">
       <c r="A220" s="30">
-        <f t="shared" ref="A220:B220" si="107">A219</f>
+        <f t="shared" ref="A220" si="107">A219</f>
         <v>2024020</v>
       </c>
       <c r="B220" s="27"/>
-      <c r="C220" s="523"/>
-      <c r="D220" s="532"/>
-      <c r="E220" s="532"/>
-      <c r="F220" s="532"/>
-      <c r="G220" s="532"/>
-      <c r="H220" s="532"/>
-      <c r="I220" s="535"/>
+      <c r="C220" s="529"/>
+      <c r="D220" s="523"/>
+      <c r="E220" s="523"/>
+      <c r="F220" s="523"/>
+      <c r="G220" s="523"/>
+      <c r="H220" s="523"/>
+      <c r="I220" s="526"/>
       <c r="J220" s="181" t="s">
         <v>25</v>
       </c>
@@ -28768,17 +28768,17 @@
     </row>
     <row r="221" spans="1:24">
       <c r="A221" s="30">
-        <f t="shared" ref="A221:B221" si="108">A220</f>
+        <f t="shared" ref="A221" si="108">A220</f>
         <v>2024020</v>
       </c>
       <c r="B221" s="27"/>
-      <c r="C221" s="523"/>
-      <c r="D221" s="532"/>
-      <c r="E221" s="532"/>
-      <c r="F221" s="532"/>
-      <c r="G221" s="532"/>
-      <c r="H221" s="532"/>
-      <c r="I221" s="535"/>
+      <c r="C221" s="529"/>
+      <c r="D221" s="523"/>
+      <c r="E221" s="523"/>
+      <c r="F221" s="523"/>
+      <c r="G221" s="523"/>
+      <c r="H221" s="523"/>
+      <c r="I221" s="526"/>
       <c r="J221" s="181" t="s">
         <v>37</v>
       </c>
@@ -28802,17 +28802,17 @@
     </row>
     <row r="222" spans="1:24">
       <c r="A222" s="30">
-        <f t="shared" ref="A222:B222" si="109">A221</f>
+        <f t="shared" ref="A222" si="109">A221</f>
         <v>2024020</v>
       </c>
       <c r="B222" s="27"/>
-      <c r="C222" s="523"/>
-      <c r="D222" s="532"/>
-      <c r="E222" s="532"/>
-      <c r="F222" s="532"/>
-      <c r="G222" s="532"/>
-      <c r="H222" s="532"/>
-      <c r="I222" s="535"/>
+      <c r="C222" s="529"/>
+      <c r="D222" s="523"/>
+      <c r="E222" s="523"/>
+      <c r="F222" s="523"/>
+      <c r="G222" s="523"/>
+      <c r="H222" s="523"/>
+      <c r="I222" s="526"/>
       <c r="J222" s="181" t="s">
         <v>38</v>
       </c>
@@ -28844,17 +28844,17 @@
     </row>
     <row r="223" spans="1:24">
       <c r="A223" s="30">
-        <f t="shared" ref="A223:B223" si="110">A222</f>
+        <f t="shared" ref="A223" si="110">A222</f>
         <v>2024020</v>
       </c>
       <c r="B223" s="27"/>
-      <c r="C223" s="523"/>
-      <c r="D223" s="532"/>
-      <c r="E223" s="532"/>
-      <c r="F223" s="532"/>
-      <c r="G223" s="532"/>
-      <c r="H223" s="532"/>
-      <c r="I223" s="535"/>
+      <c r="C223" s="529"/>
+      <c r="D223" s="523"/>
+      <c r="E223" s="523"/>
+      <c r="F223" s="523"/>
+      <c r="G223" s="523"/>
+      <c r="H223" s="523"/>
+      <c r="I223" s="526"/>
       <c r="J223" s="181" t="s">
         <v>26</v>
       </c>
@@ -28886,17 +28886,17 @@
     </row>
     <row r="224" spans="1:24">
       <c r="A224" s="30">
-        <f t="shared" ref="A224:B224" si="111">A223</f>
+        <f t="shared" ref="A224" si="111">A223</f>
         <v>2024020</v>
       </c>
       <c r="B224" s="27"/>
-      <c r="C224" s="523"/>
-      <c r="D224" s="532"/>
-      <c r="E224" s="532"/>
-      <c r="F224" s="532"/>
-      <c r="G224" s="532"/>
-      <c r="H224" s="532"/>
-      <c r="I224" s="535"/>
+      <c r="C224" s="529"/>
+      <c r="D224" s="523"/>
+      <c r="E224" s="523"/>
+      <c r="F224" s="523"/>
+      <c r="G224" s="523"/>
+      <c r="H224" s="523"/>
+      <c r="I224" s="526"/>
       <c r="J224" s="181" t="s">
         <v>27</v>
       </c>
@@ -28928,17 +28928,17 @@
     </row>
     <row r="225" spans="1:24">
       <c r="A225" s="30">
-        <f t="shared" ref="A225:B225" si="112">A224</f>
+        <f t="shared" ref="A225" si="112">A224</f>
         <v>2024020</v>
       </c>
       <c r="B225" s="27"/>
-      <c r="C225" s="523"/>
-      <c r="D225" s="532"/>
-      <c r="E225" s="532"/>
-      <c r="F225" s="532"/>
-      <c r="G225" s="532"/>
-      <c r="H225" s="532"/>
-      <c r="I225" s="535"/>
+      <c r="C225" s="529"/>
+      <c r="D225" s="523"/>
+      <c r="E225" s="523"/>
+      <c r="F225" s="523"/>
+      <c r="G225" s="523"/>
+      <c r="H225" s="523"/>
+      <c r="I225" s="526"/>
       <c r="J225" s="181" t="s">
         <v>28</v>
       </c>
@@ -28970,17 +28970,17 @@
     </row>
     <row r="226" spans="1:24">
       <c r="A226" s="30">
-        <f t="shared" ref="A226:B226" si="113">A225</f>
+        <f t="shared" ref="A226" si="113">A225</f>
         <v>2024020</v>
       </c>
       <c r="B226" s="27"/>
-      <c r="C226" s="524"/>
-      <c r="D226" s="533"/>
-      <c r="E226" s="533"/>
-      <c r="F226" s="533"/>
-      <c r="G226" s="533"/>
-      <c r="H226" s="533"/>
-      <c r="I226" s="536"/>
+      <c r="C226" s="530"/>
+      <c r="D226" s="524"/>
+      <c r="E226" s="524"/>
+      <c r="F226" s="524"/>
+      <c r="G226" s="524"/>
+      <c r="H226" s="524"/>
+      <c r="I226" s="527"/>
       <c r="J226" s="182" t="s">
         <v>29</v>
       </c>
@@ -29015,16 +29015,16 @@
         <v>2025002</v>
       </c>
       <c r="B227" s="2"/>
-      <c r="C227" s="522">
+      <c r="C227" s="528">
         <f t="shared" si="96"/>
         <v>29</v>
       </c>
-      <c r="D227" s="525"/>
-      <c r="E227" s="525"/>
-      <c r="F227" s="525"/>
-      <c r="G227" s="525"/>
-      <c r="H227" s="525"/>
-      <c r="I227" s="528" t="s">
+      <c r="D227" s="549"/>
+      <c r="E227" s="549"/>
+      <c r="F227" s="549"/>
+      <c r="G227" s="549"/>
+      <c r="H227" s="549"/>
+      <c r="I227" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J227" s="186" t="s">
@@ -29085,17 +29085,17 @@
     </row>
     <row r="228" spans="1:24">
       <c r="A228" s="30">
-        <f t="shared" ref="A228:B228" si="115">A227</f>
+        <f t="shared" ref="A228" si="115">A227</f>
         <v>2025002</v>
       </c>
       <c r="B228" s="27"/>
-      <c r="C228" s="523"/>
-      <c r="D228" s="526"/>
-      <c r="E228" s="526"/>
-      <c r="F228" s="526"/>
-      <c r="G228" s="526"/>
-      <c r="H228" s="526"/>
-      <c r="I228" s="529"/>
+      <c r="C228" s="529"/>
+      <c r="D228" s="550"/>
+      <c r="E228" s="550"/>
+      <c r="F228" s="550"/>
+      <c r="G228" s="550"/>
+      <c r="H228" s="550"/>
+      <c r="I228" s="553"/>
       <c r="J228" s="181" t="s">
         <v>25</v>
       </c>
@@ -29139,17 +29139,17 @@
     </row>
     <row r="229" spans="1:24">
       <c r="A229" s="30">
-        <f t="shared" ref="A229:B229" si="117">A228</f>
+        <f t="shared" ref="A229" si="117">A228</f>
         <v>2025002</v>
       </c>
       <c r="B229" s="27"/>
-      <c r="C229" s="523"/>
-      <c r="D229" s="526"/>
-      <c r="E229" s="526"/>
-      <c r="F229" s="526"/>
-      <c r="G229" s="526"/>
-      <c r="H229" s="526"/>
-      <c r="I229" s="529"/>
+      <c r="C229" s="529"/>
+      <c r="D229" s="550"/>
+      <c r="E229" s="550"/>
+      <c r="F229" s="550"/>
+      <c r="G229" s="550"/>
+      <c r="H229" s="550"/>
+      <c r="I229" s="553"/>
       <c r="J229" s="181" t="s">
         <v>37</v>
       </c>
@@ -29175,17 +29175,17 @@
     </row>
     <row r="230" spans="1:24">
       <c r="A230" s="30">
-        <f t="shared" ref="A230:B230" si="118">A229</f>
+        <f t="shared" ref="A230" si="118">A229</f>
         <v>2025002</v>
       </c>
       <c r="B230" s="27"/>
-      <c r="C230" s="523"/>
-      <c r="D230" s="526"/>
-      <c r="E230" s="526"/>
-      <c r="F230" s="526"/>
-      <c r="G230" s="526"/>
-      <c r="H230" s="526"/>
-      <c r="I230" s="529"/>
+      <c r="C230" s="529"/>
+      <c r="D230" s="550"/>
+      <c r="E230" s="550"/>
+      <c r="F230" s="550"/>
+      <c r="G230" s="550"/>
+      <c r="H230" s="550"/>
+      <c r="I230" s="553"/>
       <c r="J230" s="181" t="s">
         <v>38</v>
       </c>
@@ -29229,17 +29229,17 @@
     </row>
     <row r="231" spans="1:24">
       <c r="A231" s="30">
-        <f t="shared" ref="A231:B231" si="119">A230</f>
+        <f t="shared" ref="A231" si="119">A230</f>
         <v>2025002</v>
       </c>
       <c r="B231" s="27"/>
-      <c r="C231" s="523"/>
-      <c r="D231" s="526"/>
-      <c r="E231" s="526"/>
-      <c r="F231" s="526"/>
-      <c r="G231" s="526"/>
-      <c r="H231" s="526"/>
-      <c r="I231" s="529"/>
+      <c r="C231" s="529"/>
+      <c r="D231" s="550"/>
+      <c r="E231" s="550"/>
+      <c r="F231" s="550"/>
+      <c r="G231" s="550"/>
+      <c r="H231" s="550"/>
+      <c r="I231" s="553"/>
       <c r="J231" s="181" t="s">
         <v>26</v>
       </c>
@@ -29283,17 +29283,17 @@
     </row>
     <row r="232" spans="1:24">
       <c r="A232" s="30">
-        <f t="shared" ref="A232:B232" si="120">A231</f>
+        <f t="shared" ref="A232" si="120">A231</f>
         <v>2025002</v>
       </c>
       <c r="B232" s="27"/>
-      <c r="C232" s="523"/>
-      <c r="D232" s="526"/>
-      <c r="E232" s="526"/>
-      <c r="F232" s="526"/>
-      <c r="G232" s="526"/>
-      <c r="H232" s="526"/>
-      <c r="I232" s="529"/>
+      <c r="C232" s="529"/>
+      <c r="D232" s="550"/>
+      <c r="E232" s="550"/>
+      <c r="F232" s="550"/>
+      <c r="G232" s="550"/>
+      <c r="H232" s="550"/>
+      <c r="I232" s="553"/>
       <c r="J232" s="181" t="s">
         <v>27</v>
       </c>
@@ -29337,17 +29337,17 @@
     </row>
     <row r="233" spans="1:24">
       <c r="A233" s="30">
-        <f t="shared" ref="A233:B233" si="121">A232</f>
+        <f t="shared" ref="A233" si="121">A232</f>
         <v>2025002</v>
       </c>
       <c r="B233" s="27"/>
-      <c r="C233" s="523"/>
-      <c r="D233" s="526"/>
-      <c r="E233" s="526"/>
-      <c r="F233" s="526"/>
-      <c r="G233" s="526"/>
-      <c r="H233" s="526"/>
-      <c r="I233" s="529"/>
+      <c r="C233" s="529"/>
+      <c r="D233" s="550"/>
+      <c r="E233" s="550"/>
+      <c r="F233" s="550"/>
+      <c r="G233" s="550"/>
+      <c r="H233" s="550"/>
+      <c r="I233" s="553"/>
       <c r="J233" s="181" t="s">
         <v>28</v>
       </c>
@@ -29391,17 +29391,17 @@
     </row>
     <row r="234" spans="1:24">
       <c r="A234" s="30">
-        <f t="shared" ref="A234:B234" si="122">A233</f>
+        <f t="shared" ref="A234" si="122">A233</f>
         <v>2025002</v>
       </c>
       <c r="B234" s="27"/>
-      <c r="C234" s="524"/>
-      <c r="D234" s="527"/>
-      <c r="E234" s="527"/>
-      <c r="F234" s="527"/>
-      <c r="G234" s="527"/>
-      <c r="H234" s="527"/>
-      <c r="I234" s="530"/>
+      <c r="C234" s="530"/>
+      <c r="D234" s="551"/>
+      <c r="E234" s="551"/>
+      <c r="F234" s="551"/>
+      <c r="G234" s="551"/>
+      <c r="H234" s="551"/>
+      <c r="I234" s="554"/>
       <c r="J234" s="182" t="s">
         <v>29</v>
       </c>
@@ -29448,16 +29448,16 @@
         <v>2025003</v>
       </c>
       <c r="B235" s="2"/>
-      <c r="C235" s="522">
+      <c r="C235" s="528">
         <f t="shared" si="96"/>
         <v>30</v>
       </c>
-      <c r="D235" s="525"/>
-      <c r="E235" s="525"/>
-      <c r="F235" s="525"/>
-      <c r="G235" s="525"/>
-      <c r="H235" s="525"/>
-      <c r="I235" s="528" t="s">
+      <c r="D235" s="549"/>
+      <c r="E235" s="549"/>
+      <c r="F235" s="549"/>
+      <c r="G235" s="549"/>
+      <c r="H235" s="549"/>
+      <c r="I235" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J235" s="186" t="s">
@@ -29518,17 +29518,17 @@
     </row>
     <row r="236" spans="1:24">
       <c r="A236" s="30">
-        <f t="shared" ref="A236:B236" si="124">A235</f>
+        <f t="shared" ref="A236" si="124">A235</f>
         <v>2025003</v>
       </c>
       <c r="B236" s="27"/>
-      <c r="C236" s="523"/>
-      <c r="D236" s="526"/>
-      <c r="E236" s="526"/>
-      <c r="F236" s="526"/>
-      <c r="G236" s="526"/>
-      <c r="H236" s="526"/>
-      <c r="I236" s="529"/>
+      <c r="C236" s="529"/>
+      <c r="D236" s="550"/>
+      <c r="E236" s="550"/>
+      <c r="F236" s="550"/>
+      <c r="G236" s="550"/>
+      <c r="H236" s="550"/>
+      <c r="I236" s="553"/>
       <c r="J236" s="181" t="s">
         <v>25</v>
       </c>
@@ -29570,17 +29570,17 @@
     </row>
     <row r="237" spans="1:24">
       <c r="A237" s="30">
-        <f t="shared" ref="A237:B237" si="126">A236</f>
+        <f t="shared" ref="A237" si="126">A236</f>
         <v>2025003</v>
       </c>
       <c r="B237" s="27"/>
-      <c r="C237" s="523"/>
-      <c r="D237" s="526"/>
-      <c r="E237" s="526"/>
-      <c r="F237" s="526"/>
-      <c r="G237" s="526"/>
-      <c r="H237" s="526"/>
-      <c r="I237" s="529"/>
+      <c r="C237" s="529"/>
+      <c r="D237" s="550"/>
+      <c r="E237" s="550"/>
+      <c r="F237" s="550"/>
+      <c r="G237" s="550"/>
+      <c r="H237" s="550"/>
+      <c r="I237" s="553"/>
       <c r="J237" s="181" t="s">
         <v>37</v>
       </c>
@@ -29606,17 +29606,17 @@
     </row>
     <row r="238" spans="1:24">
       <c r="A238" s="30">
-        <f t="shared" ref="A238:B238" si="127">A237</f>
+        <f t="shared" ref="A238" si="127">A237</f>
         <v>2025003</v>
       </c>
       <c r="B238" s="27"/>
-      <c r="C238" s="523"/>
-      <c r="D238" s="526"/>
-      <c r="E238" s="526"/>
-      <c r="F238" s="526"/>
-      <c r="G238" s="526"/>
-      <c r="H238" s="526"/>
-      <c r="I238" s="529"/>
+      <c r="C238" s="529"/>
+      <c r="D238" s="550"/>
+      <c r="E238" s="550"/>
+      <c r="F238" s="550"/>
+      <c r="G238" s="550"/>
+      <c r="H238" s="550"/>
+      <c r="I238" s="553"/>
       <c r="J238" s="181" t="s">
         <v>38</v>
       </c>
@@ -29658,17 +29658,17 @@
     </row>
     <row r="239" spans="1:24">
       <c r="A239" s="30">
-        <f t="shared" ref="A239:B239" si="128">A238</f>
+        <f t="shared" ref="A239" si="128">A238</f>
         <v>2025003</v>
       </c>
       <c r="B239" s="27"/>
-      <c r="C239" s="523"/>
-      <c r="D239" s="526"/>
-      <c r="E239" s="526"/>
-      <c r="F239" s="526"/>
-      <c r="G239" s="526"/>
-      <c r="H239" s="526"/>
-      <c r="I239" s="529"/>
+      <c r="C239" s="529"/>
+      <c r="D239" s="550"/>
+      <c r="E239" s="550"/>
+      <c r="F239" s="550"/>
+      <c r="G239" s="550"/>
+      <c r="H239" s="550"/>
+      <c r="I239" s="553"/>
       <c r="J239" s="181" t="s">
         <v>26</v>
       </c>
@@ -29710,17 +29710,17 @@
     </row>
     <row r="240" spans="1:24">
       <c r="A240" s="30">
-        <f t="shared" ref="A240:B240" si="129">A239</f>
+        <f t="shared" ref="A240" si="129">A239</f>
         <v>2025003</v>
       </c>
       <c r="B240" s="27"/>
-      <c r="C240" s="523"/>
-      <c r="D240" s="526"/>
-      <c r="E240" s="526"/>
-      <c r="F240" s="526"/>
-      <c r="G240" s="526"/>
-      <c r="H240" s="526"/>
-      <c r="I240" s="529"/>
+      <c r="C240" s="529"/>
+      <c r="D240" s="550"/>
+      <c r="E240" s="550"/>
+      <c r="F240" s="550"/>
+      <c r="G240" s="550"/>
+      <c r="H240" s="550"/>
+      <c r="I240" s="553"/>
       <c r="J240" s="181" t="s">
         <v>27</v>
       </c>
@@ -29762,17 +29762,17 @@
     </row>
     <row r="241" spans="1:24">
       <c r="A241" s="30">
-        <f t="shared" ref="A241:B241" si="130">A240</f>
+        <f t="shared" ref="A241" si="130">A240</f>
         <v>2025003</v>
       </c>
       <c r="B241" s="27"/>
-      <c r="C241" s="523"/>
-      <c r="D241" s="526"/>
-      <c r="E241" s="526"/>
-      <c r="F241" s="526"/>
-      <c r="G241" s="526"/>
-      <c r="H241" s="526"/>
-      <c r="I241" s="529"/>
+      <c r="C241" s="529"/>
+      <c r="D241" s="550"/>
+      <c r="E241" s="550"/>
+      <c r="F241" s="550"/>
+      <c r="G241" s="550"/>
+      <c r="H241" s="550"/>
+      <c r="I241" s="553"/>
       <c r="J241" s="181" t="s">
         <v>28</v>
       </c>
@@ -29814,17 +29814,17 @@
     </row>
     <row r="242" spans="1:24">
       <c r="A242" s="30">
-        <f t="shared" ref="A242:B242" si="131">A241</f>
+        <f t="shared" ref="A242" si="131">A241</f>
         <v>2025003</v>
       </c>
       <c r="B242" s="27"/>
-      <c r="C242" s="524"/>
-      <c r="D242" s="527"/>
-      <c r="E242" s="527"/>
-      <c r="F242" s="527"/>
-      <c r="G242" s="527"/>
-      <c r="H242" s="527"/>
-      <c r="I242" s="530"/>
+      <c r="C242" s="530"/>
+      <c r="D242" s="551"/>
+      <c r="E242" s="551"/>
+      <c r="F242" s="551"/>
+      <c r="G242" s="551"/>
+      <c r="H242" s="551"/>
+      <c r="I242" s="554"/>
       <c r="J242" s="182" t="s">
         <v>29</v>
       </c>
@@ -29869,18 +29869,18 @@
         <v>2025007</v>
       </c>
       <c r="B243" s="2"/>
-      <c r="C243" s="522">
+      <c r="C243" s="528">
         <f t="shared" si="96"/>
         <v>31</v>
       </c>
-      <c r="D243" s="531"/>
-      <c r="E243" s="531" t="s">
+      <c r="D243" s="522"/>
+      <c r="E243" s="522" t="s">
         <v>97</v>
       </c>
-      <c r="F243" s="531"/>
-      <c r="G243" s="531"/>
-      <c r="H243" s="531"/>
-      <c r="I243" s="534" t="s">
+      <c r="F243" s="522"/>
+      <c r="G243" s="522"/>
+      <c r="H243" s="522"/>
+      <c r="I243" s="525" t="s">
         <v>31</v>
       </c>
       <c r="J243" s="186" t="s">
@@ -29941,17 +29941,17 @@
     </row>
     <row r="244" spans="1:24">
       <c r="A244" s="30">
-        <f t="shared" ref="A244:B244" si="133">A243</f>
+        <f t="shared" ref="A244" si="133">A243</f>
         <v>2025007</v>
       </c>
       <c r="B244" s="27"/>
-      <c r="C244" s="523"/>
-      <c r="D244" s="532"/>
-      <c r="E244" s="532"/>
-      <c r="F244" s="532"/>
-      <c r="G244" s="532"/>
-      <c r="H244" s="532"/>
-      <c r="I244" s="535"/>
+      <c r="C244" s="529"/>
+      <c r="D244" s="523"/>
+      <c r="E244" s="523"/>
+      <c r="F244" s="523"/>
+      <c r="G244" s="523"/>
+      <c r="H244" s="523"/>
+      <c r="I244" s="526"/>
       <c r="J244" s="181" t="s">
         <v>25</v>
       </c>
@@ -29979,17 +29979,17 @@
     </row>
     <row r="245" spans="1:24">
       <c r="A245" s="30">
-        <f t="shared" ref="A245:B245" si="135">A244</f>
+        <f t="shared" ref="A245" si="135">A244</f>
         <v>2025007</v>
       </c>
       <c r="B245" s="27"/>
-      <c r="C245" s="523"/>
-      <c r="D245" s="532"/>
-      <c r="E245" s="532"/>
-      <c r="F245" s="532"/>
-      <c r="G245" s="532"/>
-      <c r="H245" s="532"/>
-      <c r="I245" s="535"/>
+      <c r="C245" s="529"/>
+      <c r="D245" s="523"/>
+      <c r="E245" s="523"/>
+      <c r="F245" s="523"/>
+      <c r="G245" s="523"/>
+      <c r="H245" s="523"/>
+      <c r="I245" s="526"/>
       <c r="J245" s="181" t="s">
         <v>37</v>
       </c>
@@ -30013,17 +30013,17 @@
     </row>
     <row r="246" spans="1:24">
       <c r="A246" s="30">
-        <f t="shared" ref="A246:B246" si="136">A245</f>
+        <f t="shared" ref="A246" si="136">A245</f>
         <v>2025007</v>
       </c>
       <c r="B246" s="27"/>
-      <c r="C246" s="523"/>
-      <c r="D246" s="532"/>
-      <c r="E246" s="532"/>
-      <c r="F246" s="532"/>
-      <c r="G246" s="532"/>
-      <c r="H246" s="532"/>
-      <c r="I246" s="535"/>
+      <c r="C246" s="529"/>
+      <c r="D246" s="523"/>
+      <c r="E246" s="523"/>
+      <c r="F246" s="523"/>
+      <c r="G246" s="523"/>
+      <c r="H246" s="523"/>
+      <c r="I246" s="526"/>
       <c r="J246" s="181" t="s">
         <v>38</v>
       </c>
@@ -30051,17 +30051,17 @@
     </row>
     <row r="247" spans="1:24">
       <c r="A247" s="30">
-        <f t="shared" ref="A247:B247" si="137">A246</f>
+        <f t="shared" ref="A247" si="137">A246</f>
         <v>2025007</v>
       </c>
       <c r="B247" s="27"/>
-      <c r="C247" s="523"/>
-      <c r="D247" s="532"/>
-      <c r="E247" s="532"/>
-      <c r="F247" s="532"/>
-      <c r="G247" s="532"/>
-      <c r="H247" s="532"/>
-      <c r="I247" s="535"/>
+      <c r="C247" s="529"/>
+      <c r="D247" s="523"/>
+      <c r="E247" s="523"/>
+      <c r="F247" s="523"/>
+      <c r="G247" s="523"/>
+      <c r="H247" s="523"/>
+      <c r="I247" s="526"/>
       <c r="J247" s="181" t="s">
         <v>26</v>
       </c>
@@ -30089,17 +30089,17 @@
     </row>
     <row r="248" spans="1:24">
       <c r="A248" s="30">
-        <f t="shared" ref="A248:B248" si="138">A247</f>
+        <f t="shared" ref="A248" si="138">A247</f>
         <v>2025007</v>
       </c>
       <c r="B248" s="27"/>
-      <c r="C248" s="523"/>
-      <c r="D248" s="532"/>
-      <c r="E248" s="532"/>
-      <c r="F248" s="532"/>
-      <c r="G248" s="532"/>
-      <c r="H248" s="532"/>
-      <c r="I248" s="535"/>
+      <c r="C248" s="529"/>
+      <c r="D248" s="523"/>
+      <c r="E248" s="523"/>
+      <c r="F248" s="523"/>
+      <c r="G248" s="523"/>
+      <c r="H248" s="523"/>
+      <c r="I248" s="526"/>
       <c r="J248" s="181" t="s">
         <v>27</v>
       </c>
@@ -30127,17 +30127,17 @@
     </row>
     <row r="249" spans="1:24">
       <c r="A249" s="30">
-        <f t="shared" ref="A249:B249" si="139">A248</f>
+        <f t="shared" ref="A249" si="139">A248</f>
         <v>2025007</v>
       </c>
       <c r="B249" s="27"/>
-      <c r="C249" s="523"/>
-      <c r="D249" s="532"/>
-      <c r="E249" s="532"/>
-      <c r="F249" s="532"/>
-      <c r="G249" s="532"/>
-      <c r="H249" s="532"/>
-      <c r="I249" s="535"/>
+      <c r="C249" s="529"/>
+      <c r="D249" s="523"/>
+      <c r="E249" s="523"/>
+      <c r="F249" s="523"/>
+      <c r="G249" s="523"/>
+      <c r="H249" s="523"/>
+      <c r="I249" s="526"/>
       <c r="J249" s="181" t="s">
         <v>28</v>
       </c>
@@ -30165,17 +30165,17 @@
     </row>
     <row r="250" spans="1:24">
       <c r="A250" s="30">
-        <f t="shared" ref="A250:B250" si="140">A249</f>
+        <f t="shared" ref="A250" si="140">A249</f>
         <v>2025007</v>
       </c>
       <c r="B250" s="27"/>
-      <c r="C250" s="524"/>
-      <c r="D250" s="533"/>
-      <c r="E250" s="533"/>
-      <c r="F250" s="533"/>
-      <c r="G250" s="533"/>
-      <c r="H250" s="533"/>
-      <c r="I250" s="536"/>
+      <c r="C250" s="530"/>
+      <c r="D250" s="524"/>
+      <c r="E250" s="524"/>
+      <c r="F250" s="524"/>
+      <c r="G250" s="524"/>
+      <c r="H250" s="524"/>
+      <c r="I250" s="527"/>
       <c r="J250" s="182" t="s">
         <v>29</v>
       </c>
@@ -30206,16 +30206,16 @@
         <v>2024012</v>
       </c>
       <c r="B251" s="26"/>
-      <c r="C251" s="522">
+      <c r="C251" s="528">
         <f>C235+1</f>
         <v>31</v>
       </c>
-      <c r="D251" s="575"/>
-      <c r="E251" s="575"/>
-      <c r="F251" s="575"/>
-      <c r="G251" s="575"/>
-      <c r="H251" s="575"/>
-      <c r="I251" s="578" t="s">
+      <c r="D251" s="625"/>
+      <c r="E251" s="625"/>
+      <c r="F251" s="625"/>
+      <c r="G251" s="625"/>
+      <c r="H251" s="625"/>
+      <c r="I251" s="628" t="s">
         <v>31</v>
       </c>
       <c r="J251" s="186" t="s">
@@ -30276,17 +30276,17 @@
     </row>
     <row r="252" spans="1:24">
       <c r="A252" s="30">
-        <f t="shared" ref="A252:B252" si="142">A251</f>
+        <f t="shared" ref="A252" si="142">A251</f>
         <v>2024012</v>
       </c>
       <c r="B252" s="27"/>
-      <c r="C252" s="523"/>
-      <c r="D252" s="576"/>
-      <c r="E252" s="576"/>
-      <c r="F252" s="576"/>
-      <c r="G252" s="576"/>
-      <c r="H252" s="576"/>
-      <c r="I252" s="579"/>
+      <c r="C252" s="529"/>
+      <c r="D252" s="626"/>
+      <c r="E252" s="626"/>
+      <c r="F252" s="626"/>
+      <c r="G252" s="626"/>
+      <c r="H252" s="626"/>
+      <c r="I252" s="629"/>
       <c r="J252" s="181" t="s">
         <v>25</v>
       </c>
@@ -30322,17 +30322,17 @@
     </row>
     <row r="253" spans="1:24">
       <c r="A253" s="30">
-        <f t="shared" ref="A253:B253" si="144">A252</f>
+        <f t="shared" ref="A253" si="144">A252</f>
         <v>2024012</v>
       </c>
       <c r="B253" s="27"/>
-      <c r="C253" s="523"/>
-      <c r="D253" s="576"/>
-      <c r="E253" s="576"/>
-      <c r="F253" s="576"/>
-      <c r="G253" s="576"/>
-      <c r="H253" s="576"/>
-      <c r="I253" s="579"/>
+      <c r="C253" s="529"/>
+      <c r="D253" s="626"/>
+      <c r="E253" s="626"/>
+      <c r="F253" s="626"/>
+      <c r="G253" s="626"/>
+      <c r="H253" s="626"/>
+      <c r="I253" s="629"/>
       <c r="J253" s="181" t="s">
         <v>37</v>
       </c>
@@ -30358,17 +30358,17 @@
     </row>
     <row r="254" spans="1:24">
       <c r="A254" s="30">
-        <f t="shared" ref="A254:B254" si="145">A253</f>
+        <f t="shared" ref="A254" si="145">A253</f>
         <v>2024012</v>
       </c>
       <c r="B254" s="27"/>
-      <c r="C254" s="523"/>
-      <c r="D254" s="576"/>
-      <c r="E254" s="576"/>
-      <c r="F254" s="576"/>
-      <c r="G254" s="576"/>
-      <c r="H254" s="576"/>
-      <c r="I254" s="579"/>
+      <c r="C254" s="529"/>
+      <c r="D254" s="626"/>
+      <c r="E254" s="626"/>
+      <c r="F254" s="626"/>
+      <c r="G254" s="626"/>
+      <c r="H254" s="626"/>
+      <c r="I254" s="629"/>
       <c r="J254" s="181" t="s">
         <v>38</v>
       </c>
@@ -30404,17 +30404,17 @@
     </row>
     <row r="255" spans="1:24">
       <c r="A255" s="30">
-        <f t="shared" ref="A255:B255" si="146">A254</f>
+        <f t="shared" ref="A255" si="146">A254</f>
         <v>2024012</v>
       </c>
       <c r="B255" s="27"/>
-      <c r="C255" s="523"/>
-      <c r="D255" s="576"/>
-      <c r="E255" s="576"/>
-      <c r="F255" s="576"/>
-      <c r="G255" s="576"/>
-      <c r="H255" s="576"/>
-      <c r="I255" s="579"/>
+      <c r="C255" s="529"/>
+      <c r="D255" s="626"/>
+      <c r="E255" s="626"/>
+      <c r="F255" s="626"/>
+      <c r="G255" s="626"/>
+      <c r="H255" s="626"/>
+      <c r="I255" s="629"/>
       <c r="J255" s="181" t="s">
         <v>26</v>
       </c>
@@ -30450,17 +30450,17 @@
     </row>
     <row r="256" spans="1:24">
       <c r="A256" s="30">
-        <f t="shared" ref="A256:B256" si="147">A255</f>
+        <f t="shared" ref="A256" si="147">A255</f>
         <v>2024012</v>
       </c>
       <c r="B256" s="27"/>
-      <c r="C256" s="523"/>
-      <c r="D256" s="576"/>
-      <c r="E256" s="576"/>
-      <c r="F256" s="576"/>
-      <c r="G256" s="576"/>
-      <c r="H256" s="576"/>
-      <c r="I256" s="579"/>
+      <c r="C256" s="529"/>
+      <c r="D256" s="626"/>
+      <c r="E256" s="626"/>
+      <c r="F256" s="626"/>
+      <c r="G256" s="626"/>
+      <c r="H256" s="626"/>
+      <c r="I256" s="629"/>
       <c r="J256" s="181" t="s">
         <v>27</v>
       </c>
@@ -30496,17 +30496,17 @@
     </row>
     <row r="257" spans="1:24">
       <c r="A257" s="30">
-        <f t="shared" ref="A257:B257" si="148">A256</f>
+        <f t="shared" ref="A257" si="148">A256</f>
         <v>2024012</v>
       </c>
       <c r="B257" s="27"/>
-      <c r="C257" s="523"/>
-      <c r="D257" s="576"/>
-      <c r="E257" s="576"/>
-      <c r="F257" s="576"/>
-      <c r="G257" s="576"/>
-      <c r="H257" s="576"/>
-      <c r="I257" s="579"/>
+      <c r="C257" s="529"/>
+      <c r="D257" s="626"/>
+      <c r="E257" s="626"/>
+      <c r="F257" s="626"/>
+      <c r="G257" s="626"/>
+      <c r="H257" s="626"/>
+      <c r="I257" s="629"/>
       <c r="J257" s="181" t="s">
         <v>28</v>
       </c>
@@ -30542,17 +30542,17 @@
     </row>
     <row r="258" spans="1:24">
       <c r="A258" s="30">
-        <f t="shared" ref="A258:B258" si="149">A257</f>
+        <f t="shared" ref="A258" si="149">A257</f>
         <v>2024012</v>
       </c>
       <c r="B258" s="27"/>
-      <c r="C258" s="524"/>
-      <c r="D258" s="577"/>
-      <c r="E258" s="577"/>
-      <c r="F258" s="577"/>
-      <c r="G258" s="577"/>
-      <c r="H258" s="577"/>
-      <c r="I258" s="580"/>
+      <c r="C258" s="530"/>
+      <c r="D258" s="627"/>
+      <c r="E258" s="627"/>
+      <c r="F258" s="627"/>
+      <c r="G258" s="627"/>
+      <c r="H258" s="627"/>
+      <c r="I258" s="630"/>
       <c r="J258" s="182" t="s">
         <v>29</v>
       </c>
@@ -30591,16 +30591,16 @@
         <v>2025026</v>
       </c>
       <c r="B259" s="26"/>
-      <c r="C259" s="522">
+      <c r="C259" s="528">
         <f>C243+1</f>
         <v>32</v>
       </c>
-      <c r="D259" s="575"/>
-      <c r="E259" s="575"/>
-      <c r="F259" s="575"/>
-      <c r="G259" s="575"/>
-      <c r="H259" s="575"/>
-      <c r="I259" s="578" t="s">
+      <c r="D259" s="625"/>
+      <c r="E259" s="625"/>
+      <c r="F259" s="625"/>
+      <c r="G259" s="625"/>
+      <c r="H259" s="625"/>
+      <c r="I259" s="628" t="s">
         <v>31</v>
       </c>
       <c r="J259" s="186" t="s">
@@ -30661,17 +30661,17 @@
     </row>
     <row r="260" spans="1:24">
       <c r="A260" s="30">
-        <f t="shared" ref="A260:B260" si="151">A259</f>
+        <f t="shared" ref="A260" si="151">A259</f>
         <v>2025026</v>
       </c>
       <c r="B260" s="27"/>
-      <c r="C260" s="523"/>
-      <c r="D260" s="576"/>
-      <c r="E260" s="576"/>
-      <c r="F260" s="576"/>
-      <c r="G260" s="576"/>
-      <c r="H260" s="576"/>
-      <c r="I260" s="579"/>
+      <c r="C260" s="529"/>
+      <c r="D260" s="626"/>
+      <c r="E260" s="626"/>
+      <c r="F260" s="626"/>
+      <c r="G260" s="626"/>
+      <c r="H260" s="626"/>
+      <c r="I260" s="629"/>
       <c r="J260" s="181" t="s">
         <v>25</v>
       </c>
@@ -30699,17 +30699,17 @@
     </row>
     <row r="261" spans="1:24">
       <c r="A261" s="30">
-        <f t="shared" ref="A261:B261" si="153">A260</f>
+        <f t="shared" ref="A261" si="153">A260</f>
         <v>2025026</v>
       </c>
       <c r="B261" s="27"/>
-      <c r="C261" s="523"/>
-      <c r="D261" s="576"/>
-      <c r="E261" s="576"/>
-      <c r="F261" s="576"/>
-      <c r="G261" s="576"/>
-      <c r="H261" s="576"/>
-      <c r="I261" s="579"/>
+      <c r="C261" s="529"/>
+      <c r="D261" s="626"/>
+      <c r="E261" s="626"/>
+      <c r="F261" s="626"/>
+      <c r="G261" s="626"/>
+      <c r="H261" s="626"/>
+      <c r="I261" s="629"/>
       <c r="J261" s="181" t="s">
         <v>37</v>
       </c>
@@ -30735,17 +30735,17 @@
     </row>
     <row r="262" spans="1:24">
       <c r="A262" s="30">
-        <f t="shared" ref="A262:B262" si="154">A261</f>
+        <f t="shared" ref="A262" si="154">A261</f>
         <v>2025026</v>
       </c>
       <c r="B262" s="27"/>
-      <c r="C262" s="523"/>
-      <c r="D262" s="576"/>
-      <c r="E262" s="576"/>
-      <c r="F262" s="576"/>
-      <c r="G262" s="576"/>
-      <c r="H262" s="576"/>
-      <c r="I262" s="579"/>
+      <c r="C262" s="529"/>
+      <c r="D262" s="626"/>
+      <c r="E262" s="626"/>
+      <c r="F262" s="626"/>
+      <c r="G262" s="626"/>
+      <c r="H262" s="626"/>
+      <c r="I262" s="629"/>
       <c r="J262" s="181" t="s">
         <v>38</v>
       </c>
@@ -30773,17 +30773,17 @@
     </row>
     <row r="263" spans="1:24">
       <c r="A263" s="30">
-        <f t="shared" ref="A263:B263" si="155">A262</f>
+        <f t="shared" ref="A263" si="155">A262</f>
         <v>2025026</v>
       </c>
       <c r="B263" s="27"/>
-      <c r="C263" s="523"/>
-      <c r="D263" s="576"/>
-      <c r="E263" s="576"/>
-      <c r="F263" s="576"/>
-      <c r="G263" s="576"/>
-      <c r="H263" s="576"/>
-      <c r="I263" s="579"/>
+      <c r="C263" s="529"/>
+      <c r="D263" s="626"/>
+      <c r="E263" s="626"/>
+      <c r="F263" s="626"/>
+      <c r="G263" s="626"/>
+      <c r="H263" s="626"/>
+      <c r="I263" s="629"/>
       <c r="J263" s="181" t="s">
         <v>26</v>
       </c>
@@ -30811,17 +30811,17 @@
     </row>
     <row r="264" spans="1:24">
       <c r="A264" s="30">
-        <f t="shared" ref="A264:B264" si="156">A263</f>
+        <f t="shared" ref="A264" si="156">A263</f>
         <v>2025026</v>
       </c>
       <c r="B264" s="27"/>
-      <c r="C264" s="523"/>
-      <c r="D264" s="576"/>
-      <c r="E264" s="576"/>
-      <c r="F264" s="576"/>
-      <c r="G264" s="576"/>
-      <c r="H264" s="576"/>
-      <c r="I264" s="579"/>
+      <c r="C264" s="529"/>
+      <c r="D264" s="626"/>
+      <c r="E264" s="626"/>
+      <c r="F264" s="626"/>
+      <c r="G264" s="626"/>
+      <c r="H264" s="626"/>
+      <c r="I264" s="629"/>
       <c r="J264" s="181" t="s">
         <v>27</v>
       </c>
@@ -30849,17 +30849,17 @@
     </row>
     <row r="265" spans="1:24">
       <c r="A265" s="30">
-        <f t="shared" ref="A265:B265" si="157">A264</f>
+        <f t="shared" ref="A265" si="157">A264</f>
         <v>2025026</v>
       </c>
       <c r="B265" s="27"/>
-      <c r="C265" s="523"/>
-      <c r="D265" s="576"/>
-      <c r="E265" s="576"/>
-      <c r="F265" s="576"/>
-      <c r="G265" s="576"/>
-      <c r="H265" s="576"/>
-      <c r="I265" s="579"/>
+      <c r="C265" s="529"/>
+      <c r="D265" s="626"/>
+      <c r="E265" s="626"/>
+      <c r="F265" s="626"/>
+      <c r="G265" s="626"/>
+      <c r="H265" s="626"/>
+      <c r="I265" s="629"/>
       <c r="J265" s="181" t="s">
         <v>28</v>
       </c>
@@ -30887,17 +30887,17 @@
     </row>
     <row r="266" spans="1:24">
       <c r="A266" s="30">
-        <f t="shared" ref="A266:B266" si="158">A265</f>
+        <f t="shared" ref="A266" si="158">A265</f>
         <v>2025026</v>
       </c>
       <c r="B266" s="27"/>
-      <c r="C266" s="524"/>
-      <c r="D266" s="577"/>
-      <c r="E266" s="577"/>
-      <c r="F266" s="577"/>
-      <c r="G266" s="577"/>
-      <c r="H266" s="577"/>
-      <c r="I266" s="580"/>
+      <c r="C266" s="530"/>
+      <c r="D266" s="627"/>
+      <c r="E266" s="627"/>
+      <c r="F266" s="627"/>
+      <c r="G266" s="627"/>
+      <c r="H266" s="627"/>
+      <c r="I266" s="630"/>
       <c r="J266" s="182" t="s">
         <v>29</v>
       </c>
@@ -30928,16 +30928,16 @@
         <v>2025025</v>
       </c>
       <c r="B267" s="26"/>
-      <c r="C267" s="522">
+      <c r="C267" s="528">
         <f t="shared" ref="C267" si="159">C259+1</f>
         <v>33</v>
       </c>
-      <c r="D267" s="525"/>
-      <c r="E267" s="525"/>
-      <c r="F267" s="525"/>
-      <c r="G267" s="525"/>
-      <c r="H267" s="525"/>
-      <c r="I267" s="528" t="s">
+      <c r="D267" s="549"/>
+      <c r="E267" s="549"/>
+      <c r="F267" s="549"/>
+      <c r="G267" s="549"/>
+      <c r="H267" s="549"/>
+      <c r="I267" s="552" t="s">
         <v>31</v>
       </c>
       <c r="J267" s="186" t="s">
@@ -30998,17 +30998,17 @@
     </row>
     <row r="268" spans="1:24">
       <c r="A268" s="30">
-        <f t="shared" ref="A268:B268" si="161">A267</f>
+        <f t="shared" ref="A268" si="161">A267</f>
         <v>2025025</v>
       </c>
       <c r="B268" s="27"/>
-      <c r="C268" s="523"/>
-      <c r="D268" s="526"/>
-      <c r="E268" s="526"/>
-      <c r="F268" s="526"/>
-      <c r="G268" s="526"/>
-      <c r="H268" s="526"/>
-      <c r="I268" s="529"/>
+      <c r="C268" s="529"/>
+      <c r="D268" s="550"/>
+      <c r="E268" s="550"/>
+      <c r="F268" s="550"/>
+      <c r="G268" s="550"/>
+      <c r="H268" s="550"/>
+      <c r="I268" s="553"/>
       <c r="J268" s="181" t="s">
         <v>25</v>
       </c>
@@ -31045,13 +31045,13 @@
         <f t="shared" si="163"/>
         <v>0</v>
       </c>
-      <c r="C269" s="523"/>
-      <c r="D269" s="526"/>
-      <c r="E269" s="526"/>
-      <c r="F269" s="526"/>
-      <c r="G269" s="526"/>
-      <c r="H269" s="526"/>
-      <c r="I269" s="529"/>
+      <c r="C269" s="529"/>
+      <c r="D269" s="550"/>
+      <c r="E269" s="550"/>
+      <c r="F269" s="550"/>
+      <c r="G269" s="550"/>
+      <c r="H269" s="550"/>
+      <c r="I269" s="553"/>
       <c r="J269" s="181" t="s">
         <v>37</v>
       </c>
@@ -31084,13 +31084,13 @@
         <f t="shared" si="164"/>
         <v>0</v>
       </c>
-      <c r="C270" s="523"/>
-      <c r="D270" s="526"/>
-      <c r="E270" s="526"/>
-      <c r="F270" s="526"/>
-      <c r="G270" s="526"/>
-      <c r="H270" s="526"/>
-      <c r="I270" s="529"/>
+      <c r="C270" s="529"/>
+      <c r="D270" s="550"/>
+      <c r="E270" s="550"/>
+      <c r="F270" s="550"/>
+      <c r="G270" s="550"/>
+      <c r="H270" s="550"/>
+      <c r="I270" s="553"/>
       <c r="J270" s="181" t="s">
         <v>38</v>
       </c>
@@ -31127,13 +31127,13 @@
         <f t="shared" si="165"/>
         <v>0</v>
       </c>
-      <c r="C271" s="523"/>
-      <c r="D271" s="526"/>
-      <c r="E271" s="526"/>
-      <c r="F271" s="526"/>
-      <c r="G271" s="526"/>
-      <c r="H271" s="526"/>
-      <c r="I271" s="529"/>
+      <c r="C271" s="529"/>
+      <c r="D271" s="550"/>
+      <c r="E271" s="550"/>
+      <c r="F271" s="550"/>
+      <c r="G271" s="550"/>
+      <c r="H271" s="550"/>
+      <c r="I271" s="553"/>
       <c r="J271" s="181" t="s">
         <v>26</v>
       </c>
@@ -31170,13 +31170,13 @@
         <f t="shared" si="166"/>
         <v>0</v>
       </c>
-      <c r="C272" s="523"/>
-      <c r="D272" s="526"/>
-      <c r="E272" s="526"/>
-      <c r="F272" s="526"/>
-      <c r="G272" s="526"/>
-      <c r="H272" s="526"/>
-      <c r="I272" s="529"/>
+      <c r="C272" s="529"/>
+      <c r="D272" s="550"/>
+      <c r="E272" s="550"/>
+      <c r="F272" s="550"/>
+      <c r="G272" s="550"/>
+      <c r="H272" s="550"/>
+      <c r="I272" s="553"/>
       <c r="J272" s="181" t="s">
         <v>27</v>
       </c>
@@ -31213,13 +31213,13 @@
         <f t="shared" si="167"/>
         <v>0</v>
       </c>
-      <c r="C273" s="523"/>
-      <c r="D273" s="526"/>
-      <c r="E273" s="526"/>
-      <c r="F273" s="526"/>
-      <c r="G273" s="526"/>
-      <c r="H273" s="526"/>
-      <c r="I273" s="529"/>
+      <c r="C273" s="529"/>
+      <c r="D273" s="550"/>
+      <c r="E273" s="550"/>
+      <c r="F273" s="550"/>
+      <c r="G273" s="550"/>
+      <c r="H273" s="550"/>
+      <c r="I273" s="553"/>
       <c r="J273" s="181" t="s">
         <v>28</v>
       </c>
@@ -31256,13 +31256,13 @@
         <f t="shared" si="168"/>
         <v>0</v>
       </c>
-      <c r="C274" s="572"/>
-      <c r="D274" s="573"/>
-      <c r="E274" s="573"/>
-      <c r="F274" s="573"/>
-      <c r="G274" s="573"/>
-      <c r="H274" s="573"/>
-      <c r="I274" s="574"/>
+      <c r="C274" s="622"/>
+      <c r="D274" s="623"/>
+      <c r="E274" s="623"/>
+      <c r="F274" s="623"/>
+      <c r="G274" s="623"/>
+      <c r="H274" s="623"/>
+      <c r="I274" s="624"/>
       <c r="J274" s="212" t="s">
         <v>29</v>
       </c>
@@ -31293,13 +31293,13 @@
     <row r="275" spans="1:24" s="1" customFormat="1" ht="39" customHeight="1" thickTop="1">
       <c r="A275" s="28"/>
       <c r="B275" s="25"/>
-      <c r="C275" s="558"/>
-      <c r="D275" s="559"/>
-      <c r="E275" s="559"/>
-      <c r="F275" s="559"/>
-      <c r="G275" s="559"/>
-      <c r="H275" s="559"/>
-      <c r="I275" s="560"/>
+      <c r="C275" s="540"/>
+      <c r="D275" s="541"/>
+      <c r="E275" s="541"/>
+      <c r="F275" s="541"/>
+      <c r="G275" s="541"/>
+      <c r="H275" s="541"/>
+      <c r="I275" s="542"/>
       <c r="J275" s="205" t="str">
         <f>J2</f>
         <v>人件費合計</v>
@@ -32629,7 +32629,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="53">
-        <f t="shared" ref="A6:B16" si="3">+A5</f>
+        <f t="shared" ref="A6:A16" si="3">+A5</f>
         <v>2020031</v>
       </c>
       <c r="B6" s="54"/>
@@ -33343,7 +33343,7 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="53">
-        <f t="shared" ref="A18:B28" si="8">+A17</f>
+        <f t="shared" ref="A18:A28" si="8">+A17</f>
         <v>2022014</v>
       </c>
       <c r="B18" s="54"/>
@@ -39278,7 +39278,7 @@
         <v>2025020</v>
       </c>
       <c r="B122" s="146">
-        <f t="shared" ref="B115:B123" si="67">+B121</f>
+        <f t="shared" ref="B122:B123" si="67">+B121</f>
         <v>0</v>
       </c>
       <c r="C122" s="641"/>
